--- a/app/static/base_docs/DI July to December 2025.xlsx
+++ b/app/static/base_docs/DI July to December 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\base_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15265DA-8546-4BAC-86EE-0CAD167AEAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2399DD-E808-4877-9FB7-0373E37CB8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AC113C8-2A50-914F-A515-7C5B30E77858}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="Excel_BuiltIn_Print_Titles" localSheetId="3">'last page'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="78">
   <si>
     <t>DOCKET INVENTORY</t>
   </si>
@@ -417,9 +417,6 @@
     <t>(January to June 2025)</t>
   </si>
   <si>
-    <t>4568</t>
-  </si>
-  <si>
     <t>SC 214-012826</t>
   </si>
   <si>
@@ -451,6 +448,12 @@
   </si>
   <si>
     <t>ALL CASES</t>
+  </si>
+  <si>
+    <t>SC 213-121125</t>
+  </si>
+  <si>
+    <t>SC 218-050726</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1768,6 +1771,113 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1801,10 +1911,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1840,88 +1946,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1954,32 +1978,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2356,15 +2385,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IV61"/>
+  <dimension ref="A1:IV80"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="38" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="38" customWidth="1"/>
     <col min="3" max="3" width="32" style="38" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="38" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="38" customWidth="1"/>
+    <col min="5" max="5" width="15" style="38" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="38" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="38" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="38" customWidth="1"/>
     <col min="9" max="9" width="16" style="38" customWidth="1"/>
@@ -3194,36 +3223,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="203" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="203"/>
+      <c r="A2" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="180"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="180"/>
+      <c r="K2" s="180"/>
+      <c r="L2" s="180"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -3244,36 +3273,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
+      <c r="I4" s="181"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="181"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="204" t="s">
+      <c r="C5" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -3290,136 +3319,147 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="205" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="206"/>
-      <c r="C7" s="206"/>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="207"/>
+      <c r="A7" s="182" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="184"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="208"/>
-      <c r="B8" s="209"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="209"/>
-      <c r="L8" s="210"/>
+      <c r="A8" s="185"/>
+      <c r="B8" s="186"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="186"/>
+      <c r="H8" s="186"/>
+      <c r="I8" s="186"/>
+      <c r="J8" s="186"/>
+      <c r="K8" s="186"/>
+      <c r="L8" s="187"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="234" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="234" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="234" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="235" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="235" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="235" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="235" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="46" t="s">
+      <c r="I9" s="235" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="45" t="s">
+      <c r="J9" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="45" t="s">
+      <c r="L9" s="229" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="221"/>
-      <c r="B10" s="79" t="s">
-        <v>65</v>
+    <row r="10" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="236">
+        <v>1</v>
+      </c>
+      <c r="B10" s="174">
+        <v>4568</v>
       </c>
       <c r="C10" s="79"/>
       <c r="D10" s="79"/>
-      <c r="E10" s="222"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="222"/>
-      <c r="H10" s="222"/>
-      <c r="I10" s="222"/>
+      <c r="E10" s="172"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="172"/>
+      <c r="H10" s="172"/>
+      <c r="I10" s="172"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="223"/>
-      <c r="L10" s="79"/>
-    </row>
-    <row r="11" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="221"/>
-      <c r="B11" s="224">
+      <c r="K10" s="173"/>
+      <c r="L10" s="230"/>
+    </row>
+    <row r="11" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="236">
+        <f>A10+1</f>
+        <v>2</v>
+      </c>
+      <c r="B11" s="174">
         <v>4648</v>
       </c>
-      <c r="C11" s="225"/>
-      <c r="D11" s="225"/>
-      <c r="E11" s="226"/>
-      <c r="F11" s="226"/>
-      <c r="G11" s="226"/>
-      <c r="H11" s="226"/>
-      <c r="I11" s="226"/>
-      <c r="J11" s="225"/>
-      <c r="K11" s="224"/>
-      <c r="L11" s="225"/>
-    </row>
-    <row r="12" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="221"/>
-      <c r="B12" s="224">
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="174"/>
+      <c r="L11" s="231"/>
+    </row>
+    <row r="12" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="236">
+        <f t="shared" ref="A12:A73" si="0">A11+1</f>
+        <v>3</v>
+      </c>
+      <c r="B12" s="174">
         <v>4671</v>
       </c>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="226"/>
-      <c r="I12" s="227"/>
-      <c r="J12" s="227"/>
-      <c r="K12" s="224"/>
-      <c r="L12" s="225"/>
-    </row>
-    <row r="13" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="221"/>
-      <c r="B13" s="224">
-        <v>4674</v>
-      </c>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="226"/>
-      <c r="F13" s="224"/>
-      <c r="G13" s="224"/>
-      <c r="H13" s="224"/>
-      <c r="I13" s="224"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="227"/>
-      <c r="L13" s="225"/>
+      <c r="C12" s="175"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="177"/>
+      <c r="J12" s="177"/>
+      <c r="K12" s="174"/>
+      <c r="L12" s="231"/>
+    </row>
+    <row r="13" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="236">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B13" s="174">
+        <v>4713</v>
+      </c>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="177"/>
+      <c r="L13" s="231"/>
       <c r="M13" s="39"/>
       <c r="N13" s="39"/>
       <c r="O13" s="39"/>
@@ -3665,21 +3705,24 @@
       <c r="IU13" s="39"/>
       <c r="IV13" s="39"/>
     </row>
-    <row r="14" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="221"/>
-      <c r="B14" s="224">
-        <v>4693</v>
-      </c>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="228"/>
-      <c r="F14" s="224"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="224"/>
-      <c r="I14" s="224"/>
-      <c r="J14" s="225"/>
-      <c r="K14" s="224"/>
-      <c r="L14" s="225"/>
+    <row r="14" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="236">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B14" s="174">
+        <v>4715</v>
+      </c>
+      <c r="C14" s="175"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="174"/>
+      <c r="L14" s="231"/>
       <c r="M14" s="39"/>
       <c r="N14" s="39"/>
       <c r="O14" s="39"/>
@@ -3925,21 +3968,24 @@
       <c r="IU14" s="39"/>
       <c r="IV14" s="39"/>
     </row>
-    <row r="15" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="221"/>
-      <c r="B15" s="224">
-        <v>4713</v>
-      </c>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="224"/>
-      <c r="G15" s="226"/>
-      <c r="H15" s="224"/>
-      <c r="I15" s="224"/>
-      <c r="J15" s="225"/>
-      <c r="K15" s="224"/>
-      <c r="L15" s="225"/>
+    <row r="15" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="236">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B15" s="174">
+        <v>4716</v>
+      </c>
+      <c r="C15" s="175"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="174"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="174"/>
+      <c r="L15" s="231"/>
       <c r="M15" s="39"/>
       <c r="N15" s="39"/>
       <c r="O15" s="39"/>
@@ -4185,21 +4231,24 @@
       <c r="IU15" s="39"/>
       <c r="IV15" s="39"/>
     </row>
-    <row r="16" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="221"/>
-      <c r="B16" s="224">
-        <v>4715</v>
-      </c>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="224"/>
-      <c r="G16" s="226"/>
-      <c r="H16" s="224"/>
-      <c r="I16" s="224"/>
-      <c r="J16" s="225"/>
-      <c r="K16" s="224"/>
-      <c r="L16" s="225"/>
+    <row r="16" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="236">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B16" s="174">
+        <v>4717</v>
+      </c>
+      <c r="C16" s="175"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="178"/>
+      <c r="F16" s="174"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="175"/>
+      <c r="K16" s="174"/>
+      <c r="L16" s="231"/>
       <c r="M16" s="39"/>
       <c r="N16" s="39"/>
       <c r="O16" s="39"/>
@@ -4445,21 +4494,24 @@
       <c r="IU16" s="39"/>
       <c r="IV16" s="39"/>
     </row>
-    <row r="17" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="221"/>
-      <c r="B17" s="224">
-        <v>4716</v>
-      </c>
-      <c r="C17" s="225"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="224"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="224"/>
-      <c r="I17" s="224"/>
-      <c r="J17" s="225"/>
-      <c r="K17" s="224"/>
-      <c r="L17" s="225"/>
+    <row r="17" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="236">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B17" s="174">
+        <v>4718</v>
+      </c>
+      <c r="C17" s="175"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="174"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="174"/>
+      <c r="I17" s="174"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="174"/>
+      <c r="L17" s="231"/>
       <c r="M17" s="39"/>
       <c r="N17" s="39"/>
       <c r="O17" s="39"/>
@@ -4705,21 +4757,24 @@
       <c r="IU17" s="39"/>
       <c r="IV17" s="39"/>
     </row>
-    <row r="18" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="221"/>
-      <c r="B18" s="224">
-        <v>4717</v>
-      </c>
-      <c r="C18" s="225"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="224"/>
-      <c r="G18" s="226"/>
-      <c r="H18" s="224"/>
-      <c r="I18" s="224"/>
-      <c r="J18" s="225"/>
-      <c r="K18" s="224"/>
-      <c r="L18" s="225"/>
+    <row r="18" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="236">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B18" s="174">
+        <v>4719</v>
+      </c>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="174"/>
+      <c r="G18" s="176"/>
+      <c r="H18" s="174"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="174"/>
+      <c r="L18" s="231"/>
       <c r="M18" s="39"/>
       <c r="N18" s="39"/>
       <c r="O18" s="39"/>
@@ -4965,21 +5020,24 @@
       <c r="IU18" s="39"/>
       <c r="IV18" s="39"/>
     </row>
-    <row r="19" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="221"/>
-      <c r="B19" s="224">
-        <v>4718</v>
-      </c>
-      <c r="C19" s="225"/>
-      <c r="D19" s="225"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="224"/>
-      <c r="G19" s="226"/>
-      <c r="H19" s="224"/>
-      <c r="I19" s="224"/>
-      <c r="J19" s="225"/>
-      <c r="K19" s="224"/>
-      <c r="L19" s="225"/>
+    <row r="19" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="236">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B19" s="174">
+        <v>4720</v>
+      </c>
+      <c r="C19" s="175"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="174"/>
+      <c r="L19" s="231"/>
       <c r="M19" s="39"/>
       <c r="N19" s="39"/>
       <c r="O19" s="39"/>
@@ -5225,21 +5283,24 @@
       <c r="IU19" s="39"/>
       <c r="IV19" s="39"/>
     </row>
-    <row r="20" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="221"/>
-      <c r="B20" s="224">
-        <v>4719</v>
-      </c>
-      <c r="C20" s="225"/>
-      <c r="D20" s="225"/>
-      <c r="E20" s="228"/>
-      <c r="F20" s="224"/>
-      <c r="G20" s="226"/>
-      <c r="H20" s="224"/>
-      <c r="I20" s="224"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="224"/>
-      <c r="L20" s="225"/>
+    <row r="20" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="236">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B20" s="174">
+        <v>4721</v>
+      </c>
+      <c r="C20" s="175"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="174"/>
+      <c r="I20" s="174"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="174"/>
+      <c r="L20" s="231"/>
       <c r="M20" s="39"/>
       <c r="N20" s="39"/>
       <c r="O20" s="39"/>
@@ -5485,21 +5546,24 @@
       <c r="IU20" s="39"/>
       <c r="IV20" s="39"/>
     </row>
-    <row r="21" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="221"/>
-      <c r="B21" s="224">
-        <v>4720</v>
-      </c>
-      <c r="C21" s="225"/>
-      <c r="D21" s="225"/>
-      <c r="E21" s="228"/>
-      <c r="F21" s="224"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="224"/>
-      <c r="I21" s="224"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="224"/>
-      <c r="L21" s="225"/>
+    <row r="21" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="236">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B21" s="174">
+        <v>4722</v>
+      </c>
+      <c r="C21" s="175"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="174"/>
+      <c r="L21" s="231"/>
       <c r="M21" s="39"/>
       <c r="N21" s="39"/>
       <c r="O21" s="39"/>
@@ -5745,21 +5809,24 @@
       <c r="IU21" s="39"/>
       <c r="IV21" s="39"/>
     </row>
-    <row r="22" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="221"/>
-      <c r="B22" s="224">
-        <v>4721</v>
-      </c>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="228"/>
-      <c r="F22" s="224"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="224"/>
-      <c r="I22" s="224"/>
-      <c r="J22" s="225"/>
-      <c r="K22" s="224"/>
-      <c r="L22" s="225"/>
+    <row r="22" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="236">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B22" s="174">
+        <v>4723</v>
+      </c>
+      <c r="C22" s="175"/>
+      <c r="D22" s="175"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="176"/>
+      <c r="H22" s="174"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="231"/>
       <c r="M22" s="39"/>
       <c r="N22" s="39"/>
       <c r="O22" s="39"/>
@@ -6005,21 +6072,24 @@
       <c r="IU22" s="39"/>
       <c r="IV22" s="39"/>
     </row>
-    <row r="23" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="221"/>
-      <c r="B23" s="224">
-        <v>4722</v>
-      </c>
-      <c r="C23" s="225"/>
-      <c r="D23" s="225"/>
-      <c r="E23" s="228"/>
-      <c r="F23" s="224"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="224"/>
-      <c r="I23" s="224"/>
-      <c r="J23" s="225"/>
-      <c r="K23" s="224"/>
-      <c r="L23" s="225"/>
+    <row r="23" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="236">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B23" s="60">
+        <v>4724</v>
+      </c>
+      <c r="C23" s="175"/>
+      <c r="D23" s="175"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="176"/>
+      <c r="H23" s="174"/>
+      <c r="I23" s="174"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="174"/>
+      <c r="L23" s="231"/>
       <c r="M23" s="39"/>
       <c r="N23" s="39"/>
       <c r="O23" s="39"/>
@@ -6265,21 +6335,24 @@
       <c r="IU23" s="39"/>
       <c r="IV23" s="39"/>
     </row>
-    <row r="24" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="221"/>
-      <c r="B24" s="224">
-        <v>4723</v>
-      </c>
-      <c r="C24" s="225"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="228"/>
-      <c r="F24" s="224"/>
-      <c r="G24" s="226"/>
-      <c r="H24" s="224"/>
-      <c r="I24" s="224"/>
-      <c r="J24" s="225"/>
-      <c r="K24" s="224"/>
-      <c r="L24" s="225"/>
+    <row r="24" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="236">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B24" s="60">
+        <v>4725</v>
+      </c>
+      <c r="C24" s="175"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="174"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="174"/>
+      <c r="L24" s="231"/>
       <c r="M24" s="39"/>
       <c r="N24" s="39"/>
       <c r="O24" s="39"/>
@@ -6526,607 +6599,1048 @@
       <c r="IV24" s="39"/>
     </row>
     <row r="25" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="224"/>
-      <c r="B25" s="224">
-        <v>4724</v>
-      </c>
-      <c r="C25" s="224"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="224"/>
-      <c r="F25" s="224"/>
-      <c r="G25" s="224"/>
-      <c r="H25" s="224"/>
-      <c r="I25" s="224"/>
-      <c r="J25" s="224"/>
-      <c r="K25" s="224"/>
-      <c r="L25" s="224"/>
+      <c r="A25" s="236">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B25" s="60">
+        <v>4726</v>
+      </c>
+      <c r="C25" s="174"/>
+      <c r="D25" s="174"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="232"/>
     </row>
     <row r="26" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="224"/>
-      <c r="B26" s="224">
-        <v>4725</v>
-      </c>
-      <c r="C26" s="224"/>
-      <c r="D26" s="224"/>
-      <c r="E26" s="224"/>
-      <c r="F26" s="224"/>
-      <c r="G26" s="224"/>
-      <c r="H26" s="224"/>
-      <c r="I26" s="224"/>
-      <c r="J26" s="224"/>
-      <c r="K26" s="224"/>
-      <c r="L26" s="224"/>
+      <c r="A26" s="236">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B26" s="60">
+        <v>4732</v>
+      </c>
+      <c r="C26" s="174"/>
+      <c r="D26" s="174"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="174"/>
+      <c r="H26" s="174"/>
+      <c r="I26" s="174"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="174"/>
+      <c r="L26" s="232"/>
     </row>
     <row r="27" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="224"/>
-      <c r="B27" s="224">
-        <v>4726</v>
-      </c>
-      <c r="C27" s="224"/>
-      <c r="D27" s="224"/>
-      <c r="E27" s="224"/>
-      <c r="F27" s="224"/>
-      <c r="G27" s="224"/>
-      <c r="H27" s="224"/>
-      <c r="I27" s="224"/>
-      <c r="J27" s="224"/>
-      <c r="K27" s="224"/>
-      <c r="L27" s="224"/>
+      <c r="A27" s="236">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B27" s="60">
+        <v>4733</v>
+      </c>
+      <c r="C27" s="174"/>
+      <c r="D27" s="174"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="232"/>
     </row>
     <row r="28" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="224"/>
-      <c r="B28" s="224">
+      <c r="A28" s="236">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B28" s="60">
+        <v>4734</v>
+      </c>
+      <c r="C28" s="174"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="232"/>
+    </row>
+    <row r="29" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="236">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B29" s="60">
+        <v>4735</v>
+      </c>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="232"/>
+    </row>
+    <row r="30" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="236">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B30" s="60">
+        <v>4736</v>
+      </c>
+      <c r="C30" s="174"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="232"/>
+    </row>
+    <row r="31" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="236">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B31" s="60">
         <v>4737</v>
       </c>
-      <c r="C28" s="224"/>
-      <c r="D28" s="224"/>
-      <c r="E28" s="224"/>
-      <c r="F28" s="224"/>
-      <c r="G28" s="224"/>
-      <c r="H28" s="224"/>
-      <c r="I28" s="224"/>
-      <c r="J28" s="224"/>
-      <c r="K28" s="224"/>
-      <c r="L28" s="224"/>
-    </row>
-    <row r="29" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="224"/>
-      <c r="B29" s="224">
+      <c r="C31" s="174"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="232"/>
+    </row>
+    <row r="32" spans="1:256" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="236">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B32" s="60">
+        <v>4738</v>
+      </c>
+      <c r="C32" s="174"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="232"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="236">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B33" s="60">
+        <v>4739</v>
+      </c>
+      <c r="C33" s="174"/>
+      <c r="D33" s="174"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="174"/>
+      <c r="H33" s="174"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="174"/>
+      <c r="L33" s="232"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="236">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B34" s="60">
         <v>4740</v>
       </c>
-      <c r="C29" s="224"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="224"/>
-      <c r="F29" s="224"/>
-      <c r="G29" s="224"/>
-      <c r="H29" s="224"/>
-      <c r="I29" s="224"/>
-      <c r="J29" s="224"/>
-      <c r="K29" s="224"/>
-      <c r="L29" s="224"/>
-    </row>
-    <row r="30" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="224"/>
-      <c r="B30" s="224">
+      <c r="C34" s="174"/>
+      <c r="D34" s="174"/>
+      <c r="E34" s="174"/>
+      <c r="F34" s="174"/>
+      <c r="G34" s="174"/>
+      <c r="H34" s="174"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="174"/>
+      <c r="L34" s="232"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="236">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B35" s="60">
+        <v>4741</v>
+      </c>
+      <c r="C35" s="174"/>
+      <c r="D35" s="174"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="174"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="232"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="236">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B36" s="60">
+        <v>4742</v>
+      </c>
+      <c r="C36" s="174"/>
+      <c r="D36" s="174"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
+      <c r="H36" s="174"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="174"/>
+      <c r="K36" s="174"/>
+      <c r="L36" s="232"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="236">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B37" s="60">
+        <v>4743</v>
+      </c>
+      <c r="C37" s="174"/>
+      <c r="D37" s="174"/>
+      <c r="E37" s="174"/>
+      <c r="F37" s="174"/>
+      <c r="G37" s="174"/>
+      <c r="H37" s="174"/>
+      <c r="I37" s="174"/>
+      <c r="J37" s="174"/>
+      <c r="K37" s="174"/>
+      <c r="L37" s="232"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="236">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B38" s="60">
+        <v>4744</v>
+      </c>
+      <c r="C38" s="174"/>
+      <c r="D38" s="174"/>
+      <c r="E38" s="174"/>
+      <c r="F38" s="174"/>
+      <c r="G38" s="174"/>
+      <c r="H38" s="174"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="174"/>
+      <c r="K38" s="174"/>
+      <c r="L38" s="232"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="236">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B39" s="60">
+        <v>4745</v>
+      </c>
+      <c r="C39" s="174"/>
+      <c r="D39" s="174"/>
+      <c r="E39" s="174"/>
+      <c r="F39" s="174"/>
+      <c r="G39" s="174"/>
+      <c r="H39" s="174"/>
+      <c r="I39" s="174"/>
+      <c r="J39" s="174"/>
+      <c r="K39" s="174"/>
+      <c r="L39" s="232"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="236">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B40" s="60">
+        <v>4747</v>
+      </c>
+      <c r="C40" s="174"/>
+      <c r="D40" s="174"/>
+      <c r="E40" s="174"/>
+      <c r="F40" s="174"/>
+      <c r="G40" s="174"/>
+      <c r="H40" s="174"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="174"/>
+      <c r="K40" s="174"/>
+      <c r="L40" s="232"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="236">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B41" s="60">
+        <v>4748</v>
+      </c>
+      <c r="C41" s="174"/>
+      <c r="D41" s="174"/>
+      <c r="E41" s="174"/>
+      <c r="F41" s="174"/>
+      <c r="G41" s="174"/>
+      <c r="H41" s="174"/>
+      <c r="I41" s="174"/>
+      <c r="J41" s="174"/>
+      <c r="K41" s="174"/>
+      <c r="L41" s="232"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="236">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B42" s="60">
+        <v>4750</v>
+      </c>
+      <c r="C42" s="174"/>
+      <c r="D42" s="174"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="174"/>
+      <c r="H42" s="174"/>
+      <c r="I42" s="174"/>
+      <c r="J42" s="174"/>
+      <c r="K42" s="174"/>
+      <c r="L42" s="232"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="236">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B43" s="60">
+        <v>4751</v>
+      </c>
+      <c r="C43" s="174"/>
+      <c r="D43" s="174"/>
+      <c r="E43" s="174"/>
+      <c r="F43" s="174"/>
+      <c r="G43" s="174"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="232"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="236">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B44" s="60">
+        <v>4752</v>
+      </c>
+      <c r="C44" s="174"/>
+      <c r="D44" s="174"/>
+      <c r="E44" s="174"/>
+      <c r="F44" s="174"/>
+      <c r="G44" s="174"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="232"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="236">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B45" s="60">
+        <v>4753</v>
+      </c>
+      <c r="C45" s="174"/>
+      <c r="D45" s="174"/>
+      <c r="E45" s="174"/>
+      <c r="F45" s="174"/>
+      <c r="G45" s="174"/>
+      <c r="H45" s="174"/>
+      <c r="I45" s="174"/>
+      <c r="J45" s="174"/>
+      <c r="K45" s="174"/>
+      <c r="L45" s="232"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="236">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B46" s="60">
+        <v>4755</v>
+      </c>
+      <c r="C46" s="174"/>
+      <c r="D46" s="174"/>
+      <c r="E46" s="174"/>
+      <c r="F46" s="174"/>
+      <c r="G46" s="174"/>
+      <c r="H46" s="174"/>
+      <c r="I46" s="174"/>
+      <c r="J46" s="174"/>
+      <c r="K46" s="174"/>
+      <c r="L46" s="232"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A47" s="171">
+        <v>38</v>
+      </c>
+      <c r="B47" s="60">
+        <v>4754</v>
+      </c>
+      <c r="C47" s="174"/>
+      <c r="D47" s="174"/>
+      <c r="E47" s="174"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="174"/>
+      <c r="H47" s="174"/>
+      <c r="I47" s="174"/>
+      <c r="J47" s="174"/>
+      <c r="K47" s="174"/>
+      <c r="L47" s="232"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="236">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B48" s="60">
+        <v>4756</v>
+      </c>
+      <c r="C48" s="174"/>
+      <c r="D48" s="174"/>
+      <c r="E48" s="174"/>
+      <c r="F48" s="174"/>
+      <c r="G48" s="174"/>
+      <c r="H48" s="174"/>
+      <c r="I48" s="174"/>
+      <c r="J48" s="174"/>
+      <c r="K48" s="174"/>
+      <c r="L48" s="232"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="236">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B49" s="60">
+        <v>4749</v>
+      </c>
+      <c r="C49" s="174"/>
+      <c r="D49" s="174"/>
+      <c r="E49" s="174"/>
+      <c r="F49" s="174"/>
+      <c r="G49" s="174"/>
+      <c r="H49" s="174"/>
+      <c r="I49" s="174"/>
+      <c r="J49" s="174"/>
+      <c r="K49" s="174"/>
+      <c r="L49" s="232"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="236">
+        <f>A49+1</f>
+        <v>41</v>
+      </c>
+      <c r="B50" s="60">
         <v>4746</v>
       </c>
-      <c r="C30" s="224"/>
-      <c r="D30" s="224"/>
-      <c r="E30" s="224"/>
-      <c r="F30" s="224"/>
-      <c r="G30" s="224"/>
-      <c r="H30" s="224"/>
-      <c r="I30" s="224"/>
-      <c r="J30" s="224"/>
-      <c r="K30" s="224"/>
-      <c r="L30" s="224"/>
-    </row>
-    <row r="31" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="224"/>
-      <c r="B31" s="224">
-        <v>4748</v>
-      </c>
-      <c r="C31" s="224"/>
-      <c r="D31" s="224"/>
-      <c r="E31" s="224"/>
-      <c r="F31" s="224"/>
-      <c r="G31" s="224"/>
-      <c r="H31" s="224"/>
-      <c r="I31" s="224"/>
-      <c r="J31" s="224"/>
-      <c r="K31" s="224"/>
-      <c r="L31" s="224"/>
-    </row>
-    <row r="32" spans="1:256" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="224"/>
-      <c r="B32" s="224">
-        <v>4749</v>
-      </c>
-      <c r="C32" s="224"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="224"/>
-      <c r="F32" s="224"/>
-      <c r="G32" s="224"/>
-      <c r="H32" s="224"/>
-      <c r="I32" s="224"/>
-      <c r="J32" s="224"/>
-      <c r="K32" s="224"/>
-      <c r="L32" s="224"/>
-    </row>
-    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="224"/>
-      <c r="B33" s="224">
-        <v>4750</v>
-      </c>
-      <c r="C33" s="224"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="224"/>
-      <c r="F33" s="224"/>
-      <c r="G33" s="224"/>
-      <c r="H33" s="224"/>
-      <c r="I33" s="224"/>
-      <c r="J33" s="224"/>
-      <c r="K33" s="224"/>
-      <c r="L33" s="224"/>
-    </row>
-    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="224"/>
-      <c r="B34" s="224">
-        <v>4752</v>
-      </c>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
-      <c r="I34" s="224"/>
-      <c r="J34" s="224"/>
-      <c r="K34" s="224"/>
-      <c r="L34" s="224"/>
-    </row>
-    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="224"/>
-      <c r="B35" s="224">
-        <v>4753</v>
-      </c>
-      <c r="C35" s="224"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="224"/>
-      <c r="F35" s="224"/>
-      <c r="G35" s="224"/>
-      <c r="H35" s="224"/>
-      <c r="I35" s="224"/>
-      <c r="J35" s="224"/>
-      <c r="K35" s="224"/>
-      <c r="L35" s="224"/>
-    </row>
-    <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="224"/>
-      <c r="B36" s="224">
-        <v>4754</v>
-      </c>
-      <c r="C36" s="224"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="224"/>
-      <c r="F36" s="224"/>
-      <c r="G36" s="224"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="224"/>
-      <c r="J36" s="224"/>
-      <c r="K36" s="224"/>
-      <c r="L36" s="224"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="224"/>
-      <c r="B37" s="224">
-        <v>4756</v>
-      </c>
-      <c r="C37" s="224"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="224"/>
-      <c r="F37" s="224"/>
-      <c r="G37" s="224"/>
-      <c r="H37" s="224"/>
-      <c r="I37" s="224"/>
-      <c r="J37" s="224"/>
-      <c r="K37" s="224"/>
-      <c r="L37" s="224"/>
-    </row>
-    <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="224"/>
-      <c r="B38" s="224"/>
-      <c r="C38" s="224"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="224"/>
-      <c r="F38" s="224"/>
-      <c r="G38" s="224"/>
-      <c r="H38" s="224"/>
-      <c r="I38" s="224"/>
-      <c r="J38" s="224"/>
-      <c r="K38" s="224"/>
-      <c r="L38" s="224"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="224"/>
-      <c r="B39" s="224">
+      <c r="C50" s="174"/>
+      <c r="D50" s="174"/>
+      <c r="E50" s="174"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="174"/>
+      <c r="H50" s="174"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="174"/>
+      <c r="K50" s="174"/>
+      <c r="L50" s="232"/>
+    </row>
+    <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="236">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B51" s="60">
+        <v>4674</v>
+      </c>
+      <c r="C51" s="174"/>
+      <c r="D51" s="174"/>
+      <c r="E51" s="174"/>
+      <c r="F51" s="174"/>
+      <c r="G51" s="174"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="174"/>
+      <c r="K51" s="174"/>
+      <c r="L51" s="232"/>
+    </row>
+    <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="236">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B52" s="60">
+        <v>4693</v>
+      </c>
+      <c r="C52" s="174"/>
+      <c r="D52" s="174"/>
+      <c r="E52" s="174"/>
+      <c r="F52" s="174"/>
+      <c r="G52" s="174"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="174"/>
+      <c r="K52" s="174"/>
+      <c r="L52" s="232"/>
+    </row>
+    <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="236"/>
+      <c r="B53" s="60"/>
+      <c r="C53" s="174"/>
+      <c r="D53" s="174"/>
+      <c r="E53" s="174"/>
+      <c r="F53" s="174"/>
+      <c r="G53" s="174"/>
+      <c r="H53" s="174"/>
+      <c r="I53" s="174"/>
+      <c r="J53" s="174"/>
+      <c r="K53" s="174"/>
+      <c r="L53" s="232"/>
+    </row>
+    <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="236"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="174"/>
+      <c r="D54" s="174"/>
+      <c r="E54" s="174"/>
+      <c r="F54" s="174"/>
+      <c r="G54" s="174"/>
+      <c r="H54" s="174"/>
+      <c r="I54" s="174"/>
+      <c r="J54" s="174"/>
+      <c r="K54" s="174"/>
+      <c r="L54" s="232"/>
+    </row>
+    <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="236">
+        <v>1</v>
+      </c>
+      <c r="B55" s="60">
         <v>733</v>
       </c>
-      <c r="C39" s="224"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="224"/>
-      <c r="H39" s="224"/>
-      <c r="I39" s="224"/>
-      <c r="J39" s="224"/>
-      <c r="K39" s="224"/>
-      <c r="L39" s="224"/>
-    </row>
-    <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="224"/>
-      <c r="B40" s="224">
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
+      <c r="H55" s="174"/>
+      <c r="I55" s="174"/>
+      <c r="J55" s="174"/>
+      <c r="K55" s="174"/>
+      <c r="L55" s="232"/>
+    </row>
+    <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="236">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B56" s="60">
+        <v>755</v>
+      </c>
+      <c r="C56" s="174"/>
+      <c r="D56" s="174"/>
+      <c r="E56" s="174"/>
+      <c r="F56" s="174"/>
+      <c r="G56" s="174"/>
+      <c r="H56" s="174"/>
+      <c r="I56" s="174"/>
+      <c r="J56" s="174"/>
+      <c r="K56" s="174"/>
+      <c r="L56" s="232"/>
+    </row>
+    <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="236">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B57" s="60">
+        <v>760</v>
+      </c>
+      <c r="C57" s="174"/>
+      <c r="D57" s="174"/>
+      <c r="E57" s="174"/>
+      <c r="F57" s="174"/>
+      <c r="G57" s="174"/>
+      <c r="H57" s="174"/>
+      <c r="I57" s="174"/>
+      <c r="J57" s="174"/>
+      <c r="K57" s="174"/>
+      <c r="L57" s="232"/>
+    </row>
+    <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="236">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B58" s="60">
+        <v>762</v>
+      </c>
+      <c r="C58" s="174"/>
+      <c r="D58" s="174"/>
+      <c r="E58" s="174"/>
+      <c r="F58" s="174"/>
+      <c r="G58" s="174"/>
+      <c r="H58" s="174"/>
+      <c r="I58" s="174"/>
+      <c r="J58" s="174"/>
+      <c r="K58" s="174"/>
+      <c r="L58" s="232"/>
+    </row>
+    <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="236">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B59" s="60">
+        <v>763</v>
+      </c>
+      <c r="C59" s="174"/>
+      <c r="D59" s="174"/>
+      <c r="E59" s="174"/>
+      <c r="F59" s="174"/>
+      <c r="G59" s="174"/>
+      <c r="H59" s="174"/>
+      <c r="I59" s="174"/>
+      <c r="J59" s="174"/>
+      <c r="K59" s="174"/>
+      <c r="L59" s="232"/>
+    </row>
+    <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="236">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B60" s="60">
+        <v>765</v>
+      </c>
+      <c r="C60" s="174"/>
+      <c r="D60" s="174"/>
+      <c r="E60" s="174"/>
+      <c r="F60" s="174"/>
+      <c r="G60" s="174"/>
+      <c r="H60" s="174"/>
+      <c r="I60" s="174"/>
+      <c r="J60" s="174"/>
+      <c r="K60" s="174"/>
+      <c r="L60" s="232"/>
+    </row>
+    <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="236">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B61" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
+      <c r="J61" s="60"/>
+      <c r="K61" s="60"/>
+    </row>
+    <row r="62" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="236">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B62" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="60"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="236">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B63" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="236">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B64" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="60"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="60"/>
+    </row>
+    <row r="65" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="236">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B65" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="60"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+    </row>
+    <row r="66" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="236">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B66" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+    </row>
+    <row r="67" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="236">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B67" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="60"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="60"/>
+    </row>
+    <row r="68" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="171">
+        <v>14</v>
+      </c>
+      <c r="B68" s="60">
         <v>744</v>
       </c>
-      <c r="C40" s="224"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="224"/>
-      <c r="F40" s="224"/>
-      <c r="G40" s="224"/>
-      <c r="H40" s="224"/>
-      <c r="I40" s="224"/>
-      <c r="J40" s="224"/>
-      <c r="K40" s="224"/>
-      <c r="L40" s="224"/>
-    </row>
-    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="224"/>
-      <c r="B41" s="224">
+      <c r="C68" s="60"/>
+      <c r="D68" s="60"/>
+      <c r="E68" s="60"/>
+      <c r="F68" s="60"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="60"/>
+      <c r="I68" s="60"/>
+      <c r="J68" s="60"/>
+      <c r="K68" s="60"/>
+    </row>
+    <row r="69" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="236">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B69" s="60">
         <v>754</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="224"/>
-      <c r="F41" s="224"/>
-      <c r="G41" s="224"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="224"/>
-      <c r="J41" s="224"/>
-      <c r="K41" s="224"/>
-      <c r="L41" s="224"/>
-    </row>
-    <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="224"/>
-      <c r="B42" s="224">
-        <v>755</v>
-      </c>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-    </row>
-    <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="224"/>
-      <c r="B43" s="224">
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+    </row>
+    <row r="70" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="236">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B70" s="60">
         <v>758</v>
       </c>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-    </row>
-    <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="224"/>
-      <c r="B44" s="224">
+      <c r="C70" s="60"/>
+      <c r="D70" s="60"/>
+      <c r="E70" s="60"/>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+    </row>
+    <row r="71" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="236">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B71" s="60">
         <v>761</v>
       </c>
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
-      <c r="F44" s="224"/>
-      <c r="G44" s="224"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="224"/>
-      <c r="J44" s="224"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-    </row>
-    <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="224"/>
-      <c r="B45" s="224">
-        <v>762</v>
-      </c>
-      <c r="C45" s="224"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="224"/>
-      <c r="F45" s="224"/>
-      <c r="G45" s="224"/>
-      <c r="H45" s="224"/>
-      <c r="I45" s="224"/>
-      <c r="J45" s="224"/>
-      <c r="K45" s="224"/>
-      <c r="L45" s="224"/>
-    </row>
-    <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="224"/>
-      <c r="B46" s="224">
-        <v>763</v>
-      </c>
-      <c r="C46" s="224"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="224"/>
-      <c r="F46" s="224"/>
-      <c r="G46" s="224"/>
-      <c r="H46" s="224"/>
-      <c r="I46" s="224"/>
-      <c r="J46" s="224"/>
-      <c r="K46" s="224"/>
-      <c r="L46" s="224"/>
-    </row>
-    <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47" s="224"/>
-      <c r="B47" s="224">
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="60"/>
+    </row>
+    <row r="72" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="236">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B72" s="60">
         <v>764</v>
       </c>
-      <c r="C47" s="224"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="224"/>
-      <c r="F47" s="224"/>
-      <c r="G47" s="224"/>
-      <c r="H47" s="224"/>
-      <c r="I47" s="224"/>
-      <c r="J47" s="224"/>
-      <c r="K47" s="224"/>
-      <c r="L47" s="224"/>
-    </row>
-    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="224"/>
-      <c r="B48" s="224">
-        <v>765</v>
-      </c>
-      <c r="C48" s="224"/>
-      <c r="D48" s="224"/>
-      <c r="E48" s="224"/>
-      <c r="F48" s="224"/>
-      <c r="G48" s="224"/>
-      <c r="H48" s="224"/>
-      <c r="I48" s="224"/>
-      <c r="J48" s="224"/>
-      <c r="K48" s="224"/>
-      <c r="L48" s="224"/>
-    </row>
-    <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49" s="224"/>
-      <c r="B49" s="224">
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="60"/>
+      <c r="K72" s="60"/>
+    </row>
+    <row r="73" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="236">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B73" s="60">
         <v>766</v>
       </c>
-      <c r="C49" s="224"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="224"/>
-      <c r="I49" s="224"/>
-      <c r="J49" s="224"/>
-      <c r="K49" s="224"/>
-      <c r="L49" s="224"/>
-    </row>
-    <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="224"/>
-      <c r="B50" s="224">
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="60"/>
+      <c r="K73" s="60"/>
+    </row>
+    <row r="74" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="236">
+        <f t="shared" ref="A74:A80" si="1">A73+1</f>
+        <v>20</v>
+      </c>
+      <c r="B74" s="60">
         <v>767</v>
       </c>
-      <c r="C50" s="224"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="224"/>
-      <c r="F50" s="224"/>
-      <c r="G50" s="224"/>
-      <c r="H50" s="224"/>
-      <c r="I50" s="224"/>
-      <c r="J50" s="224"/>
-      <c r="K50" s="224"/>
-      <c r="L50" s="224"/>
-    </row>
-    <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="224"/>
-      <c r="B51" s="224">
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+    </row>
+    <row r="75" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="236">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B75" s="60">
         <v>768</v>
       </c>
-      <c r="C51" s="224"/>
-      <c r="D51" s="224"/>
-      <c r="E51" s="224"/>
-      <c r="F51" s="224"/>
-      <c r="G51" s="224"/>
-      <c r="H51" s="224"/>
-      <c r="I51" s="224"/>
-      <c r="J51" s="224"/>
-      <c r="K51" s="224"/>
-      <c r="L51" s="224"/>
-    </row>
-    <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="224"/>
-      <c r="B52" s="224">
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="60"/>
+    </row>
+    <row r="76" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="236">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B76" s="60">
         <v>769</v>
       </c>
-      <c r="C52" s="224"/>
-      <c r="D52" s="224"/>
-      <c r="E52" s="224"/>
-      <c r="F52" s="224"/>
-      <c r="G52" s="224"/>
-      <c r="H52" s="224"/>
-      <c r="I52" s="224"/>
-      <c r="J52" s="224"/>
-      <c r="K52" s="224"/>
-      <c r="L52" s="224"/>
-    </row>
-    <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A53" s="224"/>
-      <c r="B53" s="224" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53" s="224"/>
-      <c r="D53" s="224"/>
-      <c r="E53" s="224"/>
-      <c r="F53" s="224"/>
-      <c r="G53" s="224"/>
-      <c r="H53" s="224"/>
-      <c r="I53" s="224"/>
-      <c r="J53" s="224"/>
-      <c r="K53" s="224"/>
-      <c r="L53" s="224"/>
-    </row>
-    <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A54" s="224"/>
-      <c r="B54" s="224" t="s">
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
+      <c r="J76" s="60"/>
+      <c r="K76" s="60"/>
+    </row>
+    <row r="77" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="236">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B77" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="C54" s="224"/>
-      <c r="D54" s="224"/>
-      <c r="E54" s="224"/>
-      <c r="F54" s="224"/>
-      <c r="G54" s="224"/>
-      <c r="H54" s="224"/>
-      <c r="I54" s="224"/>
-      <c r="J54" s="224"/>
-      <c r="K54" s="224"/>
-      <c r="L54" s="224"/>
-    </row>
-    <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="224"/>
-      <c r="B55" s="224" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55" s="224"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="224"/>
-      <c r="F55" s="224"/>
-      <c r="G55" s="224"/>
-      <c r="H55" s="224"/>
-      <c r="I55" s="224"/>
-      <c r="J55" s="224"/>
-      <c r="K55" s="224"/>
-      <c r="L55" s="224"/>
-    </row>
-    <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="224"/>
-      <c r="B56" s="224" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="224"/>
-      <c r="D56" s="224"/>
-      <c r="E56" s="224"/>
-      <c r="F56" s="224"/>
-      <c r="G56" s="224"/>
-      <c r="H56" s="224"/>
-      <c r="I56" s="224"/>
-      <c r="J56" s="224"/>
-      <c r="K56" s="224"/>
-      <c r="L56" s="224"/>
-    </row>
-    <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A57" s="224"/>
-      <c r="B57" s="224" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="224"/>
-      <c r="D57" s="224"/>
-      <c r="E57" s="224"/>
-      <c r="F57" s="224"/>
-      <c r="G57" s="224"/>
-      <c r="H57" s="224"/>
-      <c r="I57" s="224"/>
-      <c r="J57" s="224"/>
-      <c r="K57" s="224"/>
-      <c r="L57" s="224"/>
-    </row>
-    <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A58" s="224"/>
-      <c r="B58" s="224" t="s">
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
+      <c r="J77" s="60"/>
+      <c r="K77" s="60"/>
+    </row>
+    <row r="78" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="236">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B78" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="224"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="224"/>
-      <c r="F58" s="224"/>
-      <c r="G58" s="224"/>
-      <c r="H58" s="224"/>
-      <c r="I58" s="224"/>
-      <c r="J58" s="224"/>
-      <c r="K58" s="224"/>
-      <c r="L58" s="224"/>
-    </row>
-    <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59" s="224"/>
-      <c r="B59" s="224" t="s">
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="60"/>
+      <c r="I78" s="60"/>
+      <c r="J78" s="60"/>
+      <c r="K78" s="60"/>
+    </row>
+    <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="236">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B79" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C59" s="224"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="224"/>
-      <c r="F59" s="224"/>
-      <c r="G59" s="224"/>
-      <c r="H59" s="224"/>
-      <c r="I59" s="224"/>
-      <c r="J59" s="224"/>
-      <c r="K59" s="224"/>
-      <c r="L59" s="224"/>
-    </row>
-    <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A60" s="224"/>
-      <c r="B60" s="224" t="s">
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="60"/>
+      <c r="G79" s="60"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="60"/>
+      <c r="J79" s="60"/>
+      <c r="K79" s="60"/>
+    </row>
+    <row r="80" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="236">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B80" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="224"/>
-      <c r="D60" s="224"/>
-      <c r="E60" s="224"/>
-      <c r="F60" s="224"/>
-      <c r="G60" s="224"/>
-      <c r="H60" s="224"/>
-      <c r="I60" s="224"/>
-      <c r="J60" s="224"/>
-      <c r="K60" s="224"/>
-      <c r="L60" s="224"/>
-    </row>
-    <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="224"/>
-      <c r="B61" s="224" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="224"/>
-      <c r="D61" s="224"/>
-      <c r="E61" s="224"/>
-      <c r="F61" s="224"/>
-      <c r="G61" s="224"/>
-      <c r="H61" s="224"/>
-      <c r="I61" s="224"/>
-      <c r="J61" s="224"/>
-      <c r="K61" s="224"/>
-      <c r="L61" s="224"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="60"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="60"/>
+      <c r="J80" s="60"/>
+      <c r="K80" s="60"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="6">
+    <mergeCell ref="A8:L8"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="133" scale="10" firstPageNumber="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="133" scale="49" firstPageNumber="0" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -7974,36 +8488,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="180" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="203"/>
+      <c r="B2" s="180"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="180"/>
+      <c r="K2" s="180"/>
+      <c r="L2" s="180"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -8024,36 +8538,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
+      <c r="I4" s="181"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="181"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="204" t="s">
+      <c r="C5" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -8070,36 +8584,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="206"/>
-      <c r="C7" s="206"/>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="207"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="184"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="208" t="s">
+      <c r="A8" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="209"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="209"/>
-      <c r="L8" s="210"/>
+      <c r="B8" s="186"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="186"/>
+      <c r="H8" s="186"/>
+      <c r="I8" s="186"/>
+      <c r="J8" s="186"/>
+      <c r="K8" s="186"/>
+      <c r="L8" s="187"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -11539,19 +12053,19 @@
       <c r="A26" s="61">
         <v>0</v>
       </c>
-      <c r="B26" s="194" t="s">
+      <c r="B26" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="195"/>
-      <c r="D26" s="195"/>
-      <c r="E26" s="195"/>
-      <c r="F26" s="195"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="195"/>
-      <c r="I26" s="195"/>
-      <c r="J26" s="195"/>
-      <c r="K26" s="195"/>
-      <c r="L26" s="196"/>
+      <c r="C26" s="190"/>
+      <c r="D26" s="190"/>
+      <c r="E26" s="190"/>
+      <c r="F26" s="190"/>
+      <c r="G26" s="190"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="190"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="190"/>
+      <c r="L26" s="191"/>
     </row>
     <row r="27" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A27" s="62"/>
@@ -11568,20 +12082,20 @@
       <c r="L27" s="63"/>
     </row>
     <row r="28" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="197" t="s">
+      <c r="A28" s="192" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="198"/>
-      <c r="C28" s="198"/>
-      <c r="D28" s="198"/>
-      <c r="E28" s="198"/>
-      <c r="F28" s="198"/>
-      <c r="G28" s="198"/>
-      <c r="H28" s="198"/>
-      <c r="I28" s="198"/>
-      <c r="J28" s="198"/>
-      <c r="K28" s="198"/>
-      <c r="L28" s="198"/>
+      <c r="B28" s="193"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="193"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="193"/>
+      <c r="G28" s="193"/>
+      <c r="H28" s="193"/>
+      <c r="I28" s="193"/>
+      <c r="J28" s="193"/>
+      <c r="K28" s="193"/>
+      <c r="L28" s="193"/>
       <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
@@ -12201,19 +12715,19 @@
       <c r="A38" s="70">
         <v>0</v>
       </c>
-      <c r="B38" s="190" t="s">
+      <c r="B38" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="191"/>
-      <c r="D38" s="191"/>
-      <c r="E38" s="191"/>
-      <c r="F38" s="191"/>
-      <c r="G38" s="191"/>
-      <c r="H38" s="191"/>
-      <c r="I38" s="191"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="192"/>
+      <c r="C38" s="195"/>
+      <c r="D38" s="195"/>
+      <c r="E38" s="195"/>
+      <c r="F38" s="195"/>
+      <c r="G38" s="195"/>
+      <c r="H38" s="195"/>
+      <c r="I38" s="195"/>
+      <c r="J38" s="195"/>
+      <c r="K38" s="195"/>
+      <c r="L38" s="196"/>
     </row>
     <row r="39" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A39" s="71"/>
@@ -12230,20 +12744,20 @@
       <c r="L39" s="63"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="199" t="s">
+      <c r="A40" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="199"/>
-      <c r="C40" s="199"/>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="199"/>
-      <c r="J40" s="199"/>
-      <c r="K40" s="199"/>
-      <c r="L40" s="199"/>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="197"/>
+      <c r="J40" s="197"/>
+      <c r="K40" s="197"/>
+      <c r="L40" s="197"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="72"/>
@@ -12277,19 +12791,19 @@
       <c r="A43" s="80">
         <v>0</v>
       </c>
-      <c r="B43" s="200" t="s">
+      <c r="B43" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="200"/>
-      <c r="D43" s="200"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="200"/>
-      <c r="I43" s="200"/>
-      <c r="J43" s="200"/>
-      <c r="K43" s="200"/>
-      <c r="L43" s="201"/>
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="199"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="81"/>
@@ -12306,20 +12820,20 @@
       <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="193" t="s">
+      <c r="A45" s="200" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="193"/>
-      <c r="C45" s="193"/>
-      <c r="D45" s="193"/>
-      <c r="E45" s="193"/>
-      <c r="F45" s="193"/>
-      <c r="G45" s="193"/>
-      <c r="H45" s="193"/>
-      <c r="I45" s="193"/>
-      <c r="J45" s="193"/>
-      <c r="K45" s="193"/>
-      <c r="L45" s="193"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="200"/>
+      <c r="D45" s="200"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="200"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="200"/>
+      <c r="L45" s="200"/>
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="84"/>
@@ -12353,19 +12867,19 @@
       <c r="A48" s="80">
         <v>0</v>
       </c>
-      <c r="B48" s="190" t="s">
+      <c r="B48" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="191"/>
-      <c r="D48" s="191"/>
-      <c r="E48" s="191"/>
-      <c r="F48" s="191"/>
-      <c r="G48" s="191"/>
-      <c r="H48" s="191"/>
-      <c r="I48" s="191"/>
-      <c r="J48" s="191"/>
-      <c r="K48" s="191"/>
-      <c r="L48" s="192"/>
+      <c r="C48" s="195"/>
+      <c r="D48" s="195"/>
+      <c r="E48" s="195"/>
+      <c r="F48" s="195"/>
+      <c r="G48" s="195"/>
+      <c r="H48" s="195"/>
+      <c r="I48" s="195"/>
+      <c r="J48" s="195"/>
+      <c r="K48" s="195"/>
+      <c r="L48" s="196"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A49" s="71"/>
@@ -12382,20 +12896,20 @@
       <c r="L49" s="40"/>
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="193" t="s">
+      <c r="A50" s="200" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="193"/>
-      <c r="C50" s="193"/>
-      <c r="D50" s="193"/>
-      <c r="E50" s="193"/>
-      <c r="F50" s="193"/>
-      <c r="G50" s="193"/>
-      <c r="H50" s="193"/>
-      <c r="I50" s="193"/>
-      <c r="J50" s="193"/>
-      <c r="K50" s="193"/>
-      <c r="L50" s="193"/>
+      <c r="B50" s="200"/>
+      <c r="C50" s="200"/>
+      <c r="D50" s="200"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="200"/>
+      <c r="H50" s="200"/>
+      <c r="I50" s="200"/>
+      <c r="J50" s="200"/>
+      <c r="K50" s="200"/>
+      <c r="L50" s="200"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="84"/>
@@ -12429,19 +12943,19 @@
       <c r="A53" s="80">
         <v>0</v>
       </c>
-      <c r="B53" s="190" t="s">
+      <c r="B53" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="191"/>
-      <c r="D53" s="191"/>
-      <c r="E53" s="191"/>
-      <c r="F53" s="191"/>
-      <c r="G53" s="191"/>
-      <c r="H53" s="191"/>
-      <c r="I53" s="191"/>
-      <c r="J53" s="191"/>
-      <c r="K53" s="191"/>
-      <c r="L53" s="192"/>
+      <c r="C53" s="195"/>
+      <c r="D53" s="195"/>
+      <c r="E53" s="195"/>
+      <c r="F53" s="195"/>
+      <c r="G53" s="195"/>
+      <c r="H53" s="195"/>
+      <c r="I53" s="195"/>
+      <c r="J53" s="195"/>
+      <c r="K53" s="195"/>
+      <c r="L53" s="196"/>
     </row>
     <row r="54" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A54" s="71"/>
@@ -12458,20 +12972,20 @@
       <c r="L54" s="40"/>
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="193" t="s">
+      <c r="A55" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="193"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
+      <c r="B55" s="200"/>
+      <c r="C55" s="200"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="200"/>
+      <c r="G55" s="200"/>
+      <c r="H55" s="200"/>
+      <c r="I55" s="200"/>
+      <c r="J55" s="200"/>
+      <c r="K55" s="200"/>
+      <c r="L55" s="200"/>
     </row>
     <row r="56" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="90"/>
@@ -12505,19 +13019,19 @@
       <c r="A58" s="80">
         <v>0</v>
       </c>
-      <c r="B58" s="190" t="s">
+      <c r="B58" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="191"/>
-      <c r="D58" s="191"/>
-      <c r="E58" s="191"/>
-      <c r="F58" s="191"/>
-      <c r="G58" s="191"/>
-      <c r="H58" s="191"/>
-      <c r="I58" s="191"/>
-      <c r="J58" s="191"/>
-      <c r="K58" s="191"/>
-      <c r="L58" s="192"/>
+      <c r="C58" s="195"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="195"/>
+      <c r="L58" s="196"/>
     </row>
     <row r="59" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A59" s="71"/>
@@ -12535,10 +13049,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
-      <c r="B60" s="180" t="s">
+      <c r="B60" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="C60" s="180"/>
+      <c r="C60" s="188"/>
       <c r="D60" s="94" t="s">
         <v>30</v>
       </c>
@@ -12553,10 +13067,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
-      <c r="B61" s="180" t="s">
+      <c r="B61" s="188" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="180"/>
+      <c r="C61" s="188"/>
       <c r="D61" s="94"/>
       <c r="E61" s="95"/>
       <c r="F61" s="95"/>
@@ -12568,55 +13082,55 @@
       <c r="L61" s="96"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="181"/>
-      <c r="B62" s="182"/>
-      <c r="C62" s="182"/>
-      <c r="D62" s="182"/>
-      <c r="E62" s="182"/>
-      <c r="F62" s="182"/>
-      <c r="G62" s="182"/>
-      <c r="H62" s="182"/>
-      <c r="I62" s="182"/>
-      <c r="J62" s="182"/>
-      <c r="K62" s="182"/>
-      <c r="L62" s="183"/>
+      <c r="A62" s="210"/>
+      <c r="B62" s="211"/>
+      <c r="C62" s="211"/>
+      <c r="D62" s="211"/>
+      <c r="E62" s="211"/>
+      <c r="F62" s="211"/>
+      <c r="G62" s="211"/>
+      <c r="H62" s="211"/>
+      <c r="I62" s="211"/>
+      <c r="J62" s="211"/>
+      <c r="K62" s="211"/>
+      <c r="L62" s="212"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="184"/>
-      <c r="B63" s="185"/>
-      <c r="C63" s="185"/>
-      <c r="D63" s="185"/>
-      <c r="E63" s="185"/>
-      <c r="F63" s="185"/>
-      <c r="G63" s="185"/>
-      <c r="H63" s="185"/>
-      <c r="I63" s="185"/>
-      <c r="J63" s="185"/>
-      <c r="K63" s="185"/>
-      <c r="L63" s="186"/>
+      <c r="A63" s="213"/>
+      <c r="B63" s="214"/>
+      <c r="C63" s="214"/>
+      <c r="D63" s="214"/>
+      <c r="E63" s="214"/>
+      <c r="F63" s="214"/>
+      <c r="G63" s="214"/>
+      <c r="H63" s="214"/>
+      <c r="I63" s="214"/>
+      <c r="J63" s="214"/>
+      <c r="K63" s="214"/>
+      <c r="L63" s="215"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="187" t="s">
+      <c r="A64" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B64" s="187"/>
-      <c r="C64" s="187"/>
-      <c r="D64" s="187"/>
-      <c r="E64" s="187"/>
-      <c r="F64" s="187"/>
-      <c r="G64" s="187"/>
-      <c r="H64" s="187"/>
-      <c r="I64" s="187"/>
-      <c r="J64" s="187"/>
-      <c r="K64" s="187"/>
-      <c r="L64" s="187"/>
+      <c r="B64" s="216"/>
+      <c r="C64" s="216"/>
+      <c r="D64" s="216"/>
+      <c r="E64" s="216"/>
+      <c r="F64" s="216"/>
+      <c r="G64" s="216"/>
+      <c r="H64" s="216"/>
+      <c r="I64" s="216"/>
+      <c r="J64" s="216"/>
+      <c r="K64" s="216"/>
+      <c r="L64" s="216"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="188" t="s">
+      <c r="A65" s="217" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="188"/>
-      <c r="C65" s="188"/>
+      <c r="B65" s="217"/>
+      <c r="C65" s="217"/>
       <c r="D65" s="97"/>
       <c r="E65" s="97"/>
       <c r="F65" s="97"/>
@@ -13687,11 +14201,11 @@
       <c r="A140" s="61">
         <v>0</v>
       </c>
-      <c r="B140" s="188" t="s">
+      <c r="B140" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="C140" s="188"/>
-      <c r="D140" s="188"/>
+      <c r="C140" s="217"/>
+      <c r="D140" s="217"/>
       <c r="E140" s="95"/>
       <c r="F140" s="95"/>
       <c r="G140" s="95"/>
@@ -13777,19 +14291,19 @@
       <c r="A146" s="143">
         <v>0</v>
       </c>
-      <c r="B146" s="189" t="s">
+      <c r="B146" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="C146" s="189"/>
-      <c r="D146" s="189"/>
-      <c r="E146" s="189"/>
-      <c r="F146" s="189"/>
-      <c r="G146" s="189"/>
-      <c r="H146" s="189"/>
-      <c r="I146" s="189"/>
-      <c r="J146" s="189"/>
-      <c r="K146" s="189"/>
-      <c r="L146" s="189"/>
+      <c r="C146" s="218"/>
+      <c r="D146" s="218"/>
+      <c r="E146" s="218"/>
+      <c r="F146" s="218"/>
+      <c r="G146" s="218"/>
+      <c r="H146" s="218"/>
+      <c r="I146" s="218"/>
+      <c r="J146" s="218"/>
+      <c r="K146" s="218"/>
+      <c r="L146" s="218"/>
     </row>
     <row r="147" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A147" s="39"/>
@@ -13806,19 +14320,19 @@
       <c r="L147" s="40"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="171" t="s">
+      <c r="B148" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="C148" s="171"/>
-      <c r="D148" s="171"/>
-      <c r="E148" s="171"/>
-      <c r="F148" s="171"/>
-      <c r="G148" s="171"/>
-      <c r="H148" s="171"/>
-      <c r="I148" s="171"/>
-      <c r="J148" s="171"/>
-      <c r="K148" s="171"/>
-      <c r="L148" s="171"/>
+      <c r="C148" s="201"/>
+      <c r="D148" s="201"/>
+      <c r="E148" s="201"/>
+      <c r="F148" s="201"/>
+      <c r="G148" s="201"/>
+      <c r="H148" s="201"/>
+      <c r="I148" s="201"/>
+      <c r="J148" s="201"/>
+      <c r="K148" s="201"/>
+      <c r="L148" s="201"/>
     </row>
     <row r="149" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A149" s="89"/>
@@ -13950,19 +14464,19 @@
       <c r="A158" s="150">
         <v>0</v>
       </c>
-      <c r="B158" s="172" t="s">
+      <c r="B158" s="202" t="s">
         <v>37</v>
       </c>
-      <c r="C158" s="172"/>
-      <c r="D158" s="172"/>
-      <c r="E158" s="172"/>
-      <c r="F158" s="172"/>
-      <c r="G158" s="172"/>
-      <c r="H158" s="172"/>
-      <c r="I158" s="172"/>
-      <c r="J158" s="172"/>
-      <c r="K158" s="172"/>
-      <c r="L158" s="173"/>
+      <c r="C158" s="202"/>
+      <c r="D158" s="202"/>
+      <c r="E158" s="202"/>
+      <c r="F158" s="202"/>
+      <c r="G158" s="202"/>
+      <c r="H158" s="202"/>
+      <c r="I158" s="202"/>
+      <c r="J158" s="202"/>
+      <c r="K158" s="202"/>
+      <c r="L158" s="203"/>
     </row>
     <row r="159" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C159" s="145"/>
@@ -14098,19 +14612,19 @@
       <c r="A168" s="61">
         <v>4</v>
       </c>
-      <c r="B168" s="174" t="s">
+      <c r="B168" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="C168" s="175"/>
-      <c r="D168" s="175"/>
-      <c r="E168" s="175"/>
-      <c r="F168" s="175"/>
-      <c r="G168" s="175"/>
-      <c r="H168" s="175"/>
-      <c r="I168" s="175"/>
-      <c r="J168" s="175"/>
-      <c r="K168" s="175"/>
-      <c r="L168" s="176"/>
+      <c r="C168" s="205"/>
+      <c r="D168" s="205"/>
+      <c r="E168" s="205"/>
+      <c r="F168" s="205"/>
+      <c r="G168" s="205"/>
+      <c r="H168" s="205"/>
+      <c r="I168" s="205"/>
+      <c r="J168" s="205"/>
+      <c r="K168" s="205"/>
+      <c r="L168" s="206"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="125" t="s">
@@ -14204,19 +14718,19 @@
       <c r="A175" s="143">
         <v>2</v>
       </c>
-      <c r="B175" s="177" t="s">
+      <c r="B175" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="C175" s="178"/>
-      <c r="D175" s="178"/>
-      <c r="E175" s="178"/>
-      <c r="F175" s="178"/>
-      <c r="G175" s="178"/>
-      <c r="H175" s="178"/>
-      <c r="I175" s="178"/>
-      <c r="J175" s="178"/>
-      <c r="K175" s="178"/>
-      <c r="L175" s="179"/>
+      <c r="C175" s="208"/>
+      <c r="D175" s="208"/>
+      <c r="E175" s="208"/>
+      <c r="F175" s="208"/>
+      <c r="G175" s="208"/>
+      <c r="H175" s="208"/>
+      <c r="I175" s="208"/>
+      <c r="J175" s="208"/>
+      <c r="K175" s="208"/>
+      <c r="L175" s="209"/>
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A176" s="167">
@@ -14239,12 +14753,16 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="28">
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B158:L158"/>
+    <mergeCell ref="B168:L168"/>
+    <mergeCell ref="B175:L175"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A62:L63"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B140:D140"/>
+    <mergeCell ref="B146:L146"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="A28:L28"/>
@@ -14257,16 +14775,12 @@
     <mergeCell ref="B53:L53"/>
     <mergeCell ref="A55:L55"/>
     <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B148:L148"/>
-    <mergeCell ref="B158:L158"/>
-    <mergeCell ref="B168:L168"/>
-    <mergeCell ref="B175:L175"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="A62:L63"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="B146:L146"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15118,36 +15632,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="180" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="203"/>
+      <c r="B2" s="180"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="180"/>
+      <c r="K2" s="180"/>
+      <c r="L2" s="180"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -15168,36 +15682,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
+      <c r="I4" s="181"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="181"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="204" t="s">
+      <c r="C5" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -15214,36 +15728,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="206"/>
-      <c r="C7" s="206"/>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="207"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="184"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="208" t="s">
+      <c r="A8" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="209"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="209"/>
-      <c r="L8" s="210"/>
+      <c r="B8" s="186"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="186"/>
+      <c r="H8" s="186"/>
+      <c r="I8" s="186"/>
+      <c r="J8" s="186"/>
+      <c r="K8" s="186"/>
+      <c r="L8" s="187"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -18683,19 +19197,19 @@
       <c r="A26" s="61">
         <v>0</v>
       </c>
-      <c r="B26" s="194" t="s">
+      <c r="B26" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="195"/>
-      <c r="D26" s="195"/>
-      <c r="E26" s="195"/>
-      <c r="F26" s="195"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="195"/>
-      <c r="I26" s="195"/>
-      <c r="J26" s="195"/>
-      <c r="K26" s="195"/>
-      <c r="L26" s="196"/>
+      <c r="C26" s="190"/>
+      <c r="D26" s="190"/>
+      <c r="E26" s="190"/>
+      <c r="F26" s="190"/>
+      <c r="G26" s="190"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="190"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="190"/>
+      <c r="L26" s="191"/>
     </row>
     <row r="27" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A27" s="62"/>
@@ -18712,20 +19226,20 @@
       <c r="L27" s="63"/>
     </row>
     <row r="28" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="197" t="s">
+      <c r="A28" s="192" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="198"/>
-      <c r="C28" s="198"/>
-      <c r="D28" s="198"/>
-      <c r="E28" s="198"/>
-      <c r="F28" s="198"/>
-      <c r="G28" s="198"/>
-      <c r="H28" s="198"/>
-      <c r="I28" s="198"/>
-      <c r="J28" s="198"/>
-      <c r="K28" s="198"/>
-      <c r="L28" s="198"/>
+      <c r="B28" s="193"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="193"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="193"/>
+      <c r="G28" s="193"/>
+      <c r="H28" s="193"/>
+      <c r="I28" s="193"/>
+      <c r="J28" s="193"/>
+      <c r="K28" s="193"/>
+      <c r="L28" s="193"/>
       <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
@@ -19345,19 +19859,19 @@
       <c r="A38" s="70">
         <v>0</v>
       </c>
-      <c r="B38" s="190" t="s">
+      <c r="B38" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="191"/>
-      <c r="D38" s="191"/>
-      <c r="E38" s="191"/>
-      <c r="F38" s="191"/>
-      <c r="G38" s="191"/>
-      <c r="H38" s="191"/>
-      <c r="I38" s="191"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="192"/>
+      <c r="C38" s="195"/>
+      <c r="D38" s="195"/>
+      <c r="E38" s="195"/>
+      <c r="F38" s="195"/>
+      <c r="G38" s="195"/>
+      <c r="H38" s="195"/>
+      <c r="I38" s="195"/>
+      <c r="J38" s="195"/>
+      <c r="K38" s="195"/>
+      <c r="L38" s="196"/>
     </row>
     <row r="39" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A39" s="71"/>
@@ -19374,20 +19888,20 @@
       <c r="L39" s="63"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="199" t="s">
+      <c r="A40" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="199"/>
-      <c r="C40" s="199"/>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="199"/>
-      <c r="J40" s="199"/>
-      <c r="K40" s="199"/>
-      <c r="L40" s="199"/>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="197"/>
+      <c r="J40" s="197"/>
+      <c r="K40" s="197"/>
+      <c r="L40" s="197"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="72"/>
@@ -19421,19 +19935,19 @@
       <c r="A43" s="80">
         <v>0</v>
       </c>
-      <c r="B43" s="200" t="s">
+      <c r="B43" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="200"/>
-      <c r="D43" s="200"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="200"/>
-      <c r="I43" s="200"/>
-      <c r="J43" s="200"/>
-      <c r="K43" s="200"/>
-      <c r="L43" s="201"/>
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="199"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="81"/>
@@ -19450,20 +19964,20 @@
       <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="193" t="s">
+      <c r="A45" s="200" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="193"/>
-      <c r="C45" s="193"/>
-      <c r="D45" s="193"/>
-      <c r="E45" s="193"/>
-      <c r="F45" s="193"/>
-      <c r="G45" s="193"/>
-      <c r="H45" s="193"/>
-      <c r="I45" s="193"/>
-      <c r="J45" s="193"/>
-      <c r="K45" s="193"/>
-      <c r="L45" s="193"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="200"/>
+      <c r="D45" s="200"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="200"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="200"/>
+      <c r="L45" s="200"/>
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="84"/>
@@ -19497,19 +20011,19 @@
       <c r="A48" s="80">
         <v>0</v>
       </c>
-      <c r="B48" s="190" t="s">
+      <c r="B48" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="191"/>
-      <c r="D48" s="191"/>
-      <c r="E48" s="191"/>
-      <c r="F48" s="191"/>
-      <c r="G48" s="191"/>
-      <c r="H48" s="191"/>
-      <c r="I48" s="191"/>
-      <c r="J48" s="191"/>
-      <c r="K48" s="191"/>
-      <c r="L48" s="192"/>
+      <c r="C48" s="195"/>
+      <c r="D48" s="195"/>
+      <c r="E48" s="195"/>
+      <c r="F48" s="195"/>
+      <c r="G48" s="195"/>
+      <c r="H48" s="195"/>
+      <c r="I48" s="195"/>
+      <c r="J48" s="195"/>
+      <c r="K48" s="195"/>
+      <c r="L48" s="196"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A49" s="71"/>
@@ -19526,20 +20040,20 @@
       <c r="L49" s="40"/>
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="193" t="s">
+      <c r="A50" s="200" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="193"/>
-      <c r="C50" s="193"/>
-      <c r="D50" s="193"/>
-      <c r="E50" s="193"/>
-      <c r="F50" s="193"/>
-      <c r="G50" s="193"/>
-      <c r="H50" s="193"/>
-      <c r="I50" s="193"/>
-      <c r="J50" s="193"/>
-      <c r="K50" s="193"/>
-      <c r="L50" s="193"/>
+      <c r="B50" s="200"/>
+      <c r="C50" s="200"/>
+      <c r="D50" s="200"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="200"/>
+      <c r="H50" s="200"/>
+      <c r="I50" s="200"/>
+      <c r="J50" s="200"/>
+      <c r="K50" s="200"/>
+      <c r="L50" s="200"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="84"/>
@@ -19573,19 +20087,19 @@
       <c r="A53" s="80">
         <v>0</v>
       </c>
-      <c r="B53" s="190" t="s">
+      <c r="B53" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="191"/>
-      <c r="D53" s="191"/>
-      <c r="E53" s="191"/>
-      <c r="F53" s="191"/>
-      <c r="G53" s="191"/>
-      <c r="H53" s="191"/>
-      <c r="I53" s="191"/>
-      <c r="J53" s="191"/>
-      <c r="K53" s="191"/>
-      <c r="L53" s="192"/>
+      <c r="C53" s="195"/>
+      <c r="D53" s="195"/>
+      <c r="E53" s="195"/>
+      <c r="F53" s="195"/>
+      <c r="G53" s="195"/>
+      <c r="H53" s="195"/>
+      <c r="I53" s="195"/>
+      <c r="J53" s="195"/>
+      <c r="K53" s="195"/>
+      <c r="L53" s="196"/>
     </row>
     <row r="54" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A54" s="71"/>
@@ -19602,20 +20116,20 @@
       <c r="L54" s="40"/>
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="193" t="s">
+      <c r="A55" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="193"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
+      <c r="B55" s="200"/>
+      <c r="C55" s="200"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="200"/>
+      <c r="G55" s="200"/>
+      <c r="H55" s="200"/>
+      <c r="I55" s="200"/>
+      <c r="J55" s="200"/>
+      <c r="K55" s="200"/>
+      <c r="L55" s="200"/>
     </row>
     <row r="56" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="90"/>
@@ -19649,19 +20163,19 @@
       <c r="A58" s="80">
         <v>0</v>
       </c>
-      <c r="B58" s="190" t="s">
+      <c r="B58" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="191"/>
-      <c r="D58" s="191"/>
-      <c r="E58" s="191"/>
-      <c r="F58" s="191"/>
-      <c r="G58" s="191"/>
-      <c r="H58" s="191"/>
-      <c r="I58" s="191"/>
-      <c r="J58" s="191"/>
-      <c r="K58" s="191"/>
-      <c r="L58" s="192"/>
+      <c r="C58" s="195"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="195"/>
+      <c r="L58" s="196"/>
     </row>
     <row r="59" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A59" s="71"/>
@@ -19679,10 +20193,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
-      <c r="B60" s="180" t="s">
+      <c r="B60" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="C60" s="180"/>
+      <c r="C60" s="188"/>
       <c r="D60" s="94" t="s">
         <v>30</v>
       </c>
@@ -19697,10 +20211,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
-      <c r="B61" s="180" t="s">
+      <c r="B61" s="188" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="180"/>
+      <c r="C61" s="188"/>
       <c r="D61" s="94"/>
       <c r="E61" s="95"/>
       <c r="F61" s="95"/>
@@ -19712,55 +20226,55 @@
       <c r="L61" s="96"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="181"/>
-      <c r="B62" s="182"/>
-      <c r="C62" s="182"/>
-      <c r="D62" s="182"/>
-      <c r="E62" s="182"/>
-      <c r="F62" s="182"/>
-      <c r="G62" s="182"/>
-      <c r="H62" s="182"/>
-      <c r="I62" s="182"/>
-      <c r="J62" s="182"/>
-      <c r="K62" s="182"/>
-      <c r="L62" s="183"/>
+      <c r="A62" s="210"/>
+      <c r="B62" s="211"/>
+      <c r="C62" s="211"/>
+      <c r="D62" s="211"/>
+      <c r="E62" s="211"/>
+      <c r="F62" s="211"/>
+      <c r="G62" s="211"/>
+      <c r="H62" s="211"/>
+      <c r="I62" s="211"/>
+      <c r="J62" s="211"/>
+      <c r="K62" s="211"/>
+      <c r="L62" s="212"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="184"/>
-      <c r="B63" s="185"/>
-      <c r="C63" s="185"/>
-      <c r="D63" s="185"/>
-      <c r="E63" s="185"/>
-      <c r="F63" s="185"/>
-      <c r="G63" s="185"/>
-      <c r="H63" s="185"/>
-      <c r="I63" s="185"/>
-      <c r="J63" s="185"/>
-      <c r="K63" s="185"/>
-      <c r="L63" s="186"/>
+      <c r="A63" s="213"/>
+      <c r="B63" s="214"/>
+      <c r="C63" s="214"/>
+      <c r="D63" s="214"/>
+      <c r="E63" s="214"/>
+      <c r="F63" s="214"/>
+      <c r="G63" s="214"/>
+      <c r="H63" s="214"/>
+      <c r="I63" s="214"/>
+      <c r="J63" s="214"/>
+      <c r="K63" s="214"/>
+      <c r="L63" s="215"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="187" t="s">
+      <c r="A64" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B64" s="187"/>
-      <c r="C64" s="187"/>
-      <c r="D64" s="187"/>
-      <c r="E64" s="187"/>
-      <c r="F64" s="187"/>
-      <c r="G64" s="187"/>
-      <c r="H64" s="187"/>
-      <c r="I64" s="187"/>
-      <c r="J64" s="187"/>
-      <c r="K64" s="187"/>
-      <c r="L64" s="187"/>
+      <c r="B64" s="216"/>
+      <c r="C64" s="216"/>
+      <c r="D64" s="216"/>
+      <c r="E64" s="216"/>
+      <c r="F64" s="216"/>
+      <c r="G64" s="216"/>
+      <c r="H64" s="216"/>
+      <c r="I64" s="216"/>
+      <c r="J64" s="216"/>
+      <c r="K64" s="216"/>
+      <c r="L64" s="216"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="188" t="s">
+      <c r="A65" s="217" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="188"/>
-      <c r="C65" s="188"/>
+      <c r="B65" s="217"/>
+      <c r="C65" s="217"/>
       <c r="D65" s="97"/>
       <c r="E65" s="97"/>
       <c r="F65" s="97"/>
@@ -20831,11 +21345,11 @@
       <c r="A140" s="61">
         <v>0</v>
       </c>
-      <c r="B140" s="188" t="s">
+      <c r="B140" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="C140" s="188"/>
-      <c r="D140" s="188"/>
+      <c r="C140" s="217"/>
+      <c r="D140" s="217"/>
       <c r="E140" s="95"/>
       <c r="F140" s="95"/>
       <c r="G140" s="95"/>
@@ -20921,19 +21435,19 @@
       <c r="A146" s="143">
         <v>0</v>
       </c>
-      <c r="B146" s="189" t="s">
+      <c r="B146" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="C146" s="189"/>
-      <c r="D146" s="189"/>
-      <c r="E146" s="189"/>
-      <c r="F146" s="189"/>
-      <c r="G146" s="189"/>
-      <c r="H146" s="189"/>
-      <c r="I146" s="189"/>
-      <c r="J146" s="189"/>
-      <c r="K146" s="189"/>
-      <c r="L146" s="189"/>
+      <c r="C146" s="218"/>
+      <c r="D146" s="218"/>
+      <c r="E146" s="218"/>
+      <c r="F146" s="218"/>
+      <c r="G146" s="218"/>
+      <c r="H146" s="218"/>
+      <c r="I146" s="218"/>
+      <c r="J146" s="218"/>
+      <c r="K146" s="218"/>
+      <c r="L146" s="218"/>
     </row>
     <row r="147" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A147" s="39"/>
@@ -20950,19 +21464,19 @@
       <c r="L147" s="40"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="171" t="s">
+      <c r="B148" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="C148" s="171"/>
-      <c r="D148" s="171"/>
-      <c r="E148" s="171"/>
-      <c r="F148" s="171"/>
-      <c r="G148" s="171"/>
-      <c r="H148" s="171"/>
-      <c r="I148" s="171"/>
-      <c r="J148" s="171"/>
-      <c r="K148" s="171"/>
-      <c r="L148" s="171"/>
+      <c r="C148" s="201"/>
+      <c r="D148" s="201"/>
+      <c r="E148" s="201"/>
+      <c r="F148" s="201"/>
+      <c r="G148" s="201"/>
+      <c r="H148" s="201"/>
+      <c r="I148" s="201"/>
+      <c r="J148" s="201"/>
+      <c r="K148" s="201"/>
+      <c r="L148" s="201"/>
     </row>
     <row r="149" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A149" s="89"/>
@@ -21094,19 +21608,19 @@
       <c r="A158" s="150">
         <v>0</v>
       </c>
-      <c r="B158" s="172" t="s">
+      <c r="B158" s="202" t="s">
         <v>37</v>
       </c>
-      <c r="C158" s="172"/>
-      <c r="D158" s="172"/>
-      <c r="E158" s="172"/>
-      <c r="F158" s="172"/>
-      <c r="G158" s="172"/>
-      <c r="H158" s="172"/>
-      <c r="I158" s="172"/>
-      <c r="J158" s="172"/>
-      <c r="K158" s="172"/>
-      <c r="L158" s="173"/>
+      <c r="C158" s="202"/>
+      <c r="D158" s="202"/>
+      <c r="E158" s="202"/>
+      <c r="F158" s="202"/>
+      <c r="G158" s="202"/>
+      <c r="H158" s="202"/>
+      <c r="I158" s="202"/>
+      <c r="J158" s="202"/>
+      <c r="K158" s="202"/>
+      <c r="L158" s="203"/>
     </row>
     <row r="159" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C159" s="145"/>
@@ -21242,19 +21756,19 @@
       <c r="A168" s="61">
         <v>4</v>
       </c>
-      <c r="B168" s="174" t="s">
+      <c r="B168" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="C168" s="175"/>
-      <c r="D168" s="175"/>
-      <c r="E168" s="175"/>
-      <c r="F168" s="175"/>
-      <c r="G168" s="175"/>
-      <c r="H168" s="175"/>
-      <c r="I168" s="175"/>
-      <c r="J168" s="175"/>
-      <c r="K168" s="175"/>
-      <c r="L168" s="176"/>
+      <c r="C168" s="205"/>
+      <c r="D168" s="205"/>
+      <c r="E168" s="205"/>
+      <c r="F168" s="205"/>
+      <c r="G168" s="205"/>
+      <c r="H168" s="205"/>
+      <c r="I168" s="205"/>
+      <c r="J168" s="205"/>
+      <c r="K168" s="205"/>
+      <c r="L168" s="206"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="125" t="s">
@@ -21348,19 +21862,19 @@
       <c r="A175" s="143">
         <v>2</v>
       </c>
-      <c r="B175" s="177" t="s">
+      <c r="B175" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="C175" s="178"/>
-      <c r="D175" s="178"/>
-      <c r="E175" s="178"/>
-      <c r="F175" s="178"/>
-      <c r="G175" s="178"/>
-      <c r="H175" s="178"/>
-      <c r="I175" s="178"/>
-      <c r="J175" s="178"/>
-      <c r="K175" s="178"/>
-      <c r="L175" s="179"/>
+      <c r="C175" s="208"/>
+      <c r="D175" s="208"/>
+      <c r="E175" s="208"/>
+      <c r="F175" s="208"/>
+      <c r="G175" s="208"/>
+      <c r="H175" s="208"/>
+      <c r="I175" s="208"/>
+      <c r="J175" s="208"/>
+      <c r="K175" s="208"/>
+      <c r="L175" s="209"/>
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A176" s="167">
@@ -21383,12 +21897,15 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="28">
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A62:L63"/>
+    <mergeCell ref="B168:L168"/>
+    <mergeCell ref="B175:L175"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B140:D140"/>
+    <mergeCell ref="B146:L146"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B158:L158"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="A28:L28"/>
@@ -21402,15 +21919,12 @@
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="B53:L53"/>
     <mergeCell ref="B58:L58"/>
-    <mergeCell ref="A62:L63"/>
-    <mergeCell ref="B168:L168"/>
-    <mergeCell ref="B175:L175"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="B146:L146"/>
-    <mergeCell ref="B148:L148"/>
-    <mergeCell ref="B158:L158"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21440,75 +21954,75 @@
       <c r="A2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="211" t="s">
+      <c r="B2" s="227" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="211"/>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
+      <c r="C2" s="227"/>
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="M2" s="227"/>
     </row>
     <row r="3" spans="1:13" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="227" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="211"/>
-      <c r="I3" s="211"/>
-      <c r="J3" s="211"/>
-      <c r="K3" s="211"/>
-      <c r="L3" s="211"/>
-      <c r="M3" s="211"/>
+      <c r="C3" s="227"/>
+      <c r="D3" s="227"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="227"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="M3" s="227"/>
     </row>
     <row r="4" spans="1:13" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="227" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="211"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="227"/>
     </row>
     <row r="5" spans="1:13" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34"/>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="228" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="M5" s="212"/>
+      <c r="C5" s="228"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="228"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="228"/>
+      <c r="K5" s="228"/>
+      <c r="L5" s="228"/>
+      <c r="M5" s="228"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="33"/>
@@ -21574,54 +22088,54 @@
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
-      <c r="B10" s="213" t="s">
+      <c r="B10" s="219" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="213"/>
-      <c r="D10" s="213"/>
-      <c r="E10" s="213"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="213"/>
-      <c r="I10" s="213"/>
-      <c r="J10" s="213"/>
-      <c r="K10" s="213"/>
-      <c r="L10" s="213"/>
-      <c r="M10" s="213"/>
+      <c r="C10" s="219"/>
+      <c r="D10" s="219"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="219"/>
+      <c r="H10" s="219"/>
+      <c r="I10" s="219"/>
+      <c r="J10" s="219"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="213" t="s">
+      <c r="A11" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="213"/>
-      <c r="C11" s="213"/>
-      <c r="D11" s="213"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="213"/>
-      <c r="H11" s="213"/>
-      <c r="I11" s="213"/>
-      <c r="J11" s="213"/>
-      <c r="K11" s="213"/>
-      <c r="L11" s="213"/>
-      <c r="M11" s="213"/>
+      <c r="B11" s="219"/>
+      <c r="C11" s="219"/>
+      <c r="D11" s="219"/>
+      <c r="E11" s="219"/>
+      <c r="F11" s="219"/>
+      <c r="G11" s="219"/>
+      <c r="H11" s="219"/>
+      <c r="I11" s="219"/>
+      <c r="J11" s="219"/>
+      <c r="K11" s="219"/>
+      <c r="L11" s="219"/>
+      <c r="M11" s="219"/>
     </row>
     <row r="12" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="213" t="s">
+      <c r="A12" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="213"/>
-      <c r="C12" s="213"/>
-      <c r="D12" s="213"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="213"/>
-      <c r="H12" s="213"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="213"/>
-      <c r="K12" s="213"/>
-      <c r="L12" s="213"/>
-      <c r="M12" s="213"/>
+      <c r="B12" s="219"/>
+      <c r="C12" s="219"/>
+      <c r="D12" s="219"/>
+      <c r="E12" s="219"/>
+      <c r="F12" s="219"/>
+      <c r="G12" s="219"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="219"/>
+      <c r="J12" s="219"/>
+      <c r="K12" s="219"/>
+      <c r="L12" s="219"/>
+      <c r="M12" s="219"/>
     </row>
     <row r="13" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
@@ -21701,38 +22215,38 @@
     <row r="18" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="217" t="s">
+      <c r="C18" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="217"/>
+      <c r="D18" s="223"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="217" t="s">
+      <c r="I18" s="223" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="217"/>
-      <c r="K18" s="217"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
       <c r="L18" s="12"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="218" t="s">
+      <c r="C19" s="224" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="218"/>
+      <c r="D19" s="224"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="219" t="s">
+      <c r="I19" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="219"/>
-      <c r="K19" s="219"/>
+      <c r="J19" s="225"/>
+      <c r="K19" s="225"/>
       <c r="L19" s="4"/>
       <c r="M19" s="3"/>
     </row>
@@ -21740,13 +22254,13 @@
       <c r="B20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="220"/>
-      <c r="D20" s="220"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
       <c r="I20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J20" s="220"/>
-      <c r="K20" s="220"/>
+      <c r="J20" s="226"/>
+      <c r="K20" s="226"/>
     </row>
     <row r="24" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
@@ -21860,12 +22374,12 @@
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="214" t="s">
+      <c r="E31" s="220" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="214"/>
-      <c r="G31" s="214"/>
-      <c r="H31" s="214"/>
+      <c r="F31" s="220"/>
+      <c r="G31" s="220"/>
+      <c r="H31" s="220"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="6"/>
@@ -21877,12 +22391,12 @@
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="215" t="s">
+      <c r="E32" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="215"/>
-      <c r="G32" s="215"/>
-      <c r="H32" s="215"/>
+      <c r="F32" s="221"/>
+      <c r="G32" s="221"/>
+      <c r="H32" s="221"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="6"/>
@@ -21894,12 +22408,12 @@
       <c r="B33" s="9"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="216" t="s">
+      <c r="E33" s="222" t="s">
         <v>45</v>
       </c>
-      <c r="F33" s="216"/>
-      <c r="G33" s="216"/>
-      <c r="H33" s="216"/>
+      <c r="F33" s="222"/>
+      <c r="G33" s="222"/>
+      <c r="H33" s="222"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="6"/>
@@ -21909,6 +22423,11 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="16">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
@@ -21920,11 +22439,6 @@
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B10:M10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="1" bottom="0.25" header="0.51180555555555551" footer="0.51180555555555551"/>

--- a/app/static/base_docs/DI July to December 2025.xlsx
+++ b/app/static/base_docs/DI July to December 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\base_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8845DFC9-C1CC-4D26-9993-A3AA8DC4D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F47E12-056A-4369-B327-9565F7B38B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9AC113C8-2A50-914F-A515-7C5B30E77858}"/>
   </bookViews>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="83">
   <si>
     <t>DOCKET INVENTORY</t>
   </si>
@@ -572,7 +572,7 @@
     <numFmt numFmtId="166" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -719,6 +719,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1930,6 +1936,63 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1959,77 +2022,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2078,11 +2073,87 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2116,76 +2187,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3398,36 +3407,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-      <c r="L2" s="191"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -3448,36 +3457,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="192"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -3494,36 +3503,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="195"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="211"/>
+      <c r="K7" s="211"/>
+      <c r="L7" s="212"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="187" t="s">
+      <c r="A8" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="189"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="206"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -3567,7 +3576,7 @@
       <c r="A10" s="186">
         <v>1</v>
       </c>
-      <c r="B10" s="249">
+      <c r="B10" s="198">
         <v>4754</v>
       </c>
       <c r="C10" s="49"/>
@@ -3585,7 +3594,7 @@
       <c r="A11" s="186">
         <v>2</v>
       </c>
-      <c r="B11" s="237">
+      <c r="B11" s="187">
         <v>4756</v>
       </c>
       <c r="C11" s="53"/>
@@ -3603,7 +3612,7 @@
       <c r="A12" s="186">
         <v>3</v>
       </c>
-      <c r="B12" s="237">
+      <c r="B12" s="187">
         <v>4752</v>
       </c>
       <c r="C12" s="53"/>
@@ -3621,7 +3630,7 @@
       <c r="A13" s="186">
         <v>4</v>
       </c>
-      <c r="B13" s="237">
+      <c r="B13" s="187">
         <v>4749</v>
       </c>
       <c r="C13" s="53"/>
@@ -3639,7 +3648,7 @@
       <c r="A14" s="186">
         <v>5</v>
       </c>
-      <c r="B14" s="237">
+      <c r="B14" s="187">
         <v>4737</v>
       </c>
       <c r="C14" s="53"/>
@@ -3901,7 +3910,7 @@
       <c r="A15" s="186">
         <v>6</v>
       </c>
-      <c r="B15" s="237">
+      <c r="B15" s="187">
         <v>4746</v>
       </c>
       <c r="C15" s="53"/>
@@ -4163,7 +4172,7 @@
       <c r="A16" s="186">
         <v>7</v>
       </c>
-      <c r="B16" s="237">
+      <c r="B16" s="187">
         <v>4674</v>
       </c>
       <c r="C16" s="53"/>
@@ -4425,7 +4434,7 @@
       <c r="A17" s="186">
         <v>8</v>
       </c>
-      <c r="B17" s="237">
+      <c r="B17" s="187">
         <v>4693</v>
       </c>
       <c r="C17" s="53"/>
@@ -4687,7 +4696,7 @@
       <c r="A18" s="186">
         <v>9</v>
       </c>
-      <c r="B18" s="237">
+      <c r="B18" s="187">
         <v>4715</v>
       </c>
       <c r="C18" s="53"/>
@@ -4949,7 +4958,7 @@
       <c r="A19" s="186">
         <v>10</v>
       </c>
-      <c r="B19" s="237">
+      <c r="B19" s="187">
         <v>4716</v>
       </c>
       <c r="C19" s="53"/>
@@ -5211,7 +5220,7 @@
       <c r="A20" s="186">
         <v>11</v>
       </c>
-      <c r="B20" s="237">
+      <c r="B20" s="187">
         <v>4717</v>
       </c>
       <c r="C20" s="53"/>
@@ -5473,7 +5482,7 @@
       <c r="A21" s="186">
         <v>12</v>
       </c>
-      <c r="B21" s="237">
+      <c r="B21" s="187">
         <v>4718</v>
       </c>
       <c r="C21" s="53"/>
@@ -5735,7 +5744,7 @@
       <c r="A22" s="186">
         <v>13</v>
       </c>
-      <c r="B22" s="237">
+      <c r="B22" s="187">
         <v>4719</v>
       </c>
       <c r="C22" s="53"/>
@@ -5997,7 +6006,7 @@
       <c r="A23" s="186">
         <v>14</v>
       </c>
-      <c r="B23" s="237">
+      <c r="B23" s="187">
         <v>4720</v>
       </c>
       <c r="C23" s="53"/>
@@ -6259,7 +6268,7 @@
       <c r="A24" s="186">
         <v>15</v>
       </c>
-      <c r="B24" s="237">
+      <c r="B24" s="187">
         <v>4721</v>
       </c>
       <c r="C24" s="53"/>
@@ -6521,7 +6530,7 @@
       <c r="A25" s="186">
         <v>16</v>
       </c>
-      <c r="B25" s="237">
+      <c r="B25" s="187">
         <v>4722</v>
       </c>
       <c r="C25" s="53"/>
@@ -6783,7 +6792,7 @@
       <c r="A26" s="186">
         <v>17</v>
       </c>
-      <c r="B26" s="237">
+      <c r="B26" s="187">
         <v>4723</v>
       </c>
       <c r="C26" s="53"/>
@@ -7045,7 +7054,7 @@
       <c r="A27" s="186">
         <v>18</v>
       </c>
-      <c r="B27" s="237">
+      <c r="B27" s="187">
         <v>4724</v>
       </c>
       <c r="C27" s="53"/>
@@ -7307,7 +7316,7 @@
       <c r="A28" s="186">
         <v>19</v>
       </c>
-      <c r="B28" s="237">
+      <c r="B28" s="187">
         <v>4725</v>
       </c>
       <c r="C28" s="53"/>
@@ -7569,7 +7578,7 @@
       <c r="A29" s="186">
         <v>20</v>
       </c>
-      <c r="B29" s="237">
+      <c r="B29" s="187">
         <v>4726</v>
       </c>
       <c r="C29" s="53"/>
@@ -7828,23 +7837,23 @@
       <c r="IV29" s="39"/>
     </row>
     <row r="30" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="250">
+      <c r="A30" s="199">
         <f>COUNT(B10:B29)</f>
         <v>20</v>
       </c>
-      <c r="B30" s="215" t="s">
+      <c r="B30" s="214" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="216"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="216"/>
-      <c r="F30" s="216"/>
-      <c r="G30" s="216"/>
-      <c r="H30" s="216"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="216"/>
-      <c r="K30" s="216"/>
-      <c r="L30" s="217"/>
+      <c r="C30" s="215"/>
+      <c r="D30" s="215"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="215"/>
+      <c r="G30" s="215"/>
+      <c r="H30" s="215"/>
+      <c r="I30" s="215"/>
+      <c r="J30" s="215"/>
+      <c r="K30" s="215"/>
+      <c r="L30" s="216"/>
     </row>
     <row r="31" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A31" s="62"/>
@@ -7861,20 +7870,20 @@
       <c r="L31" s="63"/>
     </row>
     <row r="32" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="218" t="s">
+      <c r="A32" s="217" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="219"/>
-      <c r="C32" s="219"/>
-      <c r="D32" s="219"/>
-      <c r="E32" s="219"/>
-      <c r="F32" s="219"/>
-      <c r="G32" s="219"/>
-      <c r="H32" s="219"/>
-      <c r="I32" s="219"/>
-      <c r="J32" s="219"/>
-      <c r="K32" s="219"/>
-      <c r="L32" s="219"/>
+      <c r="B32" s="218"/>
+      <c r="C32" s="218"/>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="218"/>
+      <c r="H32" s="218"/>
+      <c r="I32" s="218"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="218"/>
+      <c r="L32" s="218"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
@@ -8527,23 +8536,23 @@
       <c r="L41" s="48"/>
     </row>
     <row r="42" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A42" s="251">
+      <c r="A42" s="200">
         <f>COUNT(B33:B41)</f>
         <v>4</v>
       </c>
-      <c r="B42" s="220" t="s">
+      <c r="B42" s="219" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="221"/>
-      <c r="I42" s="221"/>
-      <c r="J42" s="221"/>
-      <c r="K42" s="221"/>
-      <c r="L42" s="222"/>
+      <c r="C42" s="220"/>
+      <c r="D42" s="220"/>
+      <c r="E42" s="220"/>
+      <c r="F42" s="220"/>
+      <c r="G42" s="220"/>
+      <c r="H42" s="220"/>
+      <c r="I42" s="220"/>
+      <c r="J42" s="220"/>
+      <c r="K42" s="220"/>
+      <c r="L42" s="221"/>
     </row>
     <row r="43" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A43" s="71"/>
@@ -8560,26 +8569,26 @@
       <c r="L43" s="63"/>
     </row>
     <row r="44" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="223" t="s">
+      <c r="A44" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="223"/>
-      <c r="C44" s="223"/>
-      <c r="D44" s="223"/>
-      <c r="E44" s="223"/>
-      <c r="F44" s="223"/>
-      <c r="G44" s="223"/>
-      <c r="H44" s="223"/>
-      <c r="I44" s="223"/>
-      <c r="J44" s="223"/>
-      <c r="K44" s="223"/>
-      <c r="L44" s="223"/>
+      <c r="B44" s="222"/>
+      <c r="C44" s="222"/>
+      <c r="D44" s="222"/>
+      <c r="E44" s="222"/>
+      <c r="F44" s="222"/>
+      <c r="G44" s="222"/>
+      <c r="H44" s="222"/>
+      <c r="I44" s="222"/>
+      <c r="J44" s="222"/>
+      <c r="K44" s="222"/>
+      <c r="L44" s="222"/>
     </row>
     <row r="45" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="238">
+      <c r="A45" s="188">
         <v>1</v>
       </c>
-      <c r="B45" s="239" t="s">
+      <c r="B45" s="189" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="73"/>
@@ -8594,10 +8603,10 @@
       <c r="L45" s="72"/>
     </row>
     <row r="46" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="238">
+      <c r="A46" s="188">
         <v>2</v>
       </c>
-      <c r="B46" s="239" t="s">
+      <c r="B46" s="189" t="s">
         <v>71</v>
       </c>
       <c r="C46" s="73"/>
@@ -8612,10 +8621,10 @@
       <c r="L46" s="72"/>
     </row>
     <row r="47" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="238">
+      <c r="A47" s="188">
         <v>3</v>
       </c>
-      <c r="B47" s="239" t="s">
+      <c r="B47" s="189" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="73"/>
@@ -8633,7 +8642,7 @@
       <c r="A48" s="89">
         <v>4</v>
       </c>
-      <c r="B48" s="240" t="s">
+      <c r="B48" s="190" t="s">
         <v>67</v>
       </c>
       <c r="C48" s="75"/>
@@ -8648,23 +8657,23 @@
       <c r="L48" s="79"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="252">
+      <c r="A49" s="201">
         <f>COUNT(A45:A48)</f>
         <v>4</v>
       </c>
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="224"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="224"/>
-      <c r="I49" s="224"/>
-      <c r="J49" s="224"/>
-      <c r="K49" s="224"/>
-      <c r="L49" s="225"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="223"/>
+      <c r="I49" s="223"/>
+      <c r="J49" s="223"/>
+      <c r="K49" s="223"/>
+      <c r="L49" s="224"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="81"/>
@@ -8681,20 +8690,20 @@
       <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="226" t="s">
+      <c r="A51" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="226"/>
-      <c r="C51" s="226"/>
-      <c r="D51" s="226"/>
-      <c r="E51" s="226"/>
-      <c r="F51" s="226"/>
-      <c r="G51" s="226"/>
-      <c r="H51" s="226"/>
-      <c r="I51" s="226"/>
-      <c r="J51" s="226"/>
-      <c r="K51" s="226"/>
-      <c r="L51" s="226"/>
+      <c r="B51" s="225"/>
+      <c r="C51" s="225"/>
+      <c r="D51" s="225"/>
+      <c r="E51" s="225"/>
+      <c r="F51" s="225"/>
+      <c r="G51" s="225"/>
+      <c r="H51" s="225"/>
+      <c r="I51" s="225"/>
+      <c r="J51" s="225"/>
+      <c r="K51" s="225"/>
+      <c r="L51" s="225"/>
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="84"/>
@@ -8728,19 +8737,19 @@
       <c r="A54" s="80">
         <v>0</v>
       </c>
-      <c r="B54" s="220" t="s">
+      <c r="B54" s="219" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="221"/>
-      <c r="D54" s="221"/>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="221"/>
-      <c r="I54" s="221"/>
-      <c r="J54" s="221"/>
-      <c r="K54" s="221"/>
-      <c r="L54" s="222"/>
+      <c r="C54" s="220"/>
+      <c r="D54" s="220"/>
+      <c r="E54" s="220"/>
+      <c r="F54" s="220"/>
+      <c r="G54" s="220"/>
+      <c r="H54" s="220"/>
+      <c r="I54" s="220"/>
+      <c r="J54" s="220"/>
+      <c r="K54" s="220"/>
+      <c r="L54" s="221"/>
     </row>
     <row r="55" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A55" s="71"/>
@@ -8757,20 +8766,20 @@
       <c r="L55" s="40"/>
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="226" t="s">
+      <c r="A56" s="225" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="226"/>
-      <c r="C56" s="226"/>
-      <c r="D56" s="226"/>
-      <c r="E56" s="226"/>
-      <c r="F56" s="226"/>
-      <c r="G56" s="226"/>
-      <c r="H56" s="226"/>
-      <c r="I56" s="226"/>
-      <c r="J56" s="226"/>
-      <c r="K56" s="226"/>
-      <c r="L56" s="226"/>
+      <c r="B56" s="225"/>
+      <c r="C56" s="225"/>
+      <c r="D56" s="225"/>
+      <c r="E56" s="225"/>
+      <c r="F56" s="225"/>
+      <c r="G56" s="225"/>
+      <c r="H56" s="225"/>
+      <c r="I56" s="225"/>
+      <c r="J56" s="225"/>
+      <c r="K56" s="225"/>
+      <c r="L56" s="225"/>
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="84"/>
@@ -8804,19 +8813,19 @@
       <c r="A59" s="80">
         <v>0</v>
       </c>
-      <c r="B59" s="220" t="s">
+      <c r="B59" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="221"/>
-      <c r="D59" s="221"/>
-      <c r="E59" s="221"/>
-      <c r="F59" s="221"/>
-      <c r="G59" s="221"/>
-      <c r="H59" s="221"/>
-      <c r="I59" s="221"/>
-      <c r="J59" s="221"/>
-      <c r="K59" s="221"/>
-      <c r="L59" s="222"/>
+      <c r="C59" s="220"/>
+      <c r="D59" s="220"/>
+      <c r="E59" s="220"/>
+      <c r="F59" s="220"/>
+      <c r="G59" s="220"/>
+      <c r="H59" s="220"/>
+      <c r="I59" s="220"/>
+      <c r="J59" s="220"/>
+      <c r="K59" s="220"/>
+      <c r="L59" s="221"/>
     </row>
     <row r="60" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A60" s="71"/>
@@ -8833,20 +8842,20 @@
       <c r="L60" s="40"/>
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="226" t="s">
+      <c r="A61" s="225" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="226"/>
-      <c r="C61" s="226"/>
-      <c r="D61" s="226"/>
-      <c r="E61" s="226"/>
-      <c r="F61" s="226"/>
-      <c r="G61" s="226"/>
-      <c r="H61" s="226"/>
-      <c r="I61" s="226"/>
-      <c r="J61" s="226"/>
-      <c r="K61" s="226"/>
-      <c r="L61" s="226"/>
+      <c r="B61" s="225"/>
+      <c r="C61" s="225"/>
+      <c r="D61" s="225"/>
+      <c r="E61" s="225"/>
+      <c r="F61" s="225"/>
+      <c r="G61" s="225"/>
+      <c r="H61" s="225"/>
+      <c r="I61" s="225"/>
+      <c r="J61" s="225"/>
+      <c r="K61" s="225"/>
+      <c r="L61" s="225"/>
     </row>
     <row r="62" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="90"/>
@@ -8880,19 +8889,19 @@
       <c r="A64" s="80">
         <v>0</v>
       </c>
-      <c r="B64" s="220" t="s">
+      <c r="B64" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="221"/>
-      <c r="D64" s="221"/>
-      <c r="E64" s="221"/>
-      <c r="F64" s="221"/>
-      <c r="G64" s="221"/>
-      <c r="H64" s="221"/>
-      <c r="I64" s="221"/>
-      <c r="J64" s="221"/>
-      <c r="K64" s="221"/>
-      <c r="L64" s="222"/>
+      <c r="C64" s="220"/>
+      <c r="D64" s="220"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
+      <c r="G64" s="220"/>
+      <c r="H64" s="220"/>
+      <c r="I64" s="220"/>
+      <c r="J64" s="220"/>
+      <c r="K64" s="220"/>
+      <c r="L64" s="221"/>
     </row>
     <row r="65" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A65" s="71"/>
@@ -8909,14 +8918,14 @@
       <c r="L65" s="63"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A66" s="253">
+      <c r="A66" s="202">
         <f>A42+A49+A54+A59+A64</f>
         <v>8</v>
       </c>
-      <c r="B66" s="205" t="s">
+      <c r="B66" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="205"/>
+      <c r="C66" s="213"/>
       <c r="D66" s="94" t="s">
         <v>30</v>
       </c>
@@ -8930,14 +8939,14 @@
       <c r="L66" s="96"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="253">
+      <c r="A67" s="202">
         <f>A30+A66</f>
         <v>28</v>
       </c>
-      <c r="B67" s="205" t="s">
+      <c r="B67" s="213" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="205"/>
+      <c r="C67" s="213"/>
       <c r="D67" s="94"/>
       <c r="E67" s="95"/>
       <c r="F67" s="95"/>
@@ -8949,55 +8958,55 @@
       <c r="L67" s="96"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="206"/>
-      <c r="B68" s="207"/>
-      <c r="C68" s="207"/>
-      <c r="D68" s="207"/>
-      <c r="E68" s="207"/>
-      <c r="F68" s="207"/>
-      <c r="G68" s="207"/>
-      <c r="H68" s="207"/>
-      <c r="I68" s="207"/>
-      <c r="J68" s="207"/>
-      <c r="K68" s="207"/>
-      <c r="L68" s="208"/>
+      <c r="A68" s="226"/>
+      <c r="B68" s="227"/>
+      <c r="C68" s="227"/>
+      <c r="D68" s="227"/>
+      <c r="E68" s="227"/>
+      <c r="F68" s="227"/>
+      <c r="G68" s="227"/>
+      <c r="H68" s="227"/>
+      <c r="I68" s="227"/>
+      <c r="J68" s="227"/>
+      <c r="K68" s="227"/>
+      <c r="L68" s="228"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="209"/>
-      <c r="B69" s="210"/>
-      <c r="C69" s="210"/>
-      <c r="D69" s="210"/>
-      <c r="E69" s="210"/>
-      <c r="F69" s="210"/>
-      <c r="G69" s="210"/>
-      <c r="H69" s="210"/>
-      <c r="I69" s="210"/>
-      <c r="J69" s="210"/>
-      <c r="K69" s="210"/>
-      <c r="L69" s="211"/>
+      <c r="A69" s="229"/>
+      <c r="B69" s="230"/>
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
+      <c r="I69" s="230"/>
+      <c r="J69" s="230"/>
+      <c r="K69" s="230"/>
+      <c r="L69" s="231"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="212" t="s">
+      <c r="A70" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="212"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
-      <c r="F70" s="212"/>
-      <c r="G70" s="212"/>
-      <c r="H70" s="212"/>
-      <c r="I70" s="212"/>
-      <c r="J70" s="212"/>
-      <c r="K70" s="212"/>
-      <c r="L70" s="212"/>
+      <c r="B70" s="238"/>
+      <c r="C70" s="238"/>
+      <c r="D70" s="238"/>
+      <c r="E70" s="238"/>
+      <c r="F70" s="238"/>
+      <c r="G70" s="238"/>
+      <c r="H70" s="238"/>
+      <c r="I70" s="238"/>
+      <c r="J70" s="238"/>
+      <c r="K70" s="238"/>
+      <c r="L70" s="238"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
+      <c r="B71" s="239"/>
+      <c r="C71" s="239"/>
       <c r="D71" s="97"/>
       <c r="E71" s="97"/>
       <c r="F71" s="97"/>
@@ -9009,14 +9018,14 @@
       <c r="L71" s="98"/>
     </row>
     <row r="72" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="244"/>
-      <c r="B72" s="245" t="s">
+      <c r="A72" s="194"/>
+      <c r="B72" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="246" t="s">
+      <c r="C72" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="246" t="s">
+      <c r="D72" s="196" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="46" t="s">
@@ -9051,11 +9060,11 @@
       <c r="D73" s="49"/>
       <c r="E73" s="51"/>
       <c r="F73" s="51"/>
-      <c r="G73" s="248"/>
-      <c r="H73" s="248"/>
-      <c r="I73" s="248"/>
+      <c r="G73" s="197"/>
+      <c r="H73" s="197"/>
+      <c r="I73" s="197"/>
       <c r="J73" s="48"/>
-      <c r="K73" s="248"/>
+      <c r="K73" s="197"/>
       <c r="L73" s="48"/>
     </row>
     <row r="74" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
@@ -9067,11 +9076,11 @@
       <c r="D74" s="49"/>
       <c r="E74" s="51"/>
       <c r="F74" s="51"/>
-      <c r="G74" s="248"/>
-      <c r="H74" s="248"/>
-      <c r="I74" s="248"/>
+      <c r="G74" s="197"/>
+      <c r="H74" s="197"/>
+      <c r="I74" s="197"/>
       <c r="J74" s="48"/>
-      <c r="K74" s="248"/>
+      <c r="K74" s="197"/>
       <c r="L74" s="48"/>
     </row>
     <row r="75" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
@@ -9083,9 +9092,9 @@
       <c r="D75" s="49"/>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
-      <c r="G75" s="248"/>
-      <c r="H75" s="248"/>
-      <c r="I75" s="248"/>
+      <c r="G75" s="197"/>
+      <c r="H75" s="197"/>
+      <c r="I75" s="197"/>
       <c r="J75" s="48"/>
       <c r="K75" s="51"/>
       <c r="L75" s="48"/>
@@ -9099,10 +9108,10 @@
       <c r="D76" s="49"/>
       <c r="E76" s="51"/>
       <c r="F76" s="51"/>
-      <c r="G76" s="248"/>
-      <c r="H76" s="248"/>
-      <c r="I76" s="248"/>
-      <c r="J76" s="248"/>
+      <c r="G76" s="197"/>
+      <c r="H76" s="197"/>
+      <c r="I76" s="197"/>
+      <c r="J76" s="197"/>
       <c r="K76" s="51"/>
       <c r="L76" s="48"/>
     </row>
@@ -9115,10 +9124,10 @@
       <c r="D77" s="49"/>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
-      <c r="G77" s="248"/>
-      <c r="H77" s="248"/>
-      <c r="I77" s="248"/>
-      <c r="J77" s="248"/>
+      <c r="G77" s="197"/>
+      <c r="H77" s="197"/>
+      <c r="I77" s="197"/>
+      <c r="J77" s="197"/>
       <c r="K77" s="51"/>
       <c r="L77" s="48"/>
     </row>
@@ -9131,9 +9140,9 @@
       <c r="D78" s="49"/>
       <c r="E78" s="50"/>
       <c r="F78" s="51"/>
-      <c r="G78" s="248"/>
-      <c r="H78" s="248"/>
-      <c r="I78" s="248"/>
+      <c r="G78" s="197"/>
+      <c r="H78" s="197"/>
+      <c r="I78" s="197"/>
       <c r="J78" s="48"/>
       <c r="K78" s="51"/>
       <c r="L78" s="48"/>
@@ -9150,7 +9159,7 @@
       <c r="G79" s="51"/>
       <c r="H79" s="51"/>
       <c r="I79" s="51"/>
-      <c r="J79" s="248"/>
+      <c r="J79" s="197"/>
       <c r="K79" s="51"/>
       <c r="L79" s="48"/>
     </row>
@@ -9426,16 +9435,16 @@
       <c r="K96" s="52"/>
       <c r="L96" s="56"/>
     </row>
-    <row r="97" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A97" s="70">
         <f>COUNT(B73:B96)</f>
         <v>24</v>
       </c>
-      <c r="B97" s="247" t="s">
+      <c r="B97" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="247"/>
-      <c r="D97" s="247"/>
+      <c r="C97" s="240"/>
+      <c r="D97" s="240"/>
       <c r="E97" s="93"/>
       <c r="F97" s="93"/>
       <c r="G97" s="93"/>
@@ -9445,7 +9454,7 @@
       <c r="K97" s="93"/>
       <c r="L97" s="91"/>
     </row>
-    <row r="98" spans="1:12" s="38" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="123"/>
       <c r="B98" s="124"/>
       <c r="C98" s="124"/>
@@ -9459,23 +9468,23 @@
       <c r="K98" s="95"/>
       <c r="L98" s="96"/>
     </row>
-    <row r="99" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="241" t="s">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A99" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="242"/>
-      <c r="C99" s="242"/>
-      <c r="D99" s="242"/>
-      <c r="E99" s="242"/>
-      <c r="F99" s="242"/>
-      <c r="G99" s="242"/>
-      <c r="H99" s="242"/>
-      <c r="I99" s="242"/>
-      <c r="J99" s="242"/>
-      <c r="K99" s="242"/>
-      <c r="L99" s="243"/>
-    </row>
-    <row r="100" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B99" s="192"/>
+      <c r="C99" s="192"/>
+      <c r="D99" s="192"/>
+      <c r="E99" s="192"/>
+      <c r="F99" s="192"/>
+      <c r="G99" s="192"/>
+      <c r="H99" s="192"/>
+      <c r="I99" s="192"/>
+      <c r="J99" s="192"/>
+      <c r="K99" s="192"/>
+      <c r="L99" s="193"/>
+    </row>
+    <row r="100" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A100" s="89"/>
       <c r="B100" s="48">
         <v>733</v>
@@ -9491,7 +9500,7 @@
       <c r="K100" s="51"/>
       <c r="L100" s="48"/>
     </row>
-    <row r="101" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A101" s="89"/>
       <c r="B101" s="48">
         <v>755</v>
@@ -9507,7 +9516,7 @@
       <c r="K101" s="51"/>
       <c r="L101" s="48"/>
     </row>
-    <row r="102" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A102" s="89"/>
       <c r="B102" s="48">
         <v>760</v>
@@ -9523,7 +9532,7 @@
       <c r="K102" s="51"/>
       <c r="L102" s="48"/>
     </row>
-    <row r="103" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A103" s="89"/>
       <c r="B103" s="48">
         <v>762</v>
@@ -9539,7 +9548,7 @@
       <c r="K103" s="51"/>
       <c r="L103" s="48"/>
     </row>
-    <row r="104" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A104" s="89"/>
       <c r="B104" s="48">
         <v>763</v>
@@ -9555,7 +9564,7 @@
       <c r="K104" s="51"/>
       <c r="L104" s="48"/>
     </row>
-    <row r="105" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A105" s="89"/>
       <c r="B105" s="48">
         <v>765</v>
@@ -9571,26 +9580,26 @@
       <c r="K105" s="51"/>
       <c r="L105" s="48"/>
     </row>
-    <row r="106" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A106" s="252">
+    <row r="106" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A106" s="201">
         <f>COUNT(B100:B105)</f>
         <v>6</v>
       </c>
-      <c r="B106" s="254" t="s">
+      <c r="B106" s="241" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="254"/>
-      <c r="D106" s="254"/>
-      <c r="E106" s="254"/>
-      <c r="F106" s="254"/>
-      <c r="G106" s="254"/>
-      <c r="H106" s="254"/>
-      <c r="I106" s="254"/>
-      <c r="J106" s="254"/>
-      <c r="K106" s="254"/>
-      <c r="L106" s="254"/>
-    </row>
-    <row r="107" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C106" s="241"/>
+      <c r="D106" s="241"/>
+      <c r="E106" s="241"/>
+      <c r="F106" s="241"/>
+      <c r="G106" s="241"/>
+      <c r="H106" s="241"/>
+      <c r="I106" s="241"/>
+      <c r="J106" s="241"/>
+      <c r="K106" s="241"/>
+      <c r="L106" s="241"/>
+    </row>
+    <row r="107" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A107" s="39"/>
       <c r="B107" s="144"/>
       <c r="C107" s="145"/>
@@ -9604,25 +9613,25 @@
       <c r="K107" s="148"/>
       <c r="L107" s="40"/>
     </row>
-    <row r="108" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="69"/>
-      <c r="B108" s="256" t="s">
+      <c r="B108" s="242" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="256"/>
-      <c r="D108" s="256"/>
-      <c r="E108" s="256"/>
-      <c r="F108" s="256"/>
-      <c r="G108" s="256"/>
-      <c r="H108" s="256"/>
-      <c r="I108" s="256"/>
-      <c r="J108" s="256"/>
-      <c r="K108" s="256"/>
-      <c r="L108" s="256"/>
-    </row>
-    <row r="109" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C108" s="242"/>
+      <c r="D108" s="242"/>
+      <c r="E108" s="242"/>
+      <c r="F108" s="242"/>
+      <c r="G108" s="242"/>
+      <c r="H108" s="242"/>
+      <c r="I108" s="242"/>
+      <c r="J108" s="242"/>
+      <c r="K108" s="242"/>
+      <c r="L108" s="242"/>
+    </row>
+    <row r="109" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A109" s="89"/>
-      <c r="B109" s="257" t="s">
+      <c r="B109" s="203" t="s">
         <v>76</v>
       </c>
       <c r="C109" s="68"/>
@@ -9636,9 +9645,9 @@
       <c r="K109" s="59"/>
       <c r="L109" s="48"/>
     </row>
-    <row r="110" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A110" s="89"/>
-      <c r="B110" s="257" t="s">
+      <c r="B110" s="203" t="s">
         <v>65</v>
       </c>
       <c r="C110" s="68"/>
@@ -9652,9 +9661,9 @@
       <c r="K110" s="59"/>
       <c r="L110" s="48"/>
     </row>
-    <row r="111" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A111" s="89"/>
-      <c r="B111" s="257" t="s">
+      <c r="B111" s="203" t="s">
         <v>66</v>
       </c>
       <c r="C111" s="56"/>
@@ -9668,9 +9677,9 @@
       <c r="K111" s="59"/>
       <c r="L111" s="48"/>
     </row>
-    <row r="112" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A112" s="89"/>
-      <c r="B112" s="257" t="s">
+      <c r="B112" s="203" t="s">
         <v>68</v>
       </c>
       <c r="C112" s="56"/>
@@ -9684,9 +9693,9 @@
       <c r="K112" s="59"/>
       <c r="L112" s="48"/>
     </row>
-    <row r="113" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A113" s="89"/>
-      <c r="B113" s="257" t="s">
+      <c r="B113" s="203" t="s">
         <v>77</v>
       </c>
       <c r="C113" s="56"/>
@@ -9700,9 +9709,9 @@
       <c r="K113" s="59"/>
       <c r="L113" s="48"/>
     </row>
-    <row r="114" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A114" s="89"/>
-      <c r="B114" s="257" t="s">
+      <c r="B114" s="203" t="s">
         <v>69</v>
       </c>
       <c r="C114" s="56"/>
@@ -9716,9 +9725,9 @@
       <c r="K114" s="59"/>
       <c r="L114" s="48"/>
     </row>
-    <row r="115" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A115" s="89"/>
-      <c r="B115" s="257" t="s">
+      <c r="B115" s="203" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="56"/>
@@ -9732,45 +9741,45 @@
       <c r="K115" s="59"/>
       <c r="L115" s="48"/>
     </row>
-    <row r="116" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A116" s="252">
+    <row r="116" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A116" s="201">
         <f>COUNTA(B109:B115)</f>
         <v>7</v>
       </c>
-      <c r="B116" s="254" t="s">
+      <c r="B116" s="241" t="s">
         <v>37</v>
       </c>
-      <c r="C116" s="254"/>
-      <c r="D116" s="254"/>
-      <c r="E116" s="254"/>
-      <c r="F116" s="254"/>
-      <c r="G116" s="254"/>
-      <c r="H116" s="254"/>
-      <c r="I116" s="254"/>
-      <c r="J116" s="254"/>
-      <c r="K116" s="254"/>
-      <c r="L116" s="254"/>
-    </row>
-    <row r="117" spans="1:12" s="255" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A117" s="252">
+      <c r="C116" s="241"/>
+      <c r="D116" s="241"/>
+      <c r="E116" s="241"/>
+      <c r="F116" s="241"/>
+      <c r="G116" s="241"/>
+      <c r="H116" s="241"/>
+      <c r="I116" s="241"/>
+      <c r="J116" s="241"/>
+      <c r="K116" s="241"/>
+      <c r="L116" s="241"/>
+    </row>
+    <row r="117" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A117" s="201">
         <f>A116+A106</f>
         <v>13</v>
       </c>
-      <c r="B117" s="258" t="s">
+      <c r="B117" s="243" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="258"/>
-      <c r="D117" s="258"/>
-      <c r="E117" s="258"/>
-      <c r="F117" s="258"/>
-      <c r="G117" s="258"/>
-      <c r="H117" s="258"/>
-      <c r="I117" s="258"/>
-      <c r="J117" s="258"/>
-      <c r="K117" s="258"/>
-      <c r="L117" s="258"/>
-    </row>
-    <row r="118" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C117" s="243"/>
+      <c r="D117" s="243"/>
+      <c r="E117" s="243"/>
+      <c r="F117" s="243"/>
+      <c r="G117" s="243"/>
+      <c r="H117" s="243"/>
+      <c r="I117" s="243"/>
+      <c r="J117" s="243"/>
+      <c r="K117" s="243"/>
+      <c r="L117" s="243"/>
+    </row>
+    <row r="118" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A118" s="39"/>
       <c r="B118" s="40"/>
       <c r="C118" s="41"/>
@@ -9784,7 +9793,7 @@
       <c r="K118" s="42"/>
       <c r="L118" s="40"/>
     </row>
-    <row r="119" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="152" t="s">
         <v>39</v>
       </c>
@@ -9800,7 +9809,7 @@
       <c r="K119" s="153"/>
       <c r="L119" s="154"/>
     </row>
-    <row r="120" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A120" s="104"/>
       <c r="B120" s="96"/>
       <c r="C120" s="94"/>
@@ -9814,7 +9823,7 @@
       <c r="K120" s="95"/>
       <c r="L120" s="96"/>
     </row>
-    <row r="121" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A121" s="104"/>
       <c r="B121" s="96"/>
       <c r="C121" s="94"/>
@@ -9828,7 +9837,7 @@
       <c r="K121" s="95"/>
       <c r="L121" s="96"/>
     </row>
-    <row r="122" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A122" s="104"/>
       <c r="B122" s="96"/>
       <c r="C122" s="94"/>
@@ -9842,7 +9851,7 @@
       <c r="K122" s="95"/>
       <c r="L122" s="96"/>
     </row>
-    <row r="123" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A123" s="104"/>
       <c r="B123" s="96"/>
       <c r="C123" s="94"/>
@@ -9856,7 +9865,7 @@
       <c r="K123" s="95"/>
       <c r="L123" s="96"/>
     </row>
-    <row r="124" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A124" s="155"/>
       <c r="B124" s="96"/>
       <c r="C124" s="94"/>
@@ -9870,25 +9879,25 @@
       <c r="K124" s="95"/>
       <c r="L124" s="96"/>
     </row>
-    <row r="125" spans="1:12" s="38" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A125" s="61">
         <v>4</v>
       </c>
-      <c r="B125" s="199" t="s">
+      <c r="B125" s="232" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="200"/>
-      <c r="D125" s="200"/>
-      <c r="E125" s="200"/>
-      <c r="F125" s="200"/>
-      <c r="G125" s="200"/>
-      <c r="H125" s="200"/>
-      <c r="I125" s="200"/>
-      <c r="J125" s="200"/>
-      <c r="K125" s="200"/>
-      <c r="L125" s="201"/>
-    </row>
-    <row r="126" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C125" s="233"/>
+      <c r="D125" s="233"/>
+      <c r="E125" s="233"/>
+      <c r="F125" s="233"/>
+      <c r="G125" s="233"/>
+      <c r="H125" s="233"/>
+      <c r="I125" s="233"/>
+      <c r="J125" s="233"/>
+      <c r="K125" s="233"/>
+      <c r="L125" s="234"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="125" t="s">
         <v>41</v>
       </c>
@@ -9904,7 +9913,7 @@
       <c r="K126" s="97"/>
       <c r="L126" s="98"/>
     </row>
-    <row r="127" spans="1:12" s="38" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="155"/>
       <c r="B127" s="156"/>
       <c r="C127" s="94"/>
@@ -9918,7 +9927,7 @@
       <c r="K127" s="95"/>
       <c r="L127" s="96"/>
     </row>
-    <row r="128" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A128" s="155"/>
       <c r="B128" s="96"/>
       <c r="C128" s="94"/>
@@ -9932,7 +9941,7 @@
       <c r="K128" s="95"/>
       <c r="L128" s="96"/>
     </row>
-    <row r="129" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="125" t="s">
         <v>42</v>
       </c>
@@ -9948,7 +9957,7 @@
       <c r="K129" s="97"/>
       <c r="L129" s="98"/>
     </row>
-    <row r="130" spans="1:12" s="38" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="126"/>
       <c r="B130" s="127"/>
       <c r="C130" s="128"/>
@@ -9962,7 +9971,7 @@
       <c r="K130" s="158"/>
       <c r="L130" s="127"/>
     </row>
-    <row r="131" spans="1:12" s="38" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A131" s="126"/>
       <c r="B131" s="159"/>
       <c r="C131" s="160"/>
@@ -9976,25 +9985,25 @@
       <c r="K131" s="165"/>
       <c r="L131" s="166"/>
     </row>
-    <row r="132" spans="1:12" s="38" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A132" s="143">
         <v>0</v>
       </c>
-      <c r="B132" s="202" t="s">
+      <c r="B132" s="235" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="203"/>
-      <c r="D132" s="203"/>
-      <c r="E132" s="203"/>
-      <c r="F132" s="203"/>
-      <c r="G132" s="203"/>
-      <c r="H132" s="203"/>
-      <c r="I132" s="203"/>
-      <c r="J132" s="203"/>
-      <c r="K132" s="203"/>
-      <c r="L132" s="204"/>
-    </row>
-    <row r="133" spans="1:12" s="38" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C132" s="236"/>
+      <c r="D132" s="236"/>
+      <c r="E132" s="236"/>
+      <c r="F132" s="236"/>
+      <c r="G132" s="236"/>
+      <c r="H132" s="236"/>
+      <c r="I132" s="236"/>
+      <c r="J132" s="236"/>
+      <c r="K132" s="236"/>
+      <c r="L132" s="237"/>
+    </row>
+    <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="167">
         <f>A97+A117</f>
         <v>37</v>
@@ -10013,17 +10022,6 @@
       <c r="K133" s="169"/>
       <c r="L133" s="170"/>
     </row>
-    <row r="134" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="135" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="136" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="137" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="138" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="139" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="142" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="1:12" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="145" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="146" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="147" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -10070,16 +10068,18 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="29">
-    <mergeCell ref="B108:L108"/>
-    <mergeCell ref="B116:L116"/>
-    <mergeCell ref="B117:L117"/>
-    <mergeCell ref="B125:L125"/>
-    <mergeCell ref="B132:L132"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="A68:L69"/>
-    <mergeCell ref="A70:L70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="B49:L49"/>
     <mergeCell ref="B106:L106"/>
     <mergeCell ref="B54:L54"/>
     <mergeCell ref="A56:L56"/>
@@ -10087,18 +10087,16 @@
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="B64:L64"/>
     <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="B49:L49"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="A68:L69"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B108:L108"/>
+    <mergeCell ref="B116:L116"/>
+    <mergeCell ref="B117:L117"/>
+    <mergeCell ref="B125:L125"/>
+    <mergeCell ref="B132:L132"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10953,36 +10951,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-      <c r="L2" s="191"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -11003,36 +11001,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="192"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -11049,34 +11047,34 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="195"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="211"/>
+      <c r="K7" s="211"/>
+      <c r="L7" s="212"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="187"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="189"/>
+      <c r="A8" s="204"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="206"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="183" t="s">
@@ -16218,36 +16216,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-      <c r="L2" s="191"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -16268,36 +16266,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="192"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -16314,36 +16312,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="195"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="211"/>
+      <c r="K7" s="211"/>
+      <c r="L7" s="212"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="187" t="s">
+      <c r="A8" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="189"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="206"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -19783,19 +19781,19 @@
       <c r="A26" s="61">
         <v>0</v>
       </c>
-      <c r="B26" s="215" t="s">
+      <c r="B26" s="214" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="216"/>
-      <c r="D26" s="216"/>
-      <c r="E26" s="216"/>
-      <c r="F26" s="216"/>
-      <c r="G26" s="216"/>
-      <c r="H26" s="216"/>
-      <c r="I26" s="216"/>
-      <c r="J26" s="216"/>
-      <c r="K26" s="216"/>
-      <c r="L26" s="217"/>
+      <c r="C26" s="215"/>
+      <c r="D26" s="215"/>
+      <c r="E26" s="215"/>
+      <c r="F26" s="215"/>
+      <c r="G26" s="215"/>
+      <c r="H26" s="215"/>
+      <c r="I26" s="215"/>
+      <c r="J26" s="215"/>
+      <c r="K26" s="215"/>
+      <c r="L26" s="216"/>
     </row>
     <row r="27" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A27" s="62"/>
@@ -19812,20 +19810,20 @@
       <c r="L27" s="63"/>
     </row>
     <row r="28" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="218" t="s">
+      <c r="A28" s="217" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="219"/>
-      <c r="C28" s="219"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="219"/>
-      <c r="F28" s="219"/>
-      <c r="G28" s="219"/>
-      <c r="H28" s="219"/>
-      <c r="I28" s="219"/>
-      <c r="J28" s="219"/>
-      <c r="K28" s="219"/>
-      <c r="L28" s="219"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="218"/>
+      <c r="D28" s="218"/>
+      <c r="E28" s="218"/>
+      <c r="F28" s="218"/>
+      <c r="G28" s="218"/>
+      <c r="H28" s="218"/>
+      <c r="I28" s="218"/>
+      <c r="J28" s="218"/>
+      <c r="K28" s="218"/>
+      <c r="L28" s="218"/>
       <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
@@ -20445,19 +20443,19 @@
       <c r="A38" s="70">
         <v>0</v>
       </c>
-      <c r="B38" s="220" t="s">
+      <c r="B38" s="219" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="221"/>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="221"/>
-      <c r="H38" s="221"/>
-      <c r="I38" s="221"/>
-      <c r="J38" s="221"/>
-      <c r="K38" s="221"/>
-      <c r="L38" s="222"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="220"/>
+      <c r="H38" s="220"/>
+      <c r="I38" s="220"/>
+      <c r="J38" s="220"/>
+      <c r="K38" s="220"/>
+      <c r="L38" s="221"/>
     </row>
     <row r="39" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A39" s="71"/>
@@ -20474,20 +20472,20 @@
       <c r="L39" s="63"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="223" t="s">
+      <c r="A40" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="223"/>
-      <c r="C40" s="223"/>
-      <c r="D40" s="223"/>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="223"/>
-      <c r="I40" s="223"/>
-      <c r="J40" s="223"/>
-      <c r="K40" s="223"/>
-      <c r="L40" s="223"/>
+      <c r="B40" s="222"/>
+      <c r="C40" s="222"/>
+      <c r="D40" s="222"/>
+      <c r="E40" s="222"/>
+      <c r="F40" s="222"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="222"/>
+      <c r="I40" s="222"/>
+      <c r="J40" s="222"/>
+      <c r="K40" s="222"/>
+      <c r="L40" s="222"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="72"/>
@@ -20521,19 +20519,19 @@
       <c r="A43" s="80">
         <v>0</v>
       </c>
-      <c r="B43" s="224" t="s">
+      <c r="B43" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="225"/>
+      <c r="C43" s="223"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="223"/>
+      <c r="I43" s="223"/>
+      <c r="J43" s="223"/>
+      <c r="K43" s="223"/>
+      <c r="L43" s="224"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="81"/>
@@ -20550,20 +20548,20 @@
       <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="226" t="s">
+      <c r="A45" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="226"/>
-      <c r="C45" s="226"/>
-      <c r="D45" s="226"/>
-      <c r="E45" s="226"/>
-      <c r="F45" s="226"/>
-      <c r="G45" s="226"/>
-      <c r="H45" s="226"/>
-      <c r="I45" s="226"/>
-      <c r="J45" s="226"/>
-      <c r="K45" s="226"/>
-      <c r="L45" s="226"/>
+      <c r="B45" s="225"/>
+      <c r="C45" s="225"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
+      <c r="G45" s="225"/>
+      <c r="H45" s="225"/>
+      <c r="I45" s="225"/>
+      <c r="J45" s="225"/>
+      <c r="K45" s="225"/>
+      <c r="L45" s="225"/>
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="84"/>
@@ -20597,19 +20595,19 @@
       <c r="A48" s="80">
         <v>0</v>
       </c>
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="219" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="221"/>
-      <c r="K48" s="221"/>
-      <c r="L48" s="222"/>
+      <c r="C48" s="220"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="220"/>
+      <c r="F48" s="220"/>
+      <c r="G48" s="220"/>
+      <c r="H48" s="220"/>
+      <c r="I48" s="220"/>
+      <c r="J48" s="220"/>
+      <c r="K48" s="220"/>
+      <c r="L48" s="221"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A49" s="71"/>
@@ -20626,20 +20624,20 @@
       <c r="L49" s="40"/>
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="226" t="s">
+      <c r="A50" s="225" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="226"/>
-      <c r="C50" s="226"/>
-      <c r="D50" s="226"/>
-      <c r="E50" s="226"/>
-      <c r="F50" s="226"/>
-      <c r="G50" s="226"/>
-      <c r="H50" s="226"/>
-      <c r="I50" s="226"/>
-      <c r="J50" s="226"/>
-      <c r="K50" s="226"/>
-      <c r="L50" s="226"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
+      <c r="D50" s="225"/>
+      <c r="E50" s="225"/>
+      <c r="F50" s="225"/>
+      <c r="G50" s="225"/>
+      <c r="H50" s="225"/>
+      <c r="I50" s="225"/>
+      <c r="J50" s="225"/>
+      <c r="K50" s="225"/>
+      <c r="L50" s="225"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="84"/>
@@ -20673,19 +20671,19 @@
       <c r="A53" s="80">
         <v>0</v>
       </c>
-      <c r="B53" s="220" t="s">
+      <c r="B53" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="221"/>
-      <c r="D53" s="221"/>
-      <c r="E53" s="221"/>
-      <c r="F53" s="221"/>
-      <c r="G53" s="221"/>
-      <c r="H53" s="221"/>
-      <c r="I53" s="221"/>
-      <c r="J53" s="221"/>
-      <c r="K53" s="221"/>
-      <c r="L53" s="222"/>
+      <c r="C53" s="220"/>
+      <c r="D53" s="220"/>
+      <c r="E53" s="220"/>
+      <c r="F53" s="220"/>
+      <c r="G53" s="220"/>
+      <c r="H53" s="220"/>
+      <c r="I53" s="220"/>
+      <c r="J53" s="220"/>
+      <c r="K53" s="220"/>
+      <c r="L53" s="221"/>
     </row>
     <row r="54" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A54" s="71"/>
@@ -20702,20 +20700,20 @@
       <c r="L54" s="40"/>
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="226" t="s">
+      <c r="A55" s="225" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="226"/>
-      <c r="C55" s="226"/>
-      <c r="D55" s="226"/>
-      <c r="E55" s="226"/>
-      <c r="F55" s="226"/>
-      <c r="G55" s="226"/>
-      <c r="H55" s="226"/>
-      <c r="I55" s="226"/>
-      <c r="J55" s="226"/>
-      <c r="K55" s="226"/>
-      <c r="L55" s="226"/>
+      <c r="B55" s="225"/>
+      <c r="C55" s="225"/>
+      <c r="D55" s="225"/>
+      <c r="E55" s="225"/>
+      <c r="F55" s="225"/>
+      <c r="G55" s="225"/>
+      <c r="H55" s="225"/>
+      <c r="I55" s="225"/>
+      <c r="J55" s="225"/>
+      <c r="K55" s="225"/>
+      <c r="L55" s="225"/>
     </row>
     <row r="56" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="90"/>
@@ -20749,19 +20747,19 @@
       <c r="A58" s="80">
         <v>0</v>
       </c>
-      <c r="B58" s="220" t="s">
+      <c r="B58" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="221"/>
-      <c r="D58" s="221"/>
-      <c r="E58" s="221"/>
-      <c r="F58" s="221"/>
-      <c r="G58" s="221"/>
-      <c r="H58" s="221"/>
-      <c r="I58" s="221"/>
-      <c r="J58" s="221"/>
-      <c r="K58" s="221"/>
-      <c r="L58" s="222"/>
+      <c r="C58" s="220"/>
+      <c r="D58" s="220"/>
+      <c r="E58" s="220"/>
+      <c r="F58" s="220"/>
+      <c r="G58" s="220"/>
+      <c r="H58" s="220"/>
+      <c r="I58" s="220"/>
+      <c r="J58" s="220"/>
+      <c r="K58" s="220"/>
+      <c r="L58" s="221"/>
     </row>
     <row r="59" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A59" s="71"/>
@@ -20779,10 +20777,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
-      <c r="B60" s="205" t="s">
+      <c r="B60" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="C60" s="205"/>
+      <c r="C60" s="213"/>
       <c r="D60" s="94" t="s">
         <v>30</v>
       </c>
@@ -20797,10 +20795,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
-      <c r="B61" s="205" t="s">
+      <c r="B61" s="213" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="205"/>
+      <c r="C61" s="213"/>
       <c r="D61" s="94"/>
       <c r="E61" s="95"/>
       <c r="F61" s="95"/>
@@ -20812,55 +20810,55 @@
       <c r="L61" s="96"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="206"/>
-      <c r="B62" s="207"/>
-      <c r="C62" s="207"/>
-      <c r="D62" s="207"/>
-      <c r="E62" s="207"/>
-      <c r="F62" s="207"/>
-      <c r="G62" s="207"/>
-      <c r="H62" s="207"/>
-      <c r="I62" s="207"/>
-      <c r="J62" s="207"/>
-      <c r="K62" s="207"/>
-      <c r="L62" s="208"/>
+      <c r="A62" s="226"/>
+      <c r="B62" s="227"/>
+      <c r="C62" s="227"/>
+      <c r="D62" s="227"/>
+      <c r="E62" s="227"/>
+      <c r="F62" s="227"/>
+      <c r="G62" s="227"/>
+      <c r="H62" s="227"/>
+      <c r="I62" s="227"/>
+      <c r="J62" s="227"/>
+      <c r="K62" s="227"/>
+      <c r="L62" s="228"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="209"/>
-      <c r="B63" s="210"/>
-      <c r="C63" s="210"/>
-      <c r="D63" s="210"/>
-      <c r="E63" s="210"/>
-      <c r="F63" s="210"/>
-      <c r="G63" s="210"/>
-      <c r="H63" s="210"/>
-      <c r="I63" s="210"/>
-      <c r="J63" s="210"/>
-      <c r="K63" s="210"/>
-      <c r="L63" s="211"/>
+      <c r="A63" s="229"/>
+      <c r="B63" s="230"/>
+      <c r="C63" s="230"/>
+      <c r="D63" s="230"/>
+      <c r="E63" s="230"/>
+      <c r="F63" s="230"/>
+      <c r="G63" s="230"/>
+      <c r="H63" s="230"/>
+      <c r="I63" s="230"/>
+      <c r="J63" s="230"/>
+      <c r="K63" s="230"/>
+      <c r="L63" s="231"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="212" t="s">
+      <c r="A64" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="B64" s="212"/>
-      <c r="C64" s="212"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
-      <c r="F64" s="212"/>
-      <c r="G64" s="212"/>
-      <c r="H64" s="212"/>
-      <c r="I64" s="212"/>
-      <c r="J64" s="212"/>
-      <c r="K64" s="212"/>
-      <c r="L64" s="212"/>
+      <c r="B64" s="238"/>
+      <c r="C64" s="238"/>
+      <c r="D64" s="238"/>
+      <c r="E64" s="238"/>
+      <c r="F64" s="238"/>
+      <c r="G64" s="238"/>
+      <c r="H64" s="238"/>
+      <c r="I64" s="238"/>
+      <c r="J64" s="238"/>
+      <c r="K64" s="238"/>
+      <c r="L64" s="238"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="213" t="s">
+      <c r="A65" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="213"/>
-      <c r="C65" s="213"/>
+      <c r="B65" s="239"/>
+      <c r="C65" s="239"/>
       <c r="D65" s="97"/>
       <c r="E65" s="97"/>
       <c r="F65" s="97"/>
@@ -21931,11 +21929,11 @@
       <c r="A140" s="61">
         <v>0</v>
       </c>
-      <c r="B140" s="213" t="s">
+      <c r="B140" s="239" t="s">
         <v>34</v>
       </c>
-      <c r="C140" s="213"/>
-      <c r="D140" s="213"/>
+      <c r="C140" s="239"/>
+      <c r="D140" s="239"/>
       <c r="E140" s="95"/>
       <c r="F140" s="95"/>
       <c r="G140" s="95"/>
@@ -22021,19 +22019,19 @@
       <c r="A146" s="143">
         <v>0</v>
       </c>
-      <c r="B146" s="214" t="s">
+      <c r="B146" s="247" t="s">
         <v>36</v>
       </c>
-      <c r="C146" s="214"/>
-      <c r="D146" s="214"/>
-      <c r="E146" s="214"/>
-      <c r="F146" s="214"/>
-      <c r="G146" s="214"/>
-      <c r="H146" s="214"/>
-      <c r="I146" s="214"/>
-      <c r="J146" s="214"/>
-      <c r="K146" s="214"/>
-      <c r="L146" s="214"/>
+      <c r="C146" s="247"/>
+      <c r="D146" s="247"/>
+      <c r="E146" s="247"/>
+      <c r="F146" s="247"/>
+      <c r="G146" s="247"/>
+      <c r="H146" s="247"/>
+      <c r="I146" s="247"/>
+      <c r="J146" s="247"/>
+      <c r="K146" s="247"/>
+      <c r="L146" s="247"/>
     </row>
     <row r="147" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A147" s="39"/>
@@ -22050,19 +22048,19 @@
       <c r="L147" s="40"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="196" t="s">
+      <c r="B148" s="244" t="s">
         <v>22</v>
       </c>
-      <c r="C148" s="196"/>
-      <c r="D148" s="196"/>
-      <c r="E148" s="196"/>
-      <c r="F148" s="196"/>
-      <c r="G148" s="196"/>
-      <c r="H148" s="196"/>
-      <c r="I148" s="196"/>
-      <c r="J148" s="196"/>
-      <c r="K148" s="196"/>
-      <c r="L148" s="196"/>
+      <c r="C148" s="244"/>
+      <c r="D148" s="244"/>
+      <c r="E148" s="244"/>
+      <c r="F148" s="244"/>
+      <c r="G148" s="244"/>
+      <c r="H148" s="244"/>
+      <c r="I148" s="244"/>
+      <c r="J148" s="244"/>
+      <c r="K148" s="244"/>
+      <c r="L148" s="244"/>
     </row>
     <row r="149" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A149" s="89"/>
@@ -22194,19 +22192,19 @@
       <c r="A158" s="150">
         <v>0</v>
       </c>
-      <c r="B158" s="197" t="s">
+      <c r="B158" s="245" t="s">
         <v>37</v>
       </c>
-      <c r="C158" s="197"/>
-      <c r="D158" s="197"/>
-      <c r="E158" s="197"/>
-      <c r="F158" s="197"/>
-      <c r="G158" s="197"/>
-      <c r="H158" s="197"/>
-      <c r="I158" s="197"/>
-      <c r="J158" s="197"/>
-      <c r="K158" s="197"/>
-      <c r="L158" s="198"/>
+      <c r="C158" s="245"/>
+      <c r="D158" s="245"/>
+      <c r="E158" s="245"/>
+      <c r="F158" s="245"/>
+      <c r="G158" s="245"/>
+      <c r="H158" s="245"/>
+      <c r="I158" s="245"/>
+      <c r="J158" s="245"/>
+      <c r="K158" s="245"/>
+      <c r="L158" s="246"/>
     </row>
     <row r="159" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C159" s="145"/>
@@ -22342,19 +22340,19 @@
       <c r="A168" s="61">
         <v>4</v>
       </c>
-      <c r="B168" s="199" t="s">
+      <c r="B168" s="232" t="s">
         <v>40</v>
       </c>
-      <c r="C168" s="200"/>
-      <c r="D168" s="200"/>
-      <c r="E168" s="200"/>
-      <c r="F168" s="200"/>
-      <c r="G168" s="200"/>
-      <c r="H168" s="200"/>
-      <c r="I168" s="200"/>
-      <c r="J168" s="200"/>
-      <c r="K168" s="200"/>
-      <c r="L168" s="201"/>
+      <c r="C168" s="233"/>
+      <c r="D168" s="233"/>
+      <c r="E168" s="233"/>
+      <c r="F168" s="233"/>
+      <c r="G168" s="233"/>
+      <c r="H168" s="233"/>
+      <c r="I168" s="233"/>
+      <c r="J168" s="233"/>
+      <c r="K168" s="233"/>
+      <c r="L168" s="234"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="125" t="s">
@@ -22448,19 +22446,19 @@
       <c r="A175" s="143">
         <v>2</v>
       </c>
-      <c r="B175" s="202" t="s">
+      <c r="B175" s="235" t="s">
         <v>43</v>
       </c>
-      <c r="C175" s="203"/>
-      <c r="D175" s="203"/>
-      <c r="E175" s="203"/>
-      <c r="F175" s="203"/>
-      <c r="G175" s="203"/>
-      <c r="H175" s="203"/>
-      <c r="I175" s="203"/>
-      <c r="J175" s="203"/>
-      <c r="K175" s="203"/>
-      <c r="L175" s="204"/>
+      <c r="C175" s="236"/>
+      <c r="D175" s="236"/>
+      <c r="E175" s="236"/>
+      <c r="F175" s="236"/>
+      <c r="G175" s="236"/>
+      <c r="H175" s="236"/>
+      <c r="I175" s="236"/>
+      <c r="J175" s="236"/>
+      <c r="K175" s="236"/>
+      <c r="L175" s="237"/>
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A176" s="167">
@@ -22483,12 +22481,16 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="28">
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B158:L158"/>
+    <mergeCell ref="B168:L168"/>
+    <mergeCell ref="B175:L175"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A62:L63"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B140:D140"/>
+    <mergeCell ref="B146:L146"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="A28:L28"/>
@@ -22501,16 +22503,12 @@
     <mergeCell ref="B53:L53"/>
     <mergeCell ref="A55:L55"/>
     <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B148:L148"/>
-    <mergeCell ref="B158:L158"/>
-    <mergeCell ref="B168:L168"/>
-    <mergeCell ref="B175:L175"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="A62:L63"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="B146:L146"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23362,36 +23360,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-      <c r="L2" s="191"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -23412,36 +23410,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="192"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -23458,36 +23456,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="195"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="211"/>
+      <c r="K7" s="211"/>
+      <c r="L7" s="212"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="187" t="s">
+      <c r="A8" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="189"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="206"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -23531,7 +23529,7 @@
       <c r="A10" s="186">
         <v>1</v>
       </c>
-      <c r="B10" s="249">
+      <c r="B10" s="198">
         <v>4754</v>
       </c>
       <c r="C10" s="49"/>
@@ -23549,7 +23547,7 @@
       <c r="A11" s="186">
         <v>2</v>
       </c>
-      <c r="B11" s="237">
+      <c r="B11" s="187">
         <v>4756</v>
       </c>
       <c r="C11" s="53"/>
@@ -23567,7 +23565,7 @@
       <c r="A12" s="186">
         <v>3</v>
       </c>
-      <c r="B12" s="237">
+      <c r="B12" s="187">
         <v>4752</v>
       </c>
       <c r="C12" s="53"/>
@@ -23585,7 +23583,7 @@
       <c r="A13" s="186">
         <v>4</v>
       </c>
-      <c r="B13" s="237">
+      <c r="B13" s="187">
         <v>4749</v>
       </c>
       <c r="C13" s="53"/>
@@ -23603,7 +23601,7 @@
       <c r="A14" s="186">
         <v>5</v>
       </c>
-      <c r="B14" s="237">
+      <c r="B14" s="187">
         <v>4737</v>
       </c>
       <c r="C14" s="53"/>
@@ -23865,7 +23863,7 @@
       <c r="A15" s="186">
         <v>6</v>
       </c>
-      <c r="B15" s="237">
+      <c r="B15" s="187">
         <v>4746</v>
       </c>
       <c r="C15" s="53"/>
@@ -24127,7 +24125,7 @@
       <c r="A16" s="186">
         <v>7</v>
       </c>
-      <c r="B16" s="237">
+      <c r="B16" s="187">
         <v>4674</v>
       </c>
       <c r="C16" s="53"/>
@@ -24389,7 +24387,7 @@
       <c r="A17" s="186">
         <v>8</v>
       </c>
-      <c r="B17" s="237">
+      <c r="B17" s="187">
         <v>4693</v>
       </c>
       <c r="C17" s="53"/>
@@ -24651,7 +24649,7 @@
       <c r="A18" s="186">
         <v>9</v>
       </c>
-      <c r="B18" s="237">
+      <c r="B18" s="187">
         <v>4715</v>
       </c>
       <c r="C18" s="53"/>
@@ -24913,7 +24911,7 @@
       <c r="A19" s="186">
         <v>10</v>
       </c>
-      <c r="B19" s="237">
+      <c r="B19" s="187">
         <v>4716</v>
       </c>
       <c r="C19" s="53"/>
@@ -25175,7 +25173,7 @@
       <c r="A20" s="186">
         <v>11</v>
       </c>
-      <c r="B20" s="237">
+      <c r="B20" s="187">
         <v>4717</v>
       </c>
       <c r="C20" s="53"/>
@@ -25437,7 +25435,7 @@
       <c r="A21" s="186">
         <v>12</v>
       </c>
-      <c r="B21" s="237">
+      <c r="B21" s="187">
         <v>4718</v>
       </c>
       <c r="C21" s="53"/>
@@ -25699,7 +25697,7 @@
       <c r="A22" s="186">
         <v>13</v>
       </c>
-      <c r="B22" s="237">
+      <c r="B22" s="187">
         <v>4719</v>
       </c>
       <c r="C22" s="53"/>
@@ -25961,7 +25959,7 @@
       <c r="A23" s="186">
         <v>14</v>
       </c>
-      <c r="B23" s="237">
+      <c r="B23" s="187">
         <v>4720</v>
       </c>
       <c r="C23" s="53"/>
@@ -26223,7 +26221,7 @@
       <c r="A24" s="186">
         <v>15</v>
       </c>
-      <c r="B24" s="237">
+      <c r="B24" s="187">
         <v>4721</v>
       </c>
       <c r="C24" s="53"/>
@@ -26485,7 +26483,7 @@
       <c r="A25" s="186">
         <v>16</v>
       </c>
-      <c r="B25" s="237">
+      <c r="B25" s="187">
         <v>4722</v>
       </c>
       <c r="C25" s="53"/>
@@ -26747,7 +26745,7 @@
       <c r="A26" s="186">
         <v>17</v>
       </c>
-      <c r="B26" s="237">
+      <c r="B26" s="187">
         <v>4723</v>
       </c>
       <c r="C26" s="53"/>
@@ -27009,7 +27007,7 @@
       <c r="A27" s="186">
         <v>18</v>
       </c>
-      <c r="B27" s="237">
+      <c r="B27" s="187">
         <v>4724</v>
       </c>
       <c r="C27" s="53"/>
@@ -27271,7 +27269,7 @@
       <c r="A28" s="186">
         <v>19</v>
       </c>
-      <c r="B28" s="237">
+      <c r="B28" s="187">
         <v>4725</v>
       </c>
       <c r="C28" s="53"/>
@@ -27533,7 +27531,7 @@
       <c r="A29" s="186">
         <v>20</v>
       </c>
-      <c r="B29" s="237">
+      <c r="B29" s="187">
         <v>4726</v>
       </c>
       <c r="C29" s="53"/>
@@ -27792,23 +27790,23 @@
       <c r="IV29" s="39"/>
     </row>
     <row r="30" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="250">
+      <c r="A30" s="199">
         <f>COUNT(B10:B29)</f>
         <v>20</v>
       </c>
-      <c r="B30" s="215" t="s">
+      <c r="B30" s="214" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="216"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="216"/>
-      <c r="F30" s="216"/>
-      <c r="G30" s="216"/>
-      <c r="H30" s="216"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="216"/>
-      <c r="K30" s="216"/>
-      <c r="L30" s="217"/>
+      <c r="C30" s="215"/>
+      <c r="D30" s="215"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="215"/>
+      <c r="G30" s="215"/>
+      <c r="H30" s="215"/>
+      <c r="I30" s="215"/>
+      <c r="J30" s="215"/>
+      <c r="K30" s="215"/>
+      <c r="L30" s="216"/>
     </row>
     <row r="31" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A31" s="62"/>
@@ -27825,20 +27823,20 @@
       <c r="L31" s="63"/>
     </row>
     <row r="32" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="218" t="s">
+      <c r="A32" s="217" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="219"/>
-      <c r="C32" s="219"/>
-      <c r="D32" s="219"/>
-      <c r="E32" s="219"/>
-      <c r="F32" s="219"/>
-      <c r="G32" s="219"/>
-      <c r="H32" s="219"/>
-      <c r="I32" s="219"/>
-      <c r="J32" s="219"/>
-      <c r="K32" s="219"/>
-      <c r="L32" s="219"/>
+      <c r="B32" s="218"/>
+      <c r="C32" s="218"/>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="218"/>
+      <c r="H32" s="218"/>
+      <c r="I32" s="218"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="218"/>
+      <c r="L32" s="218"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
@@ -28491,23 +28489,23 @@
       <c r="L41" s="48"/>
     </row>
     <row r="42" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A42" s="251">
+      <c r="A42" s="200">
         <f>COUNT(B33:B41)</f>
         <v>4</v>
       </c>
-      <c r="B42" s="220" t="s">
+      <c r="B42" s="219" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="221"/>
-      <c r="I42" s="221"/>
-      <c r="J42" s="221"/>
-      <c r="K42" s="221"/>
-      <c r="L42" s="222"/>
+      <c r="C42" s="220"/>
+      <c r="D42" s="220"/>
+      <c r="E42" s="220"/>
+      <c r="F42" s="220"/>
+      <c r="G42" s="220"/>
+      <c r="H42" s="220"/>
+      <c r="I42" s="220"/>
+      <c r="J42" s="220"/>
+      <c r="K42" s="220"/>
+      <c r="L42" s="221"/>
     </row>
     <row r="43" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A43" s="71"/>
@@ -28524,26 +28522,26 @@
       <c r="L43" s="63"/>
     </row>
     <row r="44" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="223" t="s">
+      <c r="A44" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="223"/>
-      <c r="C44" s="223"/>
-      <c r="D44" s="223"/>
-      <c r="E44" s="223"/>
-      <c r="F44" s="223"/>
-      <c r="G44" s="223"/>
-      <c r="H44" s="223"/>
-      <c r="I44" s="223"/>
-      <c r="J44" s="223"/>
-      <c r="K44" s="223"/>
-      <c r="L44" s="223"/>
+      <c r="B44" s="222"/>
+      <c r="C44" s="222"/>
+      <c r="D44" s="222"/>
+      <c r="E44" s="222"/>
+      <c r="F44" s="222"/>
+      <c r="G44" s="222"/>
+      <c r="H44" s="222"/>
+      <c r="I44" s="222"/>
+      <c r="J44" s="222"/>
+      <c r="K44" s="222"/>
+      <c r="L44" s="222"/>
     </row>
     <row r="45" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="238">
+      <c r="A45" s="188">
         <v>1</v>
       </c>
-      <c r="B45" s="239" t="s">
+      <c r="B45" s="189" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="73"/>
@@ -28558,10 +28556,10 @@
       <c r="L45" s="72"/>
     </row>
     <row r="46" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="238">
+      <c r="A46" s="188">
         <v>2</v>
       </c>
-      <c r="B46" s="239" t="s">
+      <c r="B46" s="189" t="s">
         <v>71</v>
       </c>
       <c r="C46" s="73"/>
@@ -28576,10 +28574,10 @@
       <c r="L46" s="72"/>
     </row>
     <row r="47" spans="1:256" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="238">
+      <c r="A47" s="188">
         <v>3</v>
       </c>
-      <c r="B47" s="239" t="s">
+      <c r="B47" s="189" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="73"/>
@@ -28597,7 +28595,7 @@
       <c r="A48" s="89">
         <v>4</v>
       </c>
-      <c r="B48" s="240" t="s">
+      <c r="B48" s="190" t="s">
         <v>67</v>
       </c>
       <c r="C48" s="75"/>
@@ -28612,23 +28610,23 @@
       <c r="L48" s="79"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="252">
+      <c r="A49" s="201">
         <f>COUNT(A45:A48)</f>
         <v>4</v>
       </c>
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="224"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="224"/>
-      <c r="I49" s="224"/>
-      <c r="J49" s="224"/>
-      <c r="K49" s="224"/>
-      <c r="L49" s="225"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="223"/>
+      <c r="I49" s="223"/>
+      <c r="J49" s="223"/>
+      <c r="K49" s="223"/>
+      <c r="L49" s="224"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="81"/>
@@ -28645,20 +28643,20 @@
       <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="226" t="s">
+      <c r="A51" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="226"/>
-      <c r="C51" s="226"/>
-      <c r="D51" s="226"/>
-      <c r="E51" s="226"/>
-      <c r="F51" s="226"/>
-      <c r="G51" s="226"/>
-      <c r="H51" s="226"/>
-      <c r="I51" s="226"/>
-      <c r="J51" s="226"/>
-      <c r="K51" s="226"/>
-      <c r="L51" s="226"/>
+      <c r="B51" s="225"/>
+      <c r="C51" s="225"/>
+      <c r="D51" s="225"/>
+      <c r="E51" s="225"/>
+      <c r="F51" s="225"/>
+      <c r="G51" s="225"/>
+      <c r="H51" s="225"/>
+      <c r="I51" s="225"/>
+      <c r="J51" s="225"/>
+      <c r="K51" s="225"/>
+      <c r="L51" s="225"/>
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="84"/>
@@ -28692,19 +28690,19 @@
       <c r="A54" s="80">
         <v>0</v>
       </c>
-      <c r="B54" s="220" t="s">
+      <c r="B54" s="219" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="221"/>
-      <c r="D54" s="221"/>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="221"/>
-      <c r="I54" s="221"/>
-      <c r="J54" s="221"/>
-      <c r="K54" s="221"/>
-      <c r="L54" s="222"/>
+      <c r="C54" s="220"/>
+      <c r="D54" s="220"/>
+      <c r="E54" s="220"/>
+      <c r="F54" s="220"/>
+      <c r="G54" s="220"/>
+      <c r="H54" s="220"/>
+      <c r="I54" s="220"/>
+      <c r="J54" s="220"/>
+      <c r="K54" s="220"/>
+      <c r="L54" s="221"/>
     </row>
     <row r="55" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A55" s="71"/>
@@ -28721,20 +28719,20 @@
       <c r="L55" s="40"/>
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="226" t="s">
+      <c r="A56" s="225" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="226"/>
-      <c r="C56" s="226"/>
-      <c r="D56" s="226"/>
-      <c r="E56" s="226"/>
-      <c r="F56" s="226"/>
-      <c r="G56" s="226"/>
-      <c r="H56" s="226"/>
-      <c r="I56" s="226"/>
-      <c r="J56" s="226"/>
-      <c r="K56" s="226"/>
-      <c r="L56" s="226"/>
+      <c r="B56" s="225"/>
+      <c r="C56" s="225"/>
+      <c r="D56" s="225"/>
+      <c r="E56" s="225"/>
+      <c r="F56" s="225"/>
+      <c r="G56" s="225"/>
+      <c r="H56" s="225"/>
+      <c r="I56" s="225"/>
+      <c r="J56" s="225"/>
+      <c r="K56" s="225"/>
+      <c r="L56" s="225"/>
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="84"/>
@@ -28768,19 +28766,19 @@
       <c r="A59" s="80">
         <v>0</v>
       </c>
-      <c r="B59" s="220" t="s">
+      <c r="B59" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="221"/>
-      <c r="D59" s="221"/>
-      <c r="E59" s="221"/>
-      <c r="F59" s="221"/>
-      <c r="G59" s="221"/>
-      <c r="H59" s="221"/>
-      <c r="I59" s="221"/>
-      <c r="J59" s="221"/>
-      <c r="K59" s="221"/>
-      <c r="L59" s="222"/>
+      <c r="C59" s="220"/>
+      <c r="D59" s="220"/>
+      <c r="E59" s="220"/>
+      <c r="F59" s="220"/>
+      <c r="G59" s="220"/>
+      <c r="H59" s="220"/>
+      <c r="I59" s="220"/>
+      <c r="J59" s="220"/>
+      <c r="K59" s="220"/>
+      <c r="L59" s="221"/>
     </row>
     <row r="60" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A60" s="71"/>
@@ -28797,20 +28795,20 @@
       <c r="L60" s="40"/>
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="226" t="s">
+      <c r="A61" s="225" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="226"/>
-      <c r="C61" s="226"/>
-      <c r="D61" s="226"/>
-      <c r="E61" s="226"/>
-      <c r="F61" s="226"/>
-      <c r="G61" s="226"/>
-      <c r="H61" s="226"/>
-      <c r="I61" s="226"/>
-      <c r="J61" s="226"/>
-      <c r="K61" s="226"/>
-      <c r="L61" s="226"/>
+      <c r="B61" s="225"/>
+      <c r="C61" s="225"/>
+      <c r="D61" s="225"/>
+      <c r="E61" s="225"/>
+      <c r="F61" s="225"/>
+      <c r="G61" s="225"/>
+      <c r="H61" s="225"/>
+      <c r="I61" s="225"/>
+      <c r="J61" s="225"/>
+      <c r="K61" s="225"/>
+      <c r="L61" s="225"/>
     </row>
     <row r="62" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="90"/>
@@ -28844,19 +28842,19 @@
       <c r="A64" s="80">
         <v>0</v>
       </c>
-      <c r="B64" s="220" t="s">
+      <c r="B64" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="221"/>
-      <c r="D64" s="221"/>
-      <c r="E64" s="221"/>
-      <c r="F64" s="221"/>
-      <c r="G64" s="221"/>
-      <c r="H64" s="221"/>
-      <c r="I64" s="221"/>
-      <c r="J64" s="221"/>
-      <c r="K64" s="221"/>
-      <c r="L64" s="222"/>
+      <c r="C64" s="220"/>
+      <c r="D64" s="220"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
+      <c r="G64" s="220"/>
+      <c r="H64" s="220"/>
+      <c r="I64" s="220"/>
+      <c r="J64" s="220"/>
+      <c r="K64" s="220"/>
+      <c r="L64" s="221"/>
     </row>
     <row r="65" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A65" s="71"/>
@@ -28873,14 +28871,14 @@
       <c r="L65" s="63"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A66" s="253">
+      <c r="A66" s="202">
         <f>A42+A49+A54+A59+A64</f>
         <v>8</v>
       </c>
-      <c r="B66" s="205" t="s">
+      <c r="B66" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="205"/>
+      <c r="C66" s="213"/>
       <c r="D66" s="94" t="s">
         <v>30</v>
       </c>
@@ -28894,14 +28892,14 @@
       <c r="L66" s="96"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="253">
+      <c r="A67" s="202">
         <f>A30+A66</f>
         <v>28</v>
       </c>
-      <c r="B67" s="205" t="s">
+      <c r="B67" s="213" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="205"/>
+      <c r="C67" s="213"/>
       <c r="D67" s="94"/>
       <c r="E67" s="95"/>
       <c r="F67" s="95"/>
@@ -28913,55 +28911,55 @@
       <c r="L67" s="96"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="206"/>
-      <c r="B68" s="207"/>
-      <c r="C68" s="207"/>
-      <c r="D68" s="207"/>
-      <c r="E68" s="207"/>
-      <c r="F68" s="207"/>
-      <c r="G68" s="207"/>
-      <c r="H68" s="207"/>
-      <c r="I68" s="207"/>
-      <c r="J68" s="207"/>
-      <c r="K68" s="207"/>
-      <c r="L68" s="208"/>
+      <c r="A68" s="226"/>
+      <c r="B68" s="227"/>
+      <c r="C68" s="227"/>
+      <c r="D68" s="227"/>
+      <c r="E68" s="227"/>
+      <c r="F68" s="227"/>
+      <c r="G68" s="227"/>
+      <c r="H68" s="227"/>
+      <c r="I68" s="227"/>
+      <c r="J68" s="227"/>
+      <c r="K68" s="227"/>
+      <c r="L68" s="228"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="209"/>
-      <c r="B69" s="210"/>
-      <c r="C69" s="210"/>
-      <c r="D69" s="210"/>
-      <c r="E69" s="210"/>
-      <c r="F69" s="210"/>
-      <c r="G69" s="210"/>
-      <c r="H69" s="210"/>
-      <c r="I69" s="210"/>
-      <c r="J69" s="210"/>
-      <c r="K69" s="210"/>
-      <c r="L69" s="211"/>
+      <c r="A69" s="229"/>
+      <c r="B69" s="230"/>
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
+      <c r="I69" s="230"/>
+      <c r="J69" s="230"/>
+      <c r="K69" s="230"/>
+      <c r="L69" s="231"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="212" t="s">
+      <c r="A70" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="212"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
-      <c r="F70" s="212"/>
-      <c r="G70" s="212"/>
-      <c r="H70" s="212"/>
-      <c r="I70" s="212"/>
-      <c r="J70" s="212"/>
-      <c r="K70" s="212"/>
-      <c r="L70" s="212"/>
+      <c r="B70" s="238"/>
+      <c r="C70" s="238"/>
+      <c r="D70" s="238"/>
+      <c r="E70" s="238"/>
+      <c r="F70" s="238"/>
+      <c r="G70" s="238"/>
+      <c r="H70" s="238"/>
+      <c r="I70" s="238"/>
+      <c r="J70" s="238"/>
+      <c r="K70" s="238"/>
+      <c r="L70" s="238"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
+      <c r="B71" s="239"/>
+      <c r="C71" s="239"/>
       <c r="D71" s="97"/>
       <c r="E71" s="97"/>
       <c r="F71" s="97"/>
@@ -28973,14 +28971,14 @@
       <c r="L71" s="98"/>
     </row>
     <row r="72" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="244"/>
-      <c r="B72" s="245" t="s">
+      <c r="A72" s="194"/>
+      <c r="B72" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="246" t="s">
+      <c r="C72" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="246" t="s">
+      <c r="D72" s="196" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="46" t="s">
@@ -28989,7 +28987,9 @@
       <c r="F72" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="46"/>
+      <c r="G72" s="46" t="s">
+        <v>13</v>
+      </c>
       <c r="H72" s="46" t="s">
         <v>14</v>
       </c>
@@ -29008,18 +29008,18 @@
     </row>
     <row r="73" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A73" s="47"/>
-      <c r="B73" s="48">
+      <c r="B73" s="258">
         <v>4568</v>
       </c>
       <c r="C73" s="49"/>
       <c r="D73" s="49"/>
       <c r="E73" s="51"/>
       <c r="F73" s="51"/>
-      <c r="G73" s="248"/>
-      <c r="H73" s="248"/>
-      <c r="I73" s="248"/>
+      <c r="G73" s="197"/>
+      <c r="H73" s="197"/>
+      <c r="I73" s="197"/>
       <c r="J73" s="48"/>
-      <c r="K73" s="248"/>
+      <c r="K73" s="197"/>
       <c r="L73" s="48"/>
     </row>
     <row r="74" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
@@ -29031,11 +29031,11 @@
       <c r="D74" s="49"/>
       <c r="E74" s="51"/>
       <c r="F74" s="51"/>
-      <c r="G74" s="248"/>
-      <c r="H74" s="248"/>
-      <c r="I74" s="248"/>
+      <c r="G74" s="197"/>
+      <c r="H74" s="197"/>
+      <c r="I74" s="197"/>
       <c r="J74" s="48"/>
-      <c r="K74" s="248"/>
+      <c r="K74" s="197"/>
       <c r="L74" s="48"/>
     </row>
     <row r="75" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
@@ -29047,9 +29047,9 @@
       <c r="D75" s="49"/>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
-      <c r="G75" s="248"/>
-      <c r="H75" s="248"/>
-      <c r="I75" s="248"/>
+      <c r="G75" s="197"/>
+      <c r="H75" s="197"/>
+      <c r="I75" s="197"/>
       <c r="J75" s="48"/>
       <c r="K75" s="51"/>
       <c r="L75" s="48"/>
@@ -29063,10 +29063,10 @@
       <c r="D76" s="49"/>
       <c r="E76" s="51"/>
       <c r="F76" s="51"/>
-      <c r="G76" s="248"/>
-      <c r="H76" s="248"/>
-      <c r="I76" s="248"/>
-      <c r="J76" s="248"/>
+      <c r="G76" s="197"/>
+      <c r="H76" s="197"/>
+      <c r="I76" s="197"/>
+      <c r="J76" s="197"/>
       <c r="K76" s="51"/>
       <c r="L76" s="48"/>
     </row>
@@ -29079,10 +29079,10 @@
       <c r="D77" s="49"/>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
-      <c r="G77" s="248"/>
-      <c r="H77" s="248"/>
-      <c r="I77" s="248"/>
-      <c r="J77" s="248"/>
+      <c r="G77" s="197"/>
+      <c r="H77" s="197"/>
+      <c r="I77" s="197"/>
+      <c r="J77" s="197"/>
       <c r="K77" s="51"/>
       <c r="L77" s="48"/>
     </row>
@@ -29095,9 +29095,9 @@
       <c r="D78" s="49"/>
       <c r="E78" s="50"/>
       <c r="F78" s="51"/>
-      <c r="G78" s="248"/>
-      <c r="H78" s="248"/>
-      <c r="I78" s="248"/>
+      <c r="G78" s="197"/>
+      <c r="H78" s="197"/>
+      <c r="I78" s="197"/>
       <c r="J78" s="48"/>
       <c r="K78" s="51"/>
       <c r="L78" s="48"/>
@@ -29114,7 +29114,7 @@
       <c r="G79" s="51"/>
       <c r="H79" s="51"/>
       <c r="I79" s="51"/>
-      <c r="J79" s="248"/>
+      <c r="J79" s="197"/>
       <c r="K79" s="51"/>
       <c r="L79" s="48"/>
     </row>
@@ -29395,11 +29395,11 @@
         <f>COUNT(B73:B96)</f>
         <v>24</v>
       </c>
-      <c r="B97" s="247" t="s">
+      <c r="B97" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="247"/>
-      <c r="D97" s="247"/>
+      <c r="C97" s="240"/>
+      <c r="D97" s="240"/>
       <c r="E97" s="93"/>
       <c r="F97" s="93"/>
       <c r="G97" s="93"/>
@@ -29424,20 +29424,20 @@
       <c r="L98" s="96"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A99" s="241" t="s">
+      <c r="A99" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="242"/>
-      <c r="C99" s="242"/>
-      <c r="D99" s="242"/>
-      <c r="E99" s="242"/>
-      <c r="F99" s="242"/>
-      <c r="G99" s="242"/>
-      <c r="H99" s="242"/>
-      <c r="I99" s="242"/>
-      <c r="J99" s="242"/>
-      <c r="K99" s="242"/>
-      <c r="L99" s="243"/>
+      <c r="B99" s="192"/>
+      <c r="C99" s="192"/>
+      <c r="D99" s="192"/>
+      <c r="E99" s="192"/>
+      <c r="F99" s="192"/>
+      <c r="G99" s="192"/>
+      <c r="H99" s="192"/>
+      <c r="I99" s="192"/>
+      <c r="J99" s="192"/>
+      <c r="K99" s="192"/>
+      <c r="L99" s="193"/>
     </row>
     <row r="100" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A100" s="89"/>
@@ -29536,23 +29536,23 @@
       <c r="L105" s="48"/>
     </row>
     <row r="106" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A106" s="252">
+      <c r="A106" s="201">
         <f>COUNT(B100:B105)</f>
         <v>6</v>
       </c>
-      <c r="B106" s="254" t="s">
+      <c r="B106" s="241" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="254"/>
-      <c r="D106" s="254"/>
-      <c r="E106" s="254"/>
-      <c r="F106" s="254"/>
-      <c r="G106" s="254"/>
-      <c r="H106" s="254"/>
-      <c r="I106" s="254"/>
-      <c r="J106" s="254"/>
-      <c r="K106" s="254"/>
-      <c r="L106" s="254"/>
+      <c r="C106" s="241"/>
+      <c r="D106" s="241"/>
+      <c r="E106" s="241"/>
+      <c r="F106" s="241"/>
+      <c r="G106" s="241"/>
+      <c r="H106" s="241"/>
+      <c r="I106" s="241"/>
+      <c r="J106" s="241"/>
+      <c r="K106" s="241"/>
+      <c r="L106" s="241"/>
     </row>
     <row r="107" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A107" s="39"/>
@@ -29570,23 +29570,23 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="69"/>
-      <c r="B108" s="256" t="s">
+      <c r="B108" s="242" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="256"/>
-      <c r="D108" s="256"/>
-      <c r="E108" s="256"/>
-      <c r="F108" s="256"/>
-      <c r="G108" s="256"/>
-      <c r="H108" s="256"/>
-      <c r="I108" s="256"/>
-      <c r="J108" s="256"/>
-      <c r="K108" s="256"/>
-      <c r="L108" s="256"/>
+      <c r="C108" s="242"/>
+      <c r="D108" s="242"/>
+      <c r="E108" s="242"/>
+      <c r="F108" s="242"/>
+      <c r="G108" s="242"/>
+      <c r="H108" s="242"/>
+      <c r="I108" s="242"/>
+      <c r="J108" s="242"/>
+      <c r="K108" s="242"/>
+      <c r="L108" s="242"/>
     </row>
     <row r="109" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A109" s="89"/>
-      <c r="B109" s="257" t="s">
+      <c r="B109" s="203" t="s">
         <v>76</v>
       </c>
       <c r="C109" s="68"/>
@@ -29602,7 +29602,7 @@
     </row>
     <row r="110" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A110" s="89"/>
-      <c r="B110" s="257" t="s">
+      <c r="B110" s="203" t="s">
         <v>65</v>
       </c>
       <c r="C110" s="68"/>
@@ -29618,7 +29618,7 @@
     </row>
     <row r="111" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A111" s="89"/>
-      <c r="B111" s="257" t="s">
+      <c r="B111" s="203" t="s">
         <v>66</v>
       </c>
       <c r="C111" s="56"/>
@@ -29634,7 +29634,7 @@
     </row>
     <row r="112" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A112" s="89"/>
-      <c r="B112" s="257" t="s">
+      <c r="B112" s="203" t="s">
         <v>68</v>
       </c>
       <c r="C112" s="56"/>
@@ -29650,7 +29650,7 @@
     </row>
     <row r="113" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A113" s="89"/>
-      <c r="B113" s="257" t="s">
+      <c r="B113" s="203" t="s">
         <v>77</v>
       </c>
       <c r="C113" s="56"/>
@@ -29666,7 +29666,7 @@
     </row>
     <row r="114" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A114" s="89"/>
-      <c r="B114" s="257" t="s">
+      <c r="B114" s="203" t="s">
         <v>69</v>
       </c>
       <c r="C114" s="56"/>
@@ -29682,7 +29682,7 @@
     </row>
     <row r="115" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A115" s="89"/>
-      <c r="B115" s="257" t="s">
+      <c r="B115" s="203" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="56"/>
@@ -29697,42 +29697,42 @@
       <c r="L115" s="48"/>
     </row>
     <row r="116" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A116" s="252">
+      <c r="A116" s="201">
         <f>COUNTA(B109:B115)</f>
         <v>7</v>
       </c>
-      <c r="B116" s="254" t="s">
+      <c r="B116" s="241" t="s">
         <v>37</v>
       </c>
-      <c r="C116" s="254"/>
-      <c r="D116" s="254"/>
-      <c r="E116" s="254"/>
-      <c r="F116" s="254"/>
-      <c r="G116" s="254"/>
-      <c r="H116" s="254"/>
-      <c r="I116" s="254"/>
-      <c r="J116" s="254"/>
-      <c r="K116" s="254"/>
-      <c r="L116" s="254"/>
-    </row>
-    <row r="117" spans="1:12" s="255" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A117" s="252">
+      <c r="C116" s="241"/>
+      <c r="D116" s="241"/>
+      <c r="E116" s="241"/>
+      <c r="F116" s="241"/>
+      <c r="G116" s="241"/>
+      <c r="H116" s="241"/>
+      <c r="I116" s="241"/>
+      <c r="J116" s="241"/>
+      <c r="K116" s="241"/>
+      <c r="L116" s="241"/>
+    </row>
+    <row r="117" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A117" s="201">
         <f>A116+A106</f>
         <v>13</v>
       </c>
-      <c r="B117" s="258" t="s">
+      <c r="B117" s="243" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="258"/>
-      <c r="D117" s="258"/>
-      <c r="E117" s="258"/>
-      <c r="F117" s="258"/>
-      <c r="G117" s="258"/>
-      <c r="H117" s="258"/>
-      <c r="I117" s="258"/>
-      <c r="J117" s="258"/>
-      <c r="K117" s="258"/>
-      <c r="L117" s="258"/>
+      <c r="C117" s="243"/>
+      <c r="D117" s="243"/>
+      <c r="E117" s="243"/>
+      <c r="F117" s="243"/>
+      <c r="G117" s="243"/>
+      <c r="H117" s="243"/>
+      <c r="I117" s="243"/>
+      <c r="J117" s="243"/>
+      <c r="K117" s="243"/>
+      <c r="L117" s="243"/>
     </row>
     <row r="118" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A118" s="39"/>
@@ -29838,19 +29838,19 @@
       <c r="A125" s="61">
         <v>4</v>
       </c>
-      <c r="B125" s="199" t="s">
+      <c r="B125" s="232" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="200"/>
-      <c r="D125" s="200"/>
-      <c r="E125" s="200"/>
-      <c r="F125" s="200"/>
-      <c r="G125" s="200"/>
-      <c r="H125" s="200"/>
-      <c r="I125" s="200"/>
-      <c r="J125" s="200"/>
-      <c r="K125" s="200"/>
-      <c r="L125" s="201"/>
+      <c r="C125" s="233"/>
+      <c r="D125" s="233"/>
+      <c r="E125" s="233"/>
+      <c r="F125" s="233"/>
+      <c r="G125" s="233"/>
+      <c r="H125" s="233"/>
+      <c r="I125" s="233"/>
+      <c r="J125" s="233"/>
+      <c r="K125" s="233"/>
+      <c r="L125" s="234"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="125" t="s">
@@ -29944,19 +29944,19 @@
       <c r="A132" s="143">
         <v>0</v>
       </c>
-      <c r="B132" s="202" t="s">
+      <c r="B132" s="235" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="203"/>
-      <c r="D132" s="203"/>
-      <c r="E132" s="203"/>
-      <c r="F132" s="203"/>
-      <c r="G132" s="203"/>
-      <c r="H132" s="203"/>
-      <c r="I132" s="203"/>
-      <c r="J132" s="203"/>
-      <c r="K132" s="203"/>
-      <c r="L132" s="204"/>
+      <c r="C132" s="236"/>
+      <c r="D132" s="236"/>
+      <c r="E132" s="236"/>
+      <c r="F132" s="236"/>
+      <c r="G132" s="236"/>
+      <c r="H132" s="236"/>
+      <c r="I132" s="236"/>
+      <c r="J132" s="236"/>
+      <c r="K132" s="236"/>
+      <c r="L132" s="237"/>
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="167">
@@ -29980,12 +29980,16 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="29">
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A68:L69"/>
+    <mergeCell ref="B125:L125"/>
+    <mergeCell ref="B132:L132"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B106:L106"/>
+    <mergeCell ref="B108:L108"/>
+    <mergeCell ref="B116:L116"/>
+    <mergeCell ref="B117:L117"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B30:L30"/>
     <mergeCell ref="A32:L32"/>
@@ -29999,16 +30003,12 @@
     <mergeCell ref="B54:L54"/>
     <mergeCell ref="B59:L59"/>
     <mergeCell ref="B64:L64"/>
-    <mergeCell ref="A68:L69"/>
-    <mergeCell ref="B125:L125"/>
-    <mergeCell ref="B132:L132"/>
-    <mergeCell ref="A70:L70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B106:L106"/>
-    <mergeCell ref="B108:L108"/>
-    <mergeCell ref="B116:L116"/>
-    <mergeCell ref="B117:L117"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -30086,75 +30086,75 @@
       <c r="A2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="227" t="s">
+      <c r="B2" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="227"/>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="227"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="M2" s="227"/>
+      <c r="C2" s="256"/>
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="256"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="M2" s="256"/>
     </row>
     <row r="3" spans="1:13" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="227" t="s">
+      <c r="B3" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="227"/>
-      <c r="D3" s="227"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="227"/>
-      <c r="H3" s="227"/>
-      <c r="I3" s="227"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="M3" s="227"/>
+      <c r="C3" s="256"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="M3" s="256"/>
     </row>
     <row r="4" spans="1:13" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="227"/>
-      <c r="D4" s="227"/>
-      <c r="E4" s="227"/>
-      <c r="F4" s="227"/>
-      <c r="G4" s="227"/>
-      <c r="H4" s="227"/>
-      <c r="I4" s="227"/>
-      <c r="J4" s="227"/>
-      <c r="K4" s="227"/>
-      <c r="L4" s="227"/>
-      <c r="M4" s="227"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="256"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
+      <c r="M4" s="256"/>
     </row>
     <row r="5" spans="1:13" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34"/>
-      <c r="B5" s="228" t="s">
+      <c r="B5" s="257" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="228"/>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
-      <c r="F5" s="228"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="228"/>
-      <c r="J5" s="228"/>
-      <c r="K5" s="228"/>
-      <c r="L5" s="228"/>
-      <c r="M5" s="228"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="M5" s="257"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="33"/>
@@ -30220,54 +30220,54 @@
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
-      <c r="B10" s="229" t="s">
+      <c r="B10" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="229"/>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="229"/>
-      <c r="I10" s="229"/>
-      <c r="J10" s="229"/>
-      <c r="K10" s="229"/>
-      <c r="L10" s="229"/>
-      <c r="M10" s="229"/>
+      <c r="C10" s="248"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="248"/>
+      <c r="K10" s="248"/>
+      <c r="L10" s="248"/>
+      <c r="M10" s="248"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="229" t="s">
+      <c r="A11" s="248" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="229"/>
-      <c r="C11" s="229"/>
-      <c r="D11" s="229"/>
-      <c r="E11" s="229"/>
-      <c r="F11" s="229"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="229"/>
-      <c r="I11" s="229"/>
-      <c r="J11" s="229"/>
-      <c r="K11" s="229"/>
-      <c r="L11" s="229"/>
-      <c r="M11" s="229"/>
+      <c r="B11" s="248"/>
+      <c r="C11" s="248"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
+      <c r="M11" s="248"/>
     </row>
     <row r="12" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="229" t="s">
+      <c r="A12" s="248" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="229"/>
-      <c r="C12" s="229"/>
-      <c r="D12" s="229"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
-      <c r="K12" s="229"/>
-      <c r="L12" s="229"/>
-      <c r="M12" s="229"/>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
+      <c r="M12" s="248"/>
     </row>
     <row r="13" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
@@ -30347,38 +30347,38 @@
     <row r="18" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="233"/>
+      <c r="D18" s="252"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="233" t="s">
+      <c r="I18" s="252" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
+      <c r="J18" s="252"/>
+      <c r="K18" s="252"/>
       <c r="L18" s="12"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="234" t="s">
+      <c r="C19" s="253" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="234"/>
+      <c r="D19" s="253"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="235" t="s">
+      <c r="I19" s="254" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="235"/>
-      <c r="K19" s="235"/>
+      <c r="J19" s="254"/>
+      <c r="K19" s="254"/>
       <c r="L19" s="4"/>
       <c r="M19" s="3"/>
     </row>
@@ -30386,13 +30386,13 @@
       <c r="B20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="236"/>
-      <c r="D20" s="236"/>
+      <c r="C20" s="255"/>
+      <c r="D20" s="255"/>
       <c r="I20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J20" s="236"/>
-      <c r="K20" s="236"/>
+      <c r="J20" s="255"/>
+      <c r="K20" s="255"/>
     </row>
     <row r="24" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
@@ -30506,12 +30506,12 @@
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="230" t="s">
+      <c r="E31" s="249" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="230"/>
-      <c r="G31" s="230"/>
-      <c r="H31" s="230"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="6"/>
@@ -30523,12 +30523,12 @@
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="231" t="s">
+      <c r="E32" s="250" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="231"/>
-      <c r="G32" s="231"/>
-      <c r="H32" s="231"/>
+      <c r="F32" s="250"/>
+      <c r="G32" s="250"/>
+      <c r="H32" s="250"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="6"/>
@@ -30540,12 +30540,12 @@
       <c r="B33" s="9"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="232" t="s">
+      <c r="E33" s="251" t="s">
         <v>45</v>
       </c>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="6"/>
@@ -30555,6 +30555,11 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="16">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
@@ -30566,11 +30571,6 @@
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B10:M10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="1" bottom="0.25" header="0.51180555555555551" footer="0.51180555555555551"/>

--- a/app/static/base_docs/DI July to December 2025.xlsx
+++ b/app/static/base_docs/DI July to December 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\base_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F47E12-056A-4369-B327-9565F7B38B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8381B120-173B-4C9E-8D6F-96E4D9C3221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9AC113C8-2A50-914F-A515-7C5B30E77858}"/>
   </bookViews>
@@ -1993,83 +1993,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2143,6 +2067,86 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2154,6 +2158,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2184,16 +2194,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -3407,36 +3407,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -3457,36 +3457,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -3503,36 +3503,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="211"/>
-      <c r="L7" s="212"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="244"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="206"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="238"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -7841,19 +7841,19 @@
         <f>COUNT(B10:B29)</f>
         <v>20</v>
       </c>
-      <c r="B30" s="214" t="s">
+      <c r="B30" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="215"/>
-      <c r="J30" s="215"/>
-      <c r="K30" s="215"/>
-      <c r="L30" s="216"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="226"/>
     </row>
     <row r="31" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A31" s="62"/>
@@ -7870,20 +7870,20 @@
       <c r="L31" s="63"/>
     </row>
     <row r="32" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="217" t="s">
+      <c r="A32" s="227" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="218"/>
-      <c r="C32" s="218"/>
-      <c r="D32" s="218"/>
-      <c r="E32" s="218"/>
-      <c r="F32" s="218"/>
-      <c r="G32" s="218"/>
-      <c r="H32" s="218"/>
-      <c r="I32" s="218"/>
-      <c r="J32" s="218"/>
-      <c r="K32" s="218"/>
-      <c r="L32" s="218"/>
+      <c r="B32" s="228"/>
+      <c r="C32" s="228"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="228"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="228"/>
+      <c r="I32" s="228"/>
+      <c r="J32" s="228"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
@@ -8540,19 +8540,19 @@
         <f>COUNT(B33:B41)</f>
         <v>4</v>
       </c>
-      <c r="B42" s="219" t="s">
+      <c r="B42" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="220"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="220"/>
-      <c r="I42" s="220"/>
-      <c r="J42" s="220"/>
-      <c r="K42" s="220"/>
-      <c r="L42" s="221"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="230"/>
+      <c r="J42" s="230"/>
+      <c r="K42" s="230"/>
+      <c r="L42" s="231"/>
     </row>
     <row r="43" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A43" s="71"/>
@@ -8569,20 +8569,20 @@
       <c r="L43" s="63"/>
     </row>
     <row r="44" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="222" t="s">
+      <c r="A44" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="222"/>
-      <c r="C44" s="222"/>
-      <c r="D44" s="222"/>
-      <c r="E44" s="222"/>
-      <c r="F44" s="222"/>
-      <c r="G44" s="222"/>
-      <c r="H44" s="222"/>
-      <c r="I44" s="222"/>
-      <c r="J44" s="222"/>
-      <c r="K44" s="222"/>
-      <c r="L44" s="222"/>
+      <c r="B44" s="232"/>
+      <c r="C44" s="232"/>
+      <c r="D44" s="232"/>
+      <c r="E44" s="232"/>
+      <c r="F44" s="232"/>
+      <c r="G44" s="232"/>
+      <c r="H44" s="232"/>
+      <c r="I44" s="232"/>
+      <c r="J44" s="232"/>
+      <c r="K44" s="232"/>
+      <c r="L44" s="232"/>
     </row>
     <row r="45" spans="1:256" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="188">
@@ -8661,19 +8661,19 @@
         <f>COUNT(A45:A48)</f>
         <v>4</v>
       </c>
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="233" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="223"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="223"/>
-      <c r="F49" s="223"/>
-      <c r="G49" s="223"/>
-      <c r="H49" s="223"/>
-      <c r="I49" s="223"/>
-      <c r="J49" s="223"/>
-      <c r="K49" s="223"/>
-      <c r="L49" s="224"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
+      <c r="I49" s="233"/>
+      <c r="J49" s="233"/>
+      <c r="K49" s="233"/>
+      <c r="L49" s="234"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="81"/>
@@ -8690,20 +8690,20 @@
       <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="225" t="s">
+      <c r="A51" s="235" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="225"/>
-      <c r="C51" s="225"/>
-      <c r="D51" s="225"/>
-      <c r="E51" s="225"/>
-      <c r="F51" s="225"/>
-      <c r="G51" s="225"/>
-      <c r="H51" s="225"/>
-      <c r="I51" s="225"/>
-      <c r="J51" s="225"/>
-      <c r="K51" s="225"/>
-      <c r="L51" s="225"/>
+      <c r="B51" s="235"/>
+      <c r="C51" s="235"/>
+      <c r="D51" s="235"/>
+      <c r="E51" s="235"/>
+      <c r="F51" s="235"/>
+      <c r="G51" s="235"/>
+      <c r="H51" s="235"/>
+      <c r="I51" s="235"/>
+      <c r="J51" s="235"/>
+      <c r="K51" s="235"/>
+      <c r="L51" s="235"/>
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="84"/>
@@ -8737,19 +8737,19 @@
       <c r="A54" s="80">
         <v>0</v>
       </c>
-      <c r="B54" s="219" t="s">
+      <c r="B54" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="220"/>
-      <c r="D54" s="220"/>
-      <c r="E54" s="220"/>
-      <c r="F54" s="220"/>
-      <c r="G54" s="220"/>
-      <c r="H54" s="220"/>
-      <c r="I54" s="220"/>
-      <c r="J54" s="220"/>
-      <c r="K54" s="220"/>
-      <c r="L54" s="221"/>
+      <c r="C54" s="230"/>
+      <c r="D54" s="230"/>
+      <c r="E54" s="230"/>
+      <c r="F54" s="230"/>
+      <c r="G54" s="230"/>
+      <c r="H54" s="230"/>
+      <c r="I54" s="230"/>
+      <c r="J54" s="230"/>
+      <c r="K54" s="230"/>
+      <c r="L54" s="231"/>
     </row>
     <row r="55" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A55" s="71"/>
@@ -8766,20 +8766,20 @@
       <c r="L55" s="40"/>
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="225" t="s">
+      <c r="A56" s="235" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="225"/>
-      <c r="C56" s="225"/>
-      <c r="D56" s="225"/>
-      <c r="E56" s="225"/>
-      <c r="F56" s="225"/>
-      <c r="G56" s="225"/>
-      <c r="H56" s="225"/>
-      <c r="I56" s="225"/>
-      <c r="J56" s="225"/>
-      <c r="K56" s="225"/>
-      <c r="L56" s="225"/>
+      <c r="B56" s="235"/>
+      <c r="C56" s="235"/>
+      <c r="D56" s="235"/>
+      <c r="E56" s="235"/>
+      <c r="F56" s="235"/>
+      <c r="G56" s="235"/>
+      <c r="H56" s="235"/>
+      <c r="I56" s="235"/>
+      <c r="J56" s="235"/>
+      <c r="K56" s="235"/>
+      <c r="L56" s="235"/>
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="84"/>
@@ -8813,19 +8813,19 @@
       <c r="A59" s="80">
         <v>0</v>
       </c>
-      <c r="B59" s="219" t="s">
+      <c r="B59" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="220"/>
-      <c r="D59" s="220"/>
-      <c r="E59" s="220"/>
-      <c r="F59" s="220"/>
-      <c r="G59" s="220"/>
-      <c r="H59" s="220"/>
-      <c r="I59" s="220"/>
-      <c r="J59" s="220"/>
-      <c r="K59" s="220"/>
-      <c r="L59" s="221"/>
+      <c r="C59" s="230"/>
+      <c r="D59" s="230"/>
+      <c r="E59" s="230"/>
+      <c r="F59" s="230"/>
+      <c r="G59" s="230"/>
+      <c r="H59" s="230"/>
+      <c r="I59" s="230"/>
+      <c r="J59" s="230"/>
+      <c r="K59" s="230"/>
+      <c r="L59" s="231"/>
     </row>
     <row r="60" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A60" s="71"/>
@@ -8842,20 +8842,20 @@
       <c r="L60" s="40"/>
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="225" t="s">
+      <c r="A61" s="235" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="225"/>
-      <c r="C61" s="225"/>
-      <c r="D61" s="225"/>
-      <c r="E61" s="225"/>
-      <c r="F61" s="225"/>
-      <c r="G61" s="225"/>
-      <c r="H61" s="225"/>
-      <c r="I61" s="225"/>
-      <c r="J61" s="225"/>
-      <c r="K61" s="225"/>
-      <c r="L61" s="225"/>
+      <c r="B61" s="235"/>
+      <c r="C61" s="235"/>
+      <c r="D61" s="235"/>
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="235"/>
+      <c r="H61" s="235"/>
+      <c r="I61" s="235"/>
+      <c r="J61" s="235"/>
+      <c r="K61" s="235"/>
+      <c r="L61" s="235"/>
     </row>
     <row r="62" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="90"/>
@@ -8889,19 +8889,19 @@
       <c r="A64" s="80">
         <v>0</v>
       </c>
-      <c r="B64" s="219" t="s">
+      <c r="B64" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="220"/>
-      <c r="D64" s="220"/>
-      <c r="E64" s="220"/>
-      <c r="F64" s="220"/>
-      <c r="G64" s="220"/>
-      <c r="H64" s="220"/>
-      <c r="I64" s="220"/>
-      <c r="J64" s="220"/>
-      <c r="K64" s="220"/>
-      <c r="L64" s="221"/>
+      <c r="C64" s="230"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="230"/>
+      <c r="G64" s="230"/>
+      <c r="H64" s="230"/>
+      <c r="I64" s="230"/>
+      <c r="J64" s="230"/>
+      <c r="K64" s="230"/>
+      <c r="L64" s="231"/>
     </row>
     <row r="65" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A65" s="71"/>
@@ -8922,10 +8922,10 @@
         <f>A42+A49+A54+A59+A64</f>
         <v>8</v>
       </c>
-      <c r="B66" s="213" t="s">
+      <c r="B66" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="213"/>
+      <c r="C66" s="223"/>
       <c r="D66" s="94" t="s">
         <v>30</v>
       </c>
@@ -8943,10 +8943,10 @@
         <f>A30+A66</f>
         <v>28</v>
       </c>
-      <c r="B67" s="213" t="s">
+      <c r="B67" s="223" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="213"/>
+      <c r="C67" s="223"/>
       <c r="D67" s="94"/>
       <c r="E67" s="95"/>
       <c r="F67" s="95"/>
@@ -8958,55 +8958,55 @@
       <c r="L67" s="96"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="226"/>
-      <c r="B68" s="227"/>
-      <c r="C68" s="227"/>
-      <c r="D68" s="227"/>
-      <c r="E68" s="227"/>
-      <c r="F68" s="227"/>
-      <c r="G68" s="227"/>
-      <c r="H68" s="227"/>
-      <c r="I68" s="227"/>
-      <c r="J68" s="227"/>
-      <c r="K68" s="227"/>
-      <c r="L68" s="228"/>
+      <c r="A68" s="205"/>
+      <c r="B68" s="206"/>
+      <c r="C68" s="206"/>
+      <c r="D68" s="206"/>
+      <c r="E68" s="206"/>
+      <c r="F68" s="206"/>
+      <c r="G68" s="206"/>
+      <c r="H68" s="206"/>
+      <c r="I68" s="206"/>
+      <c r="J68" s="206"/>
+      <c r="K68" s="206"/>
+      <c r="L68" s="207"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="229"/>
-      <c r="B69" s="230"/>
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
-      <c r="I69" s="230"/>
-      <c r="J69" s="230"/>
-      <c r="K69" s="230"/>
-      <c r="L69" s="231"/>
+      <c r="A69" s="208"/>
+      <c r="B69" s="209"/>
+      <c r="C69" s="209"/>
+      <c r="D69" s="209"/>
+      <c r="E69" s="209"/>
+      <c r="F69" s="209"/>
+      <c r="G69" s="209"/>
+      <c r="H69" s="209"/>
+      <c r="I69" s="209"/>
+      <c r="J69" s="209"/>
+      <c r="K69" s="209"/>
+      <c r="L69" s="210"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="238" t="s">
+      <c r="A70" s="217" t="s">
         <v>32</v>
       </c>
-      <c r="B70" s="238"/>
-      <c r="C70" s="238"/>
-      <c r="D70" s="238"/>
-      <c r="E70" s="238"/>
-      <c r="F70" s="238"/>
-      <c r="G70" s="238"/>
-      <c r="H70" s="238"/>
-      <c r="I70" s="238"/>
-      <c r="J70" s="238"/>
-      <c r="K70" s="238"/>
-      <c r="L70" s="238"/>
+      <c r="B70" s="217"/>
+      <c r="C70" s="217"/>
+      <c r="D70" s="217"/>
+      <c r="E70" s="217"/>
+      <c r="F70" s="217"/>
+      <c r="G70" s="217"/>
+      <c r="H70" s="217"/>
+      <c r="I70" s="217"/>
+      <c r="J70" s="217"/>
+      <c r="K70" s="217"/>
+      <c r="L70" s="217"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="239" t="s">
+      <c r="A71" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="B71" s="239"/>
-      <c r="C71" s="239"/>
+      <c r="B71" s="218"/>
+      <c r="C71" s="218"/>
       <c r="D71" s="97"/>
       <c r="E71" s="97"/>
       <c r="F71" s="97"/>
@@ -9440,11 +9440,11 @@
         <f>COUNT(B73:B96)</f>
         <v>24</v>
       </c>
-      <c r="B97" s="240" t="s">
+      <c r="B97" s="219" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="240"/>
-      <c r="D97" s="240"/>
+      <c r="C97" s="219"/>
+      <c r="D97" s="219"/>
       <c r="E97" s="93"/>
       <c r="F97" s="93"/>
       <c r="G97" s="93"/>
@@ -9585,19 +9585,19 @@
         <f>COUNT(B100:B105)</f>
         <v>6</v>
       </c>
-      <c r="B106" s="241" t="s">
+      <c r="B106" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="241"/>
-      <c r="D106" s="241"/>
-      <c r="E106" s="241"/>
-      <c r="F106" s="241"/>
-      <c r="G106" s="241"/>
-      <c r="H106" s="241"/>
-      <c r="I106" s="241"/>
-      <c r="J106" s="241"/>
-      <c r="K106" s="241"/>
-      <c r="L106" s="241"/>
+      <c r="C106" s="220"/>
+      <c r="D106" s="220"/>
+      <c r="E106" s="220"/>
+      <c r="F106" s="220"/>
+      <c r="G106" s="220"/>
+      <c r="H106" s="220"/>
+      <c r="I106" s="220"/>
+      <c r="J106" s="220"/>
+      <c r="K106" s="220"/>
+      <c r="L106" s="220"/>
     </row>
     <row r="107" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A107" s="39"/>
@@ -9615,19 +9615,19 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="69"/>
-      <c r="B108" s="242" t="s">
+      <c r="B108" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="242"/>
-      <c r="D108" s="242"/>
-      <c r="E108" s="242"/>
-      <c r="F108" s="242"/>
-      <c r="G108" s="242"/>
-      <c r="H108" s="242"/>
-      <c r="I108" s="242"/>
-      <c r="J108" s="242"/>
-      <c r="K108" s="242"/>
-      <c r="L108" s="242"/>
+      <c r="C108" s="221"/>
+      <c r="D108" s="221"/>
+      <c r="E108" s="221"/>
+      <c r="F108" s="221"/>
+      <c r="G108" s="221"/>
+      <c r="H108" s="221"/>
+      <c r="I108" s="221"/>
+      <c r="J108" s="221"/>
+      <c r="K108" s="221"/>
+      <c r="L108" s="221"/>
     </row>
     <row r="109" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A109" s="89"/>
@@ -9746,38 +9746,38 @@
         <f>COUNTA(B109:B115)</f>
         <v>7</v>
       </c>
-      <c r="B116" s="241" t="s">
+      <c r="B116" s="220" t="s">
         <v>37</v>
       </c>
-      <c r="C116" s="241"/>
-      <c r="D116" s="241"/>
-      <c r="E116" s="241"/>
-      <c r="F116" s="241"/>
-      <c r="G116" s="241"/>
-      <c r="H116" s="241"/>
-      <c r="I116" s="241"/>
-      <c r="J116" s="241"/>
-      <c r="K116" s="241"/>
-      <c r="L116" s="241"/>
+      <c r="C116" s="220"/>
+      <c r="D116" s="220"/>
+      <c r="E116" s="220"/>
+      <c r="F116" s="220"/>
+      <c r="G116" s="220"/>
+      <c r="H116" s="220"/>
+      <c r="I116" s="220"/>
+      <c r="J116" s="220"/>
+      <c r="K116" s="220"/>
+      <c r="L116" s="220"/>
     </row>
     <row r="117" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A117" s="201">
         <f>A116+A106</f>
         <v>13</v>
       </c>
-      <c r="B117" s="243" t="s">
+      <c r="B117" s="222" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="243"/>
-      <c r="D117" s="243"/>
-      <c r="E117" s="243"/>
-      <c r="F117" s="243"/>
-      <c r="G117" s="243"/>
-      <c r="H117" s="243"/>
-      <c r="I117" s="243"/>
-      <c r="J117" s="243"/>
-      <c r="K117" s="243"/>
-      <c r="L117" s="243"/>
+      <c r="C117" s="222"/>
+      <c r="D117" s="222"/>
+      <c r="E117" s="222"/>
+      <c r="F117" s="222"/>
+      <c r="G117" s="222"/>
+      <c r="H117" s="222"/>
+      <c r="I117" s="222"/>
+      <c r="J117" s="222"/>
+      <c r="K117" s="222"/>
+      <c r="L117" s="222"/>
     </row>
     <row r="118" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A118" s="39"/>
@@ -9883,19 +9883,19 @@
       <c r="A125" s="61">
         <v>4</v>
       </c>
-      <c r="B125" s="232" t="s">
+      <c r="B125" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="233"/>
-      <c r="D125" s="233"/>
-      <c r="E125" s="233"/>
-      <c r="F125" s="233"/>
-      <c r="G125" s="233"/>
-      <c r="H125" s="233"/>
-      <c r="I125" s="233"/>
-      <c r="J125" s="233"/>
-      <c r="K125" s="233"/>
-      <c r="L125" s="234"/>
+      <c r="C125" s="212"/>
+      <c r="D125" s="212"/>
+      <c r="E125" s="212"/>
+      <c r="F125" s="212"/>
+      <c r="G125" s="212"/>
+      <c r="H125" s="212"/>
+      <c r="I125" s="212"/>
+      <c r="J125" s="212"/>
+      <c r="K125" s="212"/>
+      <c r="L125" s="213"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="125" t="s">
@@ -9989,19 +9989,19 @@
       <c r="A132" s="143">
         <v>0</v>
       </c>
-      <c r="B132" s="235" t="s">
+      <c r="B132" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="236"/>
-      <c r="D132" s="236"/>
-      <c r="E132" s="236"/>
-      <c r="F132" s="236"/>
-      <c r="G132" s="236"/>
-      <c r="H132" s="236"/>
-      <c r="I132" s="236"/>
-      <c r="J132" s="236"/>
-      <c r="K132" s="236"/>
-      <c r="L132" s="237"/>
+      <c r="C132" s="215"/>
+      <c r="D132" s="215"/>
+      <c r="E132" s="215"/>
+      <c r="F132" s="215"/>
+      <c r="G132" s="215"/>
+      <c r="H132" s="215"/>
+      <c r="I132" s="215"/>
+      <c r="J132" s="215"/>
+      <c r="K132" s="215"/>
+      <c r="L132" s="216"/>
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="167">
@@ -10068,6 +10068,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="29">
+    <mergeCell ref="B108:L108"/>
+    <mergeCell ref="B116:L116"/>
+    <mergeCell ref="B117:L117"/>
+    <mergeCell ref="B125:L125"/>
+    <mergeCell ref="B132:L132"/>
+    <mergeCell ref="B106:L106"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="A68:L69"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B97:D97"/>
     <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -10080,23 +10097,6 @@
     <mergeCell ref="B42:L42"/>
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="B49:L49"/>
-    <mergeCell ref="B106:L106"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="B59:L59"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="B64:L64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="A68:L69"/>
-    <mergeCell ref="A70:L70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B108:L108"/>
-    <mergeCell ref="B116:L116"/>
-    <mergeCell ref="B117:L117"/>
-    <mergeCell ref="B125:L125"/>
-    <mergeCell ref="B132:L132"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10951,36 +10951,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="240" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -11001,36 +11001,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -11047,34 +11047,34 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="242" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="211"/>
-      <c r="L7" s="212"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="244"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="204"/>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="206"/>
+      <c r="A8" s="236"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="238"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="183" t="s">
@@ -16216,36 +16216,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -16266,36 +16266,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -16312,36 +16312,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="211"/>
-      <c r="L7" s="212"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="244"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="206"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="238"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -19781,19 +19781,19 @@
       <c r="A26" s="61">
         <v>0</v>
       </c>
-      <c r="B26" s="214" t="s">
+      <c r="B26" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="215"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="215"/>
-      <c r="G26" s="215"/>
-      <c r="H26" s="215"/>
-      <c r="I26" s="215"/>
-      <c r="J26" s="215"/>
-      <c r="K26" s="215"/>
-      <c r="L26" s="216"/>
+      <c r="C26" s="225"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="226"/>
     </row>
     <row r="27" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A27" s="62"/>
@@ -19810,20 +19810,20 @@
       <c r="L27" s="63"/>
     </row>
     <row r="28" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="217" t="s">
+      <c r="A28" s="227" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="218"/>
-      <c r="C28" s="218"/>
-      <c r="D28" s="218"/>
-      <c r="E28" s="218"/>
-      <c r="F28" s="218"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="218"/>
-      <c r="I28" s="218"/>
-      <c r="J28" s="218"/>
-      <c r="K28" s="218"/>
-      <c r="L28" s="218"/>
+      <c r="B28" s="228"/>
+      <c r="C28" s="228"/>
+      <c r="D28" s="228"/>
+      <c r="E28" s="228"/>
+      <c r="F28" s="228"/>
+      <c r="G28" s="228"/>
+      <c r="H28" s="228"/>
+      <c r="I28" s="228"/>
+      <c r="J28" s="228"/>
+      <c r="K28" s="228"/>
+      <c r="L28" s="228"/>
       <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
@@ -20443,19 +20443,19 @@
       <c r="A38" s="70">
         <v>0</v>
       </c>
-      <c r="B38" s="219" t="s">
+      <c r="B38" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="220"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="220"/>
-      <c r="H38" s="220"/>
-      <c r="I38" s="220"/>
-      <c r="J38" s="220"/>
-      <c r="K38" s="220"/>
-      <c r="L38" s="221"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
+      <c r="E38" s="230"/>
+      <c r="F38" s="230"/>
+      <c r="G38" s="230"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="230"/>
+      <c r="J38" s="230"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="231"/>
     </row>
     <row r="39" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A39" s="71"/>
@@ -20472,20 +20472,20 @@
       <c r="L39" s="63"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="222" t="s">
+      <c r="A40" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="222"/>
-      <c r="C40" s="222"/>
-      <c r="D40" s="222"/>
-      <c r="E40" s="222"/>
-      <c r="F40" s="222"/>
-      <c r="G40" s="222"/>
-      <c r="H40" s="222"/>
-      <c r="I40" s="222"/>
-      <c r="J40" s="222"/>
-      <c r="K40" s="222"/>
-      <c r="L40" s="222"/>
+      <c r="B40" s="232"/>
+      <c r="C40" s="232"/>
+      <c r="D40" s="232"/>
+      <c r="E40" s="232"/>
+      <c r="F40" s="232"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="72"/>
@@ -20519,19 +20519,19 @@
       <c r="A43" s="80">
         <v>0</v>
       </c>
-      <c r="B43" s="223" t="s">
+      <c r="B43" s="233" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="223"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="224"/>
+      <c r="C43" s="233"/>
+      <c r="D43" s="233"/>
+      <c r="E43" s="233"/>
+      <c r="F43" s="233"/>
+      <c r="G43" s="233"/>
+      <c r="H43" s="233"/>
+      <c r="I43" s="233"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="234"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="81"/>
@@ -20548,20 +20548,20 @@
       <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="225" t="s">
+      <c r="A45" s="235" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="225"/>
-      <c r="C45" s="225"/>
-      <c r="D45" s="225"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
-      <c r="G45" s="225"/>
-      <c r="H45" s="225"/>
-      <c r="I45" s="225"/>
-      <c r="J45" s="225"/>
-      <c r="K45" s="225"/>
-      <c r="L45" s="225"/>
+      <c r="B45" s="235"/>
+      <c r="C45" s="235"/>
+      <c r="D45" s="235"/>
+      <c r="E45" s="235"/>
+      <c r="F45" s="235"/>
+      <c r="G45" s="235"/>
+      <c r="H45" s="235"/>
+      <c r="I45" s="235"/>
+      <c r="J45" s="235"/>
+      <c r="K45" s="235"/>
+      <c r="L45" s="235"/>
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="84"/>
@@ -20595,19 +20595,19 @@
       <c r="A48" s="80">
         <v>0</v>
       </c>
-      <c r="B48" s="219" t="s">
+      <c r="B48" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
-      <c r="J48" s="220"/>
-      <c r="K48" s="220"/>
-      <c r="L48" s="221"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="230"/>
+      <c r="L48" s="231"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A49" s="71"/>
@@ -20624,20 +20624,20 @@
       <c r="L49" s="40"/>
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="225" t="s">
+      <c r="A50" s="235" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="225"/>
-      <c r="C50" s="225"/>
-      <c r="D50" s="225"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
-      <c r="G50" s="225"/>
-      <c r="H50" s="225"/>
-      <c r="I50" s="225"/>
-      <c r="J50" s="225"/>
-      <c r="K50" s="225"/>
-      <c r="L50" s="225"/>
+      <c r="B50" s="235"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="84"/>
@@ -20671,19 +20671,19 @@
       <c r="A53" s="80">
         <v>0</v>
       </c>
-      <c r="B53" s="219" t="s">
+      <c r="B53" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="220"/>
-      <c r="D53" s="220"/>
-      <c r="E53" s="220"/>
-      <c r="F53" s="220"/>
-      <c r="G53" s="220"/>
-      <c r="H53" s="220"/>
-      <c r="I53" s="220"/>
-      <c r="J53" s="220"/>
-      <c r="K53" s="220"/>
-      <c r="L53" s="221"/>
+      <c r="C53" s="230"/>
+      <c r="D53" s="230"/>
+      <c r="E53" s="230"/>
+      <c r="F53" s="230"/>
+      <c r="G53" s="230"/>
+      <c r="H53" s="230"/>
+      <c r="I53" s="230"/>
+      <c r="J53" s="230"/>
+      <c r="K53" s="230"/>
+      <c r="L53" s="231"/>
     </row>
     <row r="54" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A54" s="71"/>
@@ -20700,20 +20700,20 @@
       <c r="L54" s="40"/>
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="225" t="s">
+      <c r="A55" s="235" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="225"/>
-      <c r="C55" s="225"/>
-      <c r="D55" s="225"/>
-      <c r="E55" s="225"/>
-      <c r="F55" s="225"/>
-      <c r="G55" s="225"/>
-      <c r="H55" s="225"/>
-      <c r="I55" s="225"/>
-      <c r="J55" s="225"/>
-      <c r="K55" s="225"/>
-      <c r="L55" s="225"/>
+      <c r="B55" s="235"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="235"/>
+      <c r="E55" s="235"/>
+      <c r="F55" s="235"/>
+      <c r="G55" s="235"/>
+      <c r="H55" s="235"/>
+      <c r="I55" s="235"/>
+      <c r="J55" s="235"/>
+      <c r="K55" s="235"/>
+      <c r="L55" s="235"/>
     </row>
     <row r="56" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="90"/>
@@ -20747,19 +20747,19 @@
       <c r="A58" s="80">
         <v>0</v>
       </c>
-      <c r="B58" s="219" t="s">
+      <c r="B58" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="220"/>
-      <c r="D58" s="220"/>
-      <c r="E58" s="220"/>
-      <c r="F58" s="220"/>
-      <c r="G58" s="220"/>
-      <c r="H58" s="220"/>
-      <c r="I58" s="220"/>
-      <c r="J58" s="220"/>
-      <c r="K58" s="220"/>
-      <c r="L58" s="221"/>
+      <c r="C58" s="230"/>
+      <c r="D58" s="230"/>
+      <c r="E58" s="230"/>
+      <c r="F58" s="230"/>
+      <c r="G58" s="230"/>
+      <c r="H58" s="230"/>
+      <c r="I58" s="230"/>
+      <c r="J58" s="230"/>
+      <c r="K58" s="230"/>
+      <c r="L58" s="231"/>
     </row>
     <row r="59" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A59" s="71"/>
@@ -20777,10 +20777,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
-      <c r="B60" s="213" t="s">
+      <c r="B60" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="C60" s="213"/>
+      <c r="C60" s="223"/>
       <c r="D60" s="94" t="s">
         <v>30</v>
       </c>
@@ -20795,10 +20795,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
-      <c r="B61" s="213" t="s">
+      <c r="B61" s="223" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="213"/>
+      <c r="C61" s="223"/>
       <c r="D61" s="94"/>
       <c r="E61" s="95"/>
       <c r="F61" s="95"/>
@@ -20810,55 +20810,55 @@
       <c r="L61" s="96"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="226"/>
-      <c r="B62" s="227"/>
-      <c r="C62" s="227"/>
-      <c r="D62" s="227"/>
-      <c r="E62" s="227"/>
-      <c r="F62" s="227"/>
-      <c r="G62" s="227"/>
-      <c r="H62" s="227"/>
-      <c r="I62" s="227"/>
-      <c r="J62" s="227"/>
-      <c r="K62" s="227"/>
-      <c r="L62" s="228"/>
+      <c r="A62" s="205"/>
+      <c r="B62" s="206"/>
+      <c r="C62" s="206"/>
+      <c r="D62" s="206"/>
+      <c r="E62" s="206"/>
+      <c r="F62" s="206"/>
+      <c r="G62" s="206"/>
+      <c r="H62" s="206"/>
+      <c r="I62" s="206"/>
+      <c r="J62" s="206"/>
+      <c r="K62" s="206"/>
+      <c r="L62" s="207"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="229"/>
-      <c r="B63" s="230"/>
-      <c r="C63" s="230"/>
-      <c r="D63" s="230"/>
-      <c r="E63" s="230"/>
-      <c r="F63" s="230"/>
-      <c r="G63" s="230"/>
-      <c r="H63" s="230"/>
-      <c r="I63" s="230"/>
-      <c r="J63" s="230"/>
-      <c r="K63" s="230"/>
-      <c r="L63" s="231"/>
+      <c r="A63" s="208"/>
+      <c r="B63" s="209"/>
+      <c r="C63" s="209"/>
+      <c r="D63" s="209"/>
+      <c r="E63" s="209"/>
+      <c r="F63" s="209"/>
+      <c r="G63" s="209"/>
+      <c r="H63" s="209"/>
+      <c r="I63" s="209"/>
+      <c r="J63" s="209"/>
+      <c r="K63" s="209"/>
+      <c r="L63" s="210"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="238" t="s">
+      <c r="A64" s="217" t="s">
         <v>32</v>
       </c>
-      <c r="B64" s="238"/>
-      <c r="C64" s="238"/>
-      <c r="D64" s="238"/>
-      <c r="E64" s="238"/>
-      <c r="F64" s="238"/>
-      <c r="G64" s="238"/>
-      <c r="H64" s="238"/>
-      <c r="I64" s="238"/>
-      <c r="J64" s="238"/>
-      <c r="K64" s="238"/>
-      <c r="L64" s="238"/>
+      <c r="B64" s="217"/>
+      <c r="C64" s="217"/>
+      <c r="D64" s="217"/>
+      <c r="E64" s="217"/>
+      <c r="F64" s="217"/>
+      <c r="G64" s="217"/>
+      <c r="H64" s="217"/>
+      <c r="I64" s="217"/>
+      <c r="J64" s="217"/>
+      <c r="K64" s="217"/>
+      <c r="L64" s="217"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="239" t="s">
+      <c r="A65" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="239"/>
-      <c r="C65" s="239"/>
+      <c r="B65" s="218"/>
+      <c r="C65" s="218"/>
       <c r="D65" s="97"/>
       <c r="E65" s="97"/>
       <c r="F65" s="97"/>
@@ -21929,11 +21929,11 @@
       <c r="A140" s="61">
         <v>0</v>
       </c>
-      <c r="B140" s="239" t="s">
+      <c r="B140" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="C140" s="239"/>
-      <c r="D140" s="239"/>
+      <c r="C140" s="218"/>
+      <c r="D140" s="218"/>
       <c r="E140" s="95"/>
       <c r="F140" s="95"/>
       <c r="G140" s="95"/>
@@ -22019,19 +22019,19 @@
       <c r="A146" s="143">
         <v>0</v>
       </c>
-      <c r="B146" s="247" t="s">
+      <c r="B146" s="248" t="s">
         <v>36</v>
       </c>
-      <c r="C146" s="247"/>
-      <c r="D146" s="247"/>
-      <c r="E146" s="247"/>
-      <c r="F146" s="247"/>
-      <c r="G146" s="247"/>
-      <c r="H146" s="247"/>
-      <c r="I146" s="247"/>
-      <c r="J146" s="247"/>
-      <c r="K146" s="247"/>
-      <c r="L146" s="247"/>
+      <c r="C146" s="248"/>
+      <c r="D146" s="248"/>
+      <c r="E146" s="248"/>
+      <c r="F146" s="248"/>
+      <c r="G146" s="248"/>
+      <c r="H146" s="248"/>
+      <c r="I146" s="248"/>
+      <c r="J146" s="248"/>
+      <c r="K146" s="248"/>
+      <c r="L146" s="248"/>
     </row>
     <row r="147" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A147" s="39"/>
@@ -22048,19 +22048,19 @@
       <c r="L147" s="40"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="244" t="s">
+      <c r="B148" s="245" t="s">
         <v>22</v>
       </c>
-      <c r="C148" s="244"/>
-      <c r="D148" s="244"/>
-      <c r="E148" s="244"/>
-      <c r="F148" s="244"/>
-      <c r="G148" s="244"/>
-      <c r="H148" s="244"/>
-      <c r="I148" s="244"/>
-      <c r="J148" s="244"/>
-      <c r="K148" s="244"/>
-      <c r="L148" s="244"/>
+      <c r="C148" s="245"/>
+      <c r="D148" s="245"/>
+      <c r="E148" s="245"/>
+      <c r="F148" s="245"/>
+      <c r="G148" s="245"/>
+      <c r="H148" s="245"/>
+      <c r="I148" s="245"/>
+      <c r="J148" s="245"/>
+      <c r="K148" s="245"/>
+      <c r="L148" s="245"/>
     </row>
     <row r="149" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A149" s="89"/>
@@ -22192,19 +22192,19 @@
       <c r="A158" s="150">
         <v>0</v>
       </c>
-      <c r="B158" s="245" t="s">
+      <c r="B158" s="246" t="s">
         <v>37</v>
       </c>
-      <c r="C158" s="245"/>
-      <c r="D158" s="245"/>
-      <c r="E158" s="245"/>
-      <c r="F158" s="245"/>
-      <c r="G158" s="245"/>
-      <c r="H158" s="245"/>
-      <c r="I158" s="245"/>
-      <c r="J158" s="245"/>
-      <c r="K158" s="245"/>
-      <c r="L158" s="246"/>
+      <c r="C158" s="246"/>
+      <c r="D158" s="246"/>
+      <c r="E158" s="246"/>
+      <c r="F158" s="246"/>
+      <c r="G158" s="246"/>
+      <c r="H158" s="246"/>
+      <c r="I158" s="246"/>
+      <c r="J158" s="246"/>
+      <c r="K158" s="246"/>
+      <c r="L158" s="247"/>
     </row>
     <row r="159" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C159" s="145"/>
@@ -22340,19 +22340,19 @@
       <c r="A168" s="61">
         <v>4</v>
       </c>
-      <c r="B168" s="232" t="s">
+      <c r="B168" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="C168" s="233"/>
-      <c r="D168" s="233"/>
-      <c r="E168" s="233"/>
-      <c r="F168" s="233"/>
-      <c r="G168" s="233"/>
-      <c r="H168" s="233"/>
-      <c r="I168" s="233"/>
-      <c r="J168" s="233"/>
-      <c r="K168" s="233"/>
-      <c r="L168" s="234"/>
+      <c r="C168" s="212"/>
+      <c r="D168" s="212"/>
+      <c r="E168" s="212"/>
+      <c r="F168" s="212"/>
+      <c r="G168" s="212"/>
+      <c r="H168" s="212"/>
+      <c r="I168" s="212"/>
+      <c r="J168" s="212"/>
+      <c r="K168" s="212"/>
+      <c r="L168" s="213"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="125" t="s">
@@ -22446,19 +22446,19 @@
       <c r="A175" s="143">
         <v>2</v>
       </c>
-      <c r="B175" s="235" t="s">
+      <c r="B175" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="C175" s="236"/>
-      <c r="D175" s="236"/>
-      <c r="E175" s="236"/>
-      <c r="F175" s="236"/>
-      <c r="G175" s="236"/>
-      <c r="H175" s="236"/>
-      <c r="I175" s="236"/>
-      <c r="J175" s="236"/>
-      <c r="K175" s="236"/>
-      <c r="L175" s="237"/>
+      <c r="C175" s="215"/>
+      <c r="D175" s="215"/>
+      <c r="E175" s="215"/>
+      <c r="F175" s="215"/>
+      <c r="G175" s="215"/>
+      <c r="H175" s="215"/>
+      <c r="I175" s="215"/>
+      <c r="J175" s="215"/>
+      <c r="K175" s="215"/>
+      <c r="L175" s="216"/>
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A176" s="167">
@@ -22481,16 +22481,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="28">
-    <mergeCell ref="B148:L148"/>
-    <mergeCell ref="B158:L158"/>
-    <mergeCell ref="B168:L168"/>
-    <mergeCell ref="B175:L175"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="A62:L63"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="B146:L146"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="A28:L28"/>
@@ -22503,12 +22499,16 @@
     <mergeCell ref="B53:L53"/>
     <mergeCell ref="A55:L55"/>
     <mergeCell ref="B58:L58"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B158:L158"/>
+    <mergeCell ref="B168:L168"/>
+    <mergeCell ref="B175:L175"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A62:L63"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B140:D140"/>
+    <mergeCell ref="B146:L146"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23360,36 +23360,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
     </row>
     <row r="2" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
@@ -23410,36 +23410,36 @@
         <v>1</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:256" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
     </row>
     <row r="6" spans="1:256" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="39"/>
@@ -23456,36 +23456,36 @@
       <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="211"/>
-      <c r="L7" s="212"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="244"/>
     </row>
     <row r="8" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="206"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="238"/>
     </row>
     <row r="9" spans="1:256" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="44" t="s">
@@ -27794,19 +27794,19 @@
         <f>COUNT(B10:B29)</f>
         <v>20</v>
       </c>
-      <c r="B30" s="214" t="s">
+      <c r="B30" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="215"/>
-      <c r="J30" s="215"/>
-      <c r="K30" s="215"/>
-      <c r="L30" s="216"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="226"/>
     </row>
     <row r="31" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A31" s="62"/>
@@ -27823,20 +27823,20 @@
       <c r="L31" s="63"/>
     </row>
     <row r="32" spans="1:256" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="217" t="s">
+      <c r="A32" s="227" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="218"/>
-      <c r="C32" s="218"/>
-      <c r="D32" s="218"/>
-      <c r="E32" s="218"/>
-      <c r="F32" s="218"/>
-      <c r="G32" s="218"/>
-      <c r="H32" s="218"/>
-      <c r="I32" s="218"/>
-      <c r="J32" s="218"/>
-      <c r="K32" s="218"/>
-      <c r="L32" s="218"/>
+      <c r="B32" s="228"/>
+      <c r="C32" s="228"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="228"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="228"/>
+      <c r="I32" s="228"/>
+      <c r="J32" s="228"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
@@ -28493,19 +28493,19 @@
         <f>COUNT(B33:B41)</f>
         <v>4</v>
       </c>
-      <c r="B42" s="219" t="s">
+      <c r="B42" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="220"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="220"/>
-      <c r="I42" s="220"/>
-      <c r="J42" s="220"/>
-      <c r="K42" s="220"/>
-      <c r="L42" s="221"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="230"/>
+      <c r="J42" s="230"/>
+      <c r="K42" s="230"/>
+      <c r="L42" s="231"/>
     </row>
     <row r="43" spans="1:256" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A43" s="71"/>
@@ -28522,20 +28522,20 @@
       <c r="L43" s="63"/>
     </row>
     <row r="44" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="222" t="s">
+      <c r="A44" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="222"/>
-      <c r="C44" s="222"/>
-      <c r="D44" s="222"/>
-      <c r="E44" s="222"/>
-      <c r="F44" s="222"/>
-      <c r="G44" s="222"/>
-      <c r="H44" s="222"/>
-      <c r="I44" s="222"/>
-      <c r="J44" s="222"/>
-      <c r="K44" s="222"/>
-      <c r="L44" s="222"/>
+      <c r="B44" s="232"/>
+      <c r="C44" s="232"/>
+      <c r="D44" s="232"/>
+      <c r="E44" s="232"/>
+      <c r="F44" s="232"/>
+      <c r="G44" s="232"/>
+      <c r="H44" s="232"/>
+      <c r="I44" s="232"/>
+      <c r="J44" s="232"/>
+      <c r="K44" s="232"/>
+      <c r="L44" s="232"/>
     </row>
     <row r="45" spans="1:256" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="188">
@@ -28614,19 +28614,19 @@
         <f>COUNT(A45:A48)</f>
         <v>4</v>
       </c>
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="233" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="223"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="223"/>
-      <c r="F49" s="223"/>
-      <c r="G49" s="223"/>
-      <c r="H49" s="223"/>
-      <c r="I49" s="223"/>
-      <c r="J49" s="223"/>
-      <c r="K49" s="223"/>
-      <c r="L49" s="224"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
+      <c r="I49" s="233"/>
+      <c r="J49" s="233"/>
+      <c r="K49" s="233"/>
+      <c r="L49" s="234"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="81"/>
@@ -28643,20 +28643,20 @@
       <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="225" t="s">
+      <c r="A51" s="235" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="225"/>
-      <c r="C51" s="225"/>
-      <c r="D51" s="225"/>
-      <c r="E51" s="225"/>
-      <c r="F51" s="225"/>
-      <c r="G51" s="225"/>
-      <c r="H51" s="225"/>
-      <c r="I51" s="225"/>
-      <c r="J51" s="225"/>
-      <c r="K51" s="225"/>
-      <c r="L51" s="225"/>
+      <c r="B51" s="235"/>
+      <c r="C51" s="235"/>
+      <c r="D51" s="235"/>
+      <c r="E51" s="235"/>
+      <c r="F51" s="235"/>
+      <c r="G51" s="235"/>
+      <c r="H51" s="235"/>
+      <c r="I51" s="235"/>
+      <c r="J51" s="235"/>
+      <c r="K51" s="235"/>
+      <c r="L51" s="235"/>
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="84"/>
@@ -28690,19 +28690,19 @@
       <c r="A54" s="80">
         <v>0</v>
       </c>
-      <c r="B54" s="219" t="s">
+      <c r="B54" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="220"/>
-      <c r="D54" s="220"/>
-      <c r="E54" s="220"/>
-      <c r="F54" s="220"/>
-      <c r="G54" s="220"/>
-      <c r="H54" s="220"/>
-      <c r="I54" s="220"/>
-      <c r="J54" s="220"/>
-      <c r="K54" s="220"/>
-      <c r="L54" s="221"/>
+      <c r="C54" s="230"/>
+      <c r="D54" s="230"/>
+      <c r="E54" s="230"/>
+      <c r="F54" s="230"/>
+      <c r="G54" s="230"/>
+      <c r="H54" s="230"/>
+      <c r="I54" s="230"/>
+      <c r="J54" s="230"/>
+      <c r="K54" s="230"/>
+      <c r="L54" s="231"/>
     </row>
     <row r="55" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A55" s="71"/>
@@ -28719,20 +28719,20 @@
       <c r="L55" s="40"/>
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="225" t="s">
+      <c r="A56" s="235" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="225"/>
-      <c r="C56" s="225"/>
-      <c r="D56" s="225"/>
-      <c r="E56" s="225"/>
-      <c r="F56" s="225"/>
-      <c r="G56" s="225"/>
-      <c r="H56" s="225"/>
-      <c r="I56" s="225"/>
-      <c r="J56" s="225"/>
-      <c r="K56" s="225"/>
-      <c r="L56" s="225"/>
+      <c r="B56" s="235"/>
+      <c r="C56" s="235"/>
+      <c r="D56" s="235"/>
+      <c r="E56" s="235"/>
+      <c r="F56" s="235"/>
+      <c r="G56" s="235"/>
+      <c r="H56" s="235"/>
+      <c r="I56" s="235"/>
+      <c r="J56" s="235"/>
+      <c r="K56" s="235"/>
+      <c r="L56" s="235"/>
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="84"/>
@@ -28766,19 +28766,19 @@
       <c r="A59" s="80">
         <v>0</v>
       </c>
-      <c r="B59" s="219" t="s">
+      <c r="B59" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="220"/>
-      <c r="D59" s="220"/>
-      <c r="E59" s="220"/>
-      <c r="F59" s="220"/>
-      <c r="G59" s="220"/>
-      <c r="H59" s="220"/>
-      <c r="I59" s="220"/>
-      <c r="J59" s="220"/>
-      <c r="K59" s="220"/>
-      <c r="L59" s="221"/>
+      <c r="C59" s="230"/>
+      <c r="D59" s="230"/>
+      <c r="E59" s="230"/>
+      <c r="F59" s="230"/>
+      <c r="G59" s="230"/>
+      <c r="H59" s="230"/>
+      <c r="I59" s="230"/>
+      <c r="J59" s="230"/>
+      <c r="K59" s="230"/>
+      <c r="L59" s="231"/>
     </row>
     <row r="60" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A60" s="71"/>
@@ -28795,20 +28795,20 @@
       <c r="L60" s="40"/>
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="225" t="s">
+      <c r="A61" s="235" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="225"/>
-      <c r="C61" s="225"/>
-      <c r="D61" s="225"/>
-      <c r="E61" s="225"/>
-      <c r="F61" s="225"/>
-      <c r="G61" s="225"/>
-      <c r="H61" s="225"/>
-      <c r="I61" s="225"/>
-      <c r="J61" s="225"/>
-      <c r="K61" s="225"/>
-      <c r="L61" s="225"/>
+      <c r="B61" s="235"/>
+      <c r="C61" s="235"/>
+      <c r="D61" s="235"/>
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="235"/>
+      <c r="H61" s="235"/>
+      <c r="I61" s="235"/>
+      <c r="J61" s="235"/>
+      <c r="K61" s="235"/>
+      <c r="L61" s="235"/>
     </row>
     <row r="62" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="90"/>
@@ -28842,19 +28842,19 @@
       <c r="A64" s="80">
         <v>0</v>
       </c>
-      <c r="B64" s="219" t="s">
+      <c r="B64" s="229" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="220"/>
-      <c r="D64" s="220"/>
-      <c r="E64" s="220"/>
-      <c r="F64" s="220"/>
-      <c r="G64" s="220"/>
-      <c r="H64" s="220"/>
-      <c r="I64" s="220"/>
-      <c r="J64" s="220"/>
-      <c r="K64" s="220"/>
-      <c r="L64" s="221"/>
+      <c r="C64" s="230"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="230"/>
+      <c r="G64" s="230"/>
+      <c r="H64" s="230"/>
+      <c r="I64" s="230"/>
+      <c r="J64" s="230"/>
+      <c r="K64" s="230"/>
+      <c r="L64" s="231"/>
     </row>
     <row r="65" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A65" s="71"/>
@@ -28875,10 +28875,10 @@
         <f>A42+A49+A54+A59+A64</f>
         <v>8</v>
       </c>
-      <c r="B66" s="213" t="s">
+      <c r="B66" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="213"/>
+      <c r="C66" s="223"/>
       <c r="D66" s="94" t="s">
         <v>30</v>
       </c>
@@ -28896,10 +28896,10 @@
         <f>A30+A66</f>
         <v>28</v>
       </c>
-      <c r="B67" s="213" t="s">
+      <c r="B67" s="223" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="213"/>
+      <c r="C67" s="223"/>
       <c r="D67" s="94"/>
       <c r="E67" s="95"/>
       <c r="F67" s="95"/>
@@ -28911,55 +28911,55 @@
       <c r="L67" s="96"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="226"/>
-      <c r="B68" s="227"/>
-      <c r="C68" s="227"/>
-      <c r="D68" s="227"/>
-      <c r="E68" s="227"/>
-      <c r="F68" s="227"/>
-      <c r="G68" s="227"/>
-      <c r="H68" s="227"/>
-      <c r="I68" s="227"/>
-      <c r="J68" s="227"/>
-      <c r="K68" s="227"/>
-      <c r="L68" s="228"/>
+      <c r="A68" s="205"/>
+      <c r="B68" s="206"/>
+      <c r="C68" s="206"/>
+      <c r="D68" s="206"/>
+      <c r="E68" s="206"/>
+      <c r="F68" s="206"/>
+      <c r="G68" s="206"/>
+      <c r="H68" s="206"/>
+      <c r="I68" s="206"/>
+      <c r="J68" s="206"/>
+      <c r="K68" s="206"/>
+      <c r="L68" s="207"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="229"/>
-      <c r="B69" s="230"/>
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
-      <c r="I69" s="230"/>
-      <c r="J69" s="230"/>
-      <c r="K69" s="230"/>
-      <c r="L69" s="231"/>
+      <c r="A69" s="208"/>
+      <c r="B69" s="209"/>
+      <c r="C69" s="209"/>
+      <c r="D69" s="209"/>
+      <c r="E69" s="209"/>
+      <c r="F69" s="209"/>
+      <c r="G69" s="209"/>
+      <c r="H69" s="209"/>
+      <c r="I69" s="209"/>
+      <c r="J69" s="209"/>
+      <c r="K69" s="209"/>
+      <c r="L69" s="210"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="238" t="s">
+      <c r="A70" s="217" t="s">
         <v>32</v>
       </c>
-      <c r="B70" s="238"/>
-      <c r="C70" s="238"/>
-      <c r="D70" s="238"/>
-      <c r="E70" s="238"/>
-      <c r="F70" s="238"/>
-      <c r="G70" s="238"/>
-      <c r="H70" s="238"/>
-      <c r="I70" s="238"/>
-      <c r="J70" s="238"/>
-      <c r="K70" s="238"/>
-      <c r="L70" s="238"/>
+      <c r="B70" s="217"/>
+      <c r="C70" s="217"/>
+      <c r="D70" s="217"/>
+      <c r="E70" s="217"/>
+      <c r="F70" s="217"/>
+      <c r="G70" s="217"/>
+      <c r="H70" s="217"/>
+      <c r="I70" s="217"/>
+      <c r="J70" s="217"/>
+      <c r="K70" s="217"/>
+      <c r="L70" s="217"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="239" t="s">
+      <c r="A71" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="B71" s="239"/>
-      <c r="C71" s="239"/>
+      <c r="B71" s="218"/>
+      <c r="C71" s="218"/>
       <c r="D71" s="97"/>
       <c r="E71" s="97"/>
       <c r="F71" s="97"/>
@@ -29008,7 +29008,7 @@
     </row>
     <row r="73" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A73" s="47"/>
-      <c r="B73" s="258">
+      <c r="B73" s="204">
         <v>4568</v>
       </c>
       <c r="C73" s="49"/>
@@ -29024,7 +29024,7 @@
     </row>
     <row r="74" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A74" s="47"/>
-      <c r="B74" s="48">
+      <c r="B74" s="204">
         <v>4648</v>
       </c>
       <c r="C74" s="49"/>
@@ -29040,7 +29040,7 @@
     </row>
     <row r="75" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A75" s="47"/>
-      <c r="B75" s="48">
+      <c r="B75" s="204">
         <v>4671</v>
       </c>
       <c r="C75" s="49"/>
@@ -29395,11 +29395,11 @@
         <f>COUNT(B73:B96)</f>
         <v>24</v>
       </c>
-      <c r="B97" s="240" t="s">
+      <c r="B97" s="219" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="240"/>
-      <c r="D97" s="240"/>
+      <c r="C97" s="219"/>
+      <c r="D97" s="219"/>
       <c r="E97" s="93"/>
       <c r="F97" s="93"/>
       <c r="G97" s="93"/>
@@ -29540,19 +29540,19 @@
         <f>COUNT(B100:B105)</f>
         <v>6</v>
       </c>
-      <c r="B106" s="241" t="s">
+      <c r="B106" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="241"/>
-      <c r="D106" s="241"/>
-      <c r="E106" s="241"/>
-      <c r="F106" s="241"/>
-      <c r="G106" s="241"/>
-      <c r="H106" s="241"/>
-      <c r="I106" s="241"/>
-      <c r="J106" s="241"/>
-      <c r="K106" s="241"/>
-      <c r="L106" s="241"/>
+      <c r="C106" s="220"/>
+      <c r="D106" s="220"/>
+      <c r="E106" s="220"/>
+      <c r="F106" s="220"/>
+      <c r="G106" s="220"/>
+      <c r="H106" s="220"/>
+      <c r="I106" s="220"/>
+      <c r="J106" s="220"/>
+      <c r="K106" s="220"/>
+      <c r="L106" s="220"/>
     </row>
     <row r="107" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A107" s="39"/>
@@ -29570,19 +29570,19 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="69"/>
-      <c r="B108" s="242" t="s">
+      <c r="B108" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="242"/>
-      <c r="D108" s="242"/>
-      <c r="E108" s="242"/>
-      <c r="F108" s="242"/>
-      <c r="G108" s="242"/>
-      <c r="H108" s="242"/>
-      <c r="I108" s="242"/>
-      <c r="J108" s="242"/>
-      <c r="K108" s="242"/>
-      <c r="L108" s="242"/>
+      <c r="C108" s="221"/>
+      <c r="D108" s="221"/>
+      <c r="E108" s="221"/>
+      <c r="F108" s="221"/>
+      <c r="G108" s="221"/>
+      <c r="H108" s="221"/>
+      <c r="I108" s="221"/>
+      <c r="J108" s="221"/>
+      <c r="K108" s="221"/>
+      <c r="L108" s="221"/>
     </row>
     <row r="109" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A109" s="89"/>
@@ -29701,38 +29701,38 @@
         <f>COUNTA(B109:B115)</f>
         <v>7</v>
       </c>
-      <c r="B116" s="241" t="s">
+      <c r="B116" s="220" t="s">
         <v>37</v>
       </c>
-      <c r="C116" s="241"/>
-      <c r="D116" s="241"/>
-      <c r="E116" s="241"/>
-      <c r="F116" s="241"/>
-      <c r="G116" s="241"/>
-      <c r="H116" s="241"/>
-      <c r="I116" s="241"/>
-      <c r="J116" s="241"/>
-      <c r="K116" s="241"/>
-      <c r="L116" s="241"/>
+      <c r="C116" s="220"/>
+      <c r="D116" s="220"/>
+      <c r="E116" s="220"/>
+      <c r="F116" s="220"/>
+      <c r="G116" s="220"/>
+      <c r="H116" s="220"/>
+      <c r="I116" s="220"/>
+      <c r="J116" s="220"/>
+      <c r="K116" s="220"/>
+      <c r="L116" s="220"/>
     </row>
     <row r="117" spans="1:12" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A117" s="201">
         <f>A116+A106</f>
         <v>13</v>
       </c>
-      <c r="B117" s="243" t="s">
+      <c r="B117" s="222" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="243"/>
-      <c r="D117" s="243"/>
-      <c r="E117" s="243"/>
-      <c r="F117" s="243"/>
-      <c r="G117" s="243"/>
-      <c r="H117" s="243"/>
-      <c r="I117" s="243"/>
-      <c r="J117" s="243"/>
-      <c r="K117" s="243"/>
-      <c r="L117" s="243"/>
+      <c r="C117" s="222"/>
+      <c r="D117" s="222"/>
+      <c r="E117" s="222"/>
+      <c r="F117" s="222"/>
+      <c r="G117" s="222"/>
+      <c r="H117" s="222"/>
+      <c r="I117" s="222"/>
+      <c r="J117" s="222"/>
+      <c r="K117" s="222"/>
+      <c r="L117" s="222"/>
     </row>
     <row r="118" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A118" s="39"/>
@@ -29838,19 +29838,19 @@
       <c r="A125" s="61">
         <v>4</v>
       </c>
-      <c r="B125" s="232" t="s">
+      <c r="B125" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="233"/>
-      <c r="D125" s="233"/>
-      <c r="E125" s="233"/>
-      <c r="F125" s="233"/>
-      <c r="G125" s="233"/>
-      <c r="H125" s="233"/>
-      <c r="I125" s="233"/>
-      <c r="J125" s="233"/>
-      <c r="K125" s="233"/>
-      <c r="L125" s="234"/>
+      <c r="C125" s="212"/>
+      <c r="D125" s="212"/>
+      <c r="E125" s="212"/>
+      <c r="F125" s="212"/>
+      <c r="G125" s="212"/>
+      <c r="H125" s="212"/>
+      <c r="I125" s="212"/>
+      <c r="J125" s="212"/>
+      <c r="K125" s="212"/>
+      <c r="L125" s="213"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="125" t="s">
@@ -29944,19 +29944,19 @@
       <c r="A132" s="143">
         <v>0</v>
       </c>
-      <c r="B132" s="235" t="s">
+      <c r="B132" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="236"/>
-      <c r="D132" s="236"/>
-      <c r="E132" s="236"/>
-      <c r="F132" s="236"/>
-      <c r="G132" s="236"/>
-      <c r="H132" s="236"/>
-      <c r="I132" s="236"/>
-      <c r="J132" s="236"/>
-      <c r="K132" s="236"/>
-      <c r="L132" s="237"/>
+      <c r="C132" s="215"/>
+      <c r="D132" s="215"/>
+      <c r="E132" s="215"/>
+      <c r="F132" s="215"/>
+      <c r="G132" s="215"/>
+      <c r="H132" s="215"/>
+      <c r="I132" s="215"/>
+      <c r="J132" s="215"/>
+      <c r="K132" s="215"/>
+      <c r="L132" s="216"/>
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="167">
@@ -29980,16 +29980,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="29">
-    <mergeCell ref="A68:L69"/>
-    <mergeCell ref="B125:L125"/>
-    <mergeCell ref="B132:L132"/>
-    <mergeCell ref="A70:L70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B106:L106"/>
-    <mergeCell ref="B108:L108"/>
-    <mergeCell ref="B116:L116"/>
-    <mergeCell ref="B117:L117"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="A7:L7"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B30:L30"/>
     <mergeCell ref="A32:L32"/>
@@ -30003,12 +29999,16 @@
     <mergeCell ref="B54:L54"/>
     <mergeCell ref="B59:L59"/>
     <mergeCell ref="B64:L64"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A68:L69"/>
+    <mergeCell ref="B125:L125"/>
+    <mergeCell ref="B132:L132"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B106:L106"/>
+    <mergeCell ref="B108:L108"/>
+    <mergeCell ref="B116:L116"/>
+    <mergeCell ref="B117:L117"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -30086,75 +30086,75 @@
       <c r="A2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="249" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="256"/>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="M2" s="256"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="M2" s="249"/>
     </row>
     <row r="3" spans="1:13" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="249" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="256"/>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="256"/>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="M3" s="256"/>
+      <c r="C3" s="249"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="249"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="M3" s="249"/>
     </row>
     <row r="4" spans="1:13" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
-      <c r="M4" s="256"/>
+      <c r="C4" s="249"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="M4" s="249"/>
     </row>
     <row r="5" spans="1:13" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34"/>
-      <c r="B5" s="257" t="s">
+      <c r="B5" s="250" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="257"/>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="M5" s="257"/>
+      <c r="C5" s="250"/>
+      <c r="D5" s="250"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="250"/>
+      <c r="G5" s="250"/>
+      <c r="H5" s="250"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="250"/>
+      <c r="L5" s="250"/>
+      <c r="M5" s="250"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="33"/>
@@ -30220,54 +30220,54 @@
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="251" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="248"/>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="248"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="248"/>
-      <c r="K10" s="248"/>
-      <c r="L10" s="248"/>
-      <c r="M10" s="248"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="251"/>
+      <c r="L10" s="251"/>
+      <c r="M10" s="251"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="248" t="s">
+      <c r="A11" s="251" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="248"/>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
-      <c r="M11" s="248"/>
+      <c r="B11" s="251"/>
+      <c r="C11" s="251"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
+      <c r="M11" s="251"/>
     </row>
     <row r="12" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="248" t="s">
+      <c r="A12" s="251" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="248"/>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="248"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="251"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="251"/>
+      <c r="F12" s="251"/>
+      <c r="G12" s="251"/>
+      <c r="H12" s="251"/>
+      <c r="I12" s="251"/>
+      <c r="J12" s="251"/>
+      <c r="K12" s="251"/>
+      <c r="L12" s="251"/>
+      <c r="M12" s="251"/>
     </row>
     <row r="13" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
@@ -30347,38 +30347,38 @@
     <row r="18" spans="1:13" s="11" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="255" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="252"/>
+      <c r="D18" s="255"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="252" t="s">
+      <c r="I18" s="255" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
       <c r="L18" s="12"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="253" t="s">
+      <c r="C19" s="256" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="253"/>
+      <c r="D19" s="256"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="254" t="s">
+      <c r="I19" s="257" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="254"/>
-      <c r="K19" s="254"/>
+      <c r="J19" s="257"/>
+      <c r="K19" s="257"/>
       <c r="L19" s="4"/>
       <c r="M19" s="3"/>
     </row>
@@ -30386,13 +30386,13 @@
       <c r="B20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="255"/>
-      <c r="D20" s="255"/>
+      <c r="C20" s="258"/>
+      <c r="D20" s="258"/>
       <c r="I20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J20" s="255"/>
-      <c r="K20" s="255"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
     </row>
     <row r="24" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
@@ -30506,12 +30506,12 @@
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="249" t="s">
+      <c r="E31" s="252" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="249"/>
+      <c r="F31" s="252"/>
+      <c r="G31" s="252"/>
+      <c r="H31" s="252"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="6"/>
@@ -30523,12 +30523,12 @@
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="250" t="s">
+      <c r="E32" s="253" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="250"/>
-      <c r="G32" s="250"/>
-      <c r="H32" s="250"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="253"/>
+      <c r="H32" s="253"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="6"/>
@@ -30540,12 +30540,12 @@
       <c r="B33" s="9"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="251" t="s">
+      <c r="E33" s="254" t="s">
         <v>45</v>
       </c>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
+      <c r="F33" s="254"/>
+      <c r="G33" s="254"/>
+      <c r="H33" s="254"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="6"/>
@@ -30555,11 +30555,6 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="16">
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
@@ -30571,6 +30566,11 @@
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B10:M10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="1" bottom="0.25" header="0.51180555555555551" footer="0.51180555555555551"/>
